--- a/project_time_sheet.xlsx
+++ b/project_time_sheet.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91A1CB4B-2609-4B1E-B10C-A14C0AE29F4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC5DA5E2-D206-4C0C-9B1D-1F5613E5A13B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2962" uniqueCount="1086">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3121" uniqueCount="1134">
   <si>
     <t xml:space="preserve">  Project Time Sheet — User Guide</t>
   </si>
@@ -3295,6 +3295,150 @@
   </si>
   <si>
     <t>Beckoff IPC reaches &gt;4 GHz speed; tested with phantom mode and production mode, IPC performs well.</t>
+  </si>
+  <si>
+    <t>When you expand the entire window, hide the task bar.</t>
+  </si>
+  <si>
+    <t>When the user expands the entire window, hide the task bar.</t>
+  </si>
+  <si>
+    <t>Feature</t>
+  </si>
+  <si>
+    <t>[2026-08-18]</t>
+  </si>
+  <si>
+    <t>Permission lock: default values must remain accessible to all default users.</t>
+  </si>
+  <si>
+    <t>Permission lock: default values must remain accessible. If allowed range starts at 1, change default to 1 for all users.</t>
+  </si>
+  <si>
+    <t>Avoid showing Contact ABI for range validation as much as possible.</t>
+  </si>
+  <si>
+    <t>For Khurram to follow up. [2026-08-18]</t>
+  </si>
+  <si>
+    <t>Only Admins and Super Admins can change custom distribution.</t>
+  </si>
+  <si>
+    <t>Only Admins and Super Admins can change custom distribution; all other users see default distribution.</t>
+  </si>
+  <si>
+    <t>Make sure the Start and Stop buttons are the same size on the home screen.</t>
+  </si>
+  <si>
+    <t>Hide Recipe Comparison from all users except Super Admins.</t>
+  </si>
+  <si>
+    <t>Hide Recipe Comparison from all users except Super Admins (not fully tested). Clarify cutstyle meaning.</t>
+  </si>
+  <si>
+    <t>When the tool-change flag is enabled, enable tool selection for all users.</t>
+  </si>
+  <si>
+    <t>When tool-change flag is enabled, enable tool selection for all users. Overall check for Recipe Add/Edit bugs.</t>
+  </si>
+  <si>
+    <t>bug, Feature</t>
+  </si>
+  <si>
+    <t>Potential overlap with existing tool-selection task. [2026-08-18]</t>
+  </si>
+  <si>
+    <t>Add a loading spinner for recipes.</t>
+  </si>
+  <si>
+    <t>Fix Edit Recipe pages so they do not use a scrollable page.</t>
+  </si>
+  <si>
+    <t>Potential overlap with existing scrollbar task. [2026-08-18]</t>
+  </si>
+  <si>
+    <t>When cloning a recipe, show a popup that allows the user to rename the cloned recipe.</t>
+  </si>
+  <si>
+    <t>Add Group Control, Batch Control, and All Robots control options.</t>
+  </si>
+  <si>
+    <t>Fix the Last Image page layout.</t>
+  </si>
+  <si>
+    <t>Remove scrolling, retain pagination, fix first image popup not opening after moving to next page.</t>
+  </si>
+  <si>
+    <t>Allow reports to be deleted.</t>
+  </si>
+  <si>
+    <t>PLC Emergency error not shown in Katana when door is opened.</t>
+  </si>
+  <si>
+    <t>Opened the door while PLC was in Emergency error; Katana was not showing any error.</t>
+  </si>
+  <si>
+    <t>DG noticed this on the cell. [2026-08-20]</t>
+  </si>
+  <si>
+    <t>Calibration offset page: table header overlays the settings menu when opened.</t>
+  </si>
+  <si>
+    <t>On the calibration offset page, opening the left settings menu causes the table header to overlay the settings menu.</t>
+  </si>
+  <si>
+    <t>[2026-08-20]</t>
+  </si>
+  <si>
+    <t>Fix robot labels offset; travel direction angle is 180 degrees wrong.</t>
+  </si>
+  <si>
+    <t>Fix the robot labels offset to top; travel direction angle is wrong - 180 degrees opposite.</t>
+  </si>
+  <si>
+    <t>Changing custom distribution causes settings panel to jump from 2 to 4 pages.</t>
+  </si>
+  <si>
+    <t>Changing the custom distribution in the settings panel causes the advanced tab to increase from 2 to 4 pages.</t>
+  </si>
+  <si>
+    <t>Layer panel: Robot IDs and Distribution columns should be swapped.</t>
+  </si>
+  <si>
+    <t>Robot ID column shows distribution limits and distribution column shows robot IDs - they should be swapped.</t>
+  </si>
+  <si>
+    <t>Settings panel is unstable and glitchy - value changes affect items and pagination.</t>
+  </si>
+  <si>
+    <t>Settings panel is not stable and glitchy; a value change causes items and pagination to change unexpectedly.</t>
+  </si>
+  <si>
+    <t>Scaling Y should be inverted.</t>
+  </si>
+  <si>
+    <t>Page freezes during phantom mode; stuck again after navigating to calibration offsets.</t>
+  </si>
+  <si>
+    <t>Page froze while phantom mode was running. After refresh it worked, then got stuck again after navigating to calibration offsets.</t>
+  </si>
+  <si>
+    <t>Stop button should trigger cycle stop, not immediate stop.</t>
+  </si>
+  <si>
+    <t>Stop button should be cycle stop, not immediate stop.</t>
+  </si>
+  <si>
+    <t>Triggers cycle stop same as WPF, check with Khurram. [2026-08-27]</t>
+  </si>
+  <si>
+    <t>Cycle stop button on each robot stays disabled after starting.</t>
+  </si>
+  <si>
+    <t>Cycle stop button on each robot is disabled when starting and continues to stay disabled/locked.</t>
+  </si>
+  <si>
+    <t>[2026-08-27]</t>
   </si>
 </sst>
 </file>
@@ -5176,7 +5320,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N1054"/>
+  <dimension ref="A1:N1077"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.6640625" customWidth="1"/>
@@ -12939,7 +13083,7 @@
         <v>594</v>
       </c>
       <c r="E288" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="F288" t="s">
         <v>431</v>
@@ -13318,7 +13462,7 @@
         <v>66</v>
       </c>
       <c r="E302" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="F302" t="s">
         <v>428</v>
@@ -13343,7 +13487,7 @@
         <v>609</v>
       </c>
       <c r="E303" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F303" t="s">
         <v>428</v>
@@ -13418,7 +13562,7 @@
         <v>66</v>
       </c>
       <c r="E306" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F306" t="s">
         <v>431</v>
@@ -13468,7 +13612,7 @@
         <v>614</v>
       </c>
       <c r="E308" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F308" t="s">
         <v>428</v>
@@ -13763,7 +13907,7 @@
         <v>625</v>
       </c>
       <c r="E319" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F319" t="s">
         <v>428</v>
@@ -13816,7 +13960,7 @@
         <v>61</v>
       </c>
       <c r="E321" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F321" t="s">
         <v>431</v>
@@ -13877,7 +14021,7 @@
         <v>61</v>
       </c>
       <c r="E323" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F323" t="s">
         <v>428</v>
@@ -14002,7 +14146,7 @@
         <v>61</v>
       </c>
       <c r="E328" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F328" t="s">
         <v>431</v>
@@ -14482,7 +14626,7 @@
         <v>66</v>
       </c>
       <c r="E347" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F347" t="s">
         <v>431</v>
@@ -20978,6 +21122,598 @@
         <v>1085</v>
       </c>
       <c r="M1054" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1055" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1055">
+        <v>524</v>
+      </c>
+      <c r="B1055" s="3" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C1055" s="3" t="s">
+        <v>1087</v>
+      </c>
+      <c r="E1055" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1055" t="s">
+        <v>431</v>
+      </c>
+      <c r="K1055" t="s">
+        <v>1088</v>
+      </c>
+      <c r="L1055" t="s">
+        <v>1089</v>
+      </c>
+      <c r="M1055" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1056" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1056">
+        <v>525</v>
+      </c>
+      <c r="B1056" s="3" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C1056" s="3" t="s">
+        <v>1091</v>
+      </c>
+      <c r="E1056" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1056" t="s">
+        <v>431</v>
+      </c>
+      <c r="K1056" t="s">
+        <v>1088</v>
+      </c>
+      <c r="L1056" t="s">
+        <v>1089</v>
+      </c>
+      <c r="M1056" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1057" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1057">
+        <v>526</v>
+      </c>
+      <c r="B1057" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C1057" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="E1057" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1057" t="s">
+        <v>431</v>
+      </c>
+      <c r="K1057" t="s">
+        <v>1088</v>
+      </c>
+      <c r="L1057" t="s">
+        <v>1093</v>
+      </c>
+      <c r="M1057" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1058" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1058">
+        <v>527</v>
+      </c>
+      <c r="B1058" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C1058" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="E1058" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1058" t="s">
+        <v>431</v>
+      </c>
+      <c r="K1058" t="s">
+        <v>1088</v>
+      </c>
+      <c r="L1058" t="s">
+        <v>1089</v>
+      </c>
+      <c r="M1058" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1059" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1059">
+        <v>528</v>
+      </c>
+      <c r="B1059" s="3" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C1059" s="3" t="s">
+        <v>1096</v>
+      </c>
+      <c r="E1059" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1059" t="s">
+        <v>431</v>
+      </c>
+      <c r="K1059" t="s">
+        <v>874</v>
+      </c>
+      <c r="L1059" t="s">
+        <v>1089</v>
+      </c>
+      <c r="M1059" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1060" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1060">
+        <v>529</v>
+      </c>
+      <c r="B1060" s="3" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C1060" s="3" t="s">
+        <v>1098</v>
+      </c>
+      <c r="E1060" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1060" t="s">
+        <v>431</v>
+      </c>
+      <c r="K1060" t="s">
+        <v>1088</v>
+      </c>
+      <c r="L1060" t="s">
+        <v>1089</v>
+      </c>
+      <c r="M1060" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1061" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1061">
+        <v>530</v>
+      </c>
+      <c r="B1061" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C1061" s="3" t="s">
+        <v>1100</v>
+      </c>
+      <c r="E1061" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1061" t="s">
+        <v>431</v>
+      </c>
+      <c r="K1061" t="s">
+        <v>1101</v>
+      </c>
+      <c r="L1061" t="s">
+        <v>1102</v>
+      </c>
+      <c r="M1061" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1062" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1062">
+        <v>531</v>
+      </c>
+      <c r="B1062" s="3" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C1062" s="3" t="s">
+        <v>1103</v>
+      </c>
+      <c r="E1062" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1062" t="s">
+        <v>431</v>
+      </c>
+      <c r="K1062" t="s">
+        <v>1088</v>
+      </c>
+      <c r="L1062" t="s">
+        <v>1089</v>
+      </c>
+      <c r="M1062" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1063" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1063">
+        <v>532</v>
+      </c>
+      <c r="B1063" s="3" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C1063" s="3" t="s">
+        <v>1104</v>
+      </c>
+      <c r="E1063" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1063" t="s">
+        <v>431</v>
+      </c>
+      <c r="K1063" t="s">
+        <v>717</v>
+      </c>
+      <c r="L1063" t="s">
+        <v>1105</v>
+      </c>
+      <c r="M1063" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1064" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1064">
+        <v>533</v>
+      </c>
+      <c r="B1064" s="3" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C1064" s="3" t="s">
+        <v>1106</v>
+      </c>
+      <c r="E1064" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1064" t="s">
+        <v>431</v>
+      </c>
+      <c r="K1064" t="s">
+        <v>1088</v>
+      </c>
+      <c r="L1064" t="s">
+        <v>1089</v>
+      </c>
+      <c r="M1064" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1065" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1065">
+        <v>534</v>
+      </c>
+      <c r="B1065" s="3" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C1065" s="3" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E1065" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1065" t="s">
+        <v>431</v>
+      </c>
+      <c r="K1065" t="s">
+        <v>1088</v>
+      </c>
+      <c r="L1065" t="s">
+        <v>1089</v>
+      </c>
+      <c r="M1065" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1066" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1066">
+        <v>535</v>
+      </c>
+      <c r="B1066" s="3" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C1066" s="3" t="s">
+        <v>1109</v>
+      </c>
+      <c r="E1066" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1066" t="s">
+        <v>431</v>
+      </c>
+      <c r="K1066" t="s">
+        <v>717</v>
+      </c>
+      <c r="L1066" t="s">
+        <v>1089</v>
+      </c>
+      <c r="M1066" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1067" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1067">
+        <v>536</v>
+      </c>
+      <c r="B1067" s="3" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C1067" s="3" t="s">
+        <v>1110</v>
+      </c>
+      <c r="E1067" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1067" t="s">
+        <v>431</v>
+      </c>
+      <c r="K1067" t="s">
+        <v>1088</v>
+      </c>
+      <c r="L1067" t="s">
+        <v>1089</v>
+      </c>
+      <c r="M1067" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1068" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1068">
+        <v>537</v>
+      </c>
+      <c r="B1068" s="3" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C1068" s="3" t="s">
+        <v>1112</v>
+      </c>
+      <c r="E1068" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1068" t="s">
+        <v>427</v>
+      </c>
+      <c r="K1068" t="s">
+        <v>717</v>
+      </c>
+      <c r="L1068" t="s">
+        <v>1113</v>
+      </c>
+      <c r="M1068" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1069" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1069">
+        <v>538</v>
+      </c>
+      <c r="B1069" s="3" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C1069" s="3" t="s">
+        <v>1115</v>
+      </c>
+      <c r="E1069" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1069" t="s">
+        <v>431</v>
+      </c>
+      <c r="K1069" t="s">
+        <v>717</v>
+      </c>
+      <c r="L1069" t="s">
+        <v>1116</v>
+      </c>
+      <c r="M1069" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1070" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1070">
+        <v>539</v>
+      </c>
+      <c r="B1070" s="3" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C1070" s="3" t="s">
+        <v>1118</v>
+      </c>
+      <c r="E1070" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1070" t="s">
+        <v>431</v>
+      </c>
+      <c r="K1070" t="s">
+        <v>717</v>
+      </c>
+      <c r="L1070" t="s">
+        <v>1116</v>
+      </c>
+      <c r="M1070" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1071" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1071">
+        <v>540</v>
+      </c>
+      <c r="B1071" s="3" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C1071" s="3" t="s">
+        <v>1120</v>
+      </c>
+      <c r="E1071" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1071" t="s">
+        <v>431</v>
+      </c>
+      <c r="K1071" t="s">
+        <v>717</v>
+      </c>
+      <c r="L1071" t="s">
+        <v>1116</v>
+      </c>
+      <c r="M1071" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1072" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1072">
+        <v>541</v>
+      </c>
+      <c r="B1072" s="3" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C1072" s="3" t="s">
+        <v>1122</v>
+      </c>
+      <c r="E1072" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1072" t="s">
+        <v>431</v>
+      </c>
+      <c r="K1072" t="s">
+        <v>717</v>
+      </c>
+      <c r="L1072" t="s">
+        <v>1116</v>
+      </c>
+      <c r="M1072" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1073" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1073">
+        <v>542</v>
+      </c>
+      <c r="B1073" s="3" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C1073" s="3" t="s">
+        <v>1124</v>
+      </c>
+      <c r="E1073" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1073" t="s">
+        <v>431</v>
+      </c>
+      <c r="K1073" t="s">
+        <v>717</v>
+      </c>
+      <c r="L1073" t="s">
+        <v>1116</v>
+      </c>
+      <c r="M1073" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1074" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1074">
+        <v>543</v>
+      </c>
+      <c r="B1074" s="3" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C1074" s="3" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E1074" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1074" t="s">
+        <v>431</v>
+      </c>
+      <c r="K1074" t="s">
+        <v>717</v>
+      </c>
+      <c r="L1074" t="s">
+        <v>1116</v>
+      </c>
+      <c r="M1074" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1075" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1075">
+        <v>544</v>
+      </c>
+      <c r="B1075" s="3" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C1075" s="3" t="s">
+        <v>1127</v>
+      </c>
+      <c r="E1075" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1075" t="s">
+        <v>431</v>
+      </c>
+      <c r="K1075" t="s">
+        <v>717</v>
+      </c>
+      <c r="L1075" t="s">
+        <v>1116</v>
+      </c>
+      <c r="M1075" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1076" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1076">
+        <v>545</v>
+      </c>
+      <c r="B1076" s="3" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C1076" s="3" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E1076" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1076" t="s">
+        <v>431</v>
+      </c>
+      <c r="L1076" t="s">
+        <v>1130</v>
+      </c>
+      <c r="M1076" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1077" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1077">
+        <v>546</v>
+      </c>
+      <c r="B1077" s="3" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C1077" s="3" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1077" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1077" t="s">
+        <v>431</v>
+      </c>
+      <c r="L1077" t="s">
+        <v>1133</v>
+      </c>
+      <c r="M1077" t="s">
         <v>69</v>
       </c>
     </row>
@@ -21107,6 +21843,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100959716F11FB6F9409089B98D1C11D330" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bc55ac45923017d94ee4534da3224188">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2e20d828-e3fd-41fd-921c-fbe0ff523ae8" xmlns:ns3="adfc7943-f9ee-4478-a01e-ebfcb6e54f53" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5bc17ad4f23ab8382a0bb5b03decca58" ns2:_="" ns3:_="">
     <xsd:import namespace="2e20d828-e3fd-41fd-921c-fbe0ff523ae8"/>
@@ -21361,15 +22106,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -21382,6 +22118,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{737DCCA1-99B2-40A5-A4E9-9FBBAC380C60}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CE6A3B7-F954-4629-B802-2205DECE6851}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -21400,14 +22144,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{737DCCA1-99B2-40A5-A4E9-9FBBAC380C60}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{407A8743-A532-48E3-9004-715BF423F4DA}">
   <ds:schemaRefs>

--- a/project_time_sheet.xlsx
+++ b/project_time_sheet.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC5DA5E2-D206-4C0C-9B1D-1F5613E5A13B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{497D3D87-B10F-49BA-A317-4A6C351579D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3121" uniqueCount="1134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3565" uniqueCount="1283">
   <si>
     <t xml:space="preserve">  Project Time Sheet — User Guide</t>
   </si>
@@ -3439,6 +3439,453 @@
   </si>
   <si>
     <t>[2026-08-27]</t>
+  </si>
+  <si>
+    <t>AI/RAW image separation: display annotated inference image in AI pane and original in RAW pane</t>
+  </si>
+  <si>
+    <t>Display annotated inference image in AI pane and original image in RAW pane.</t>
+  </si>
+  <si>
+    <t>Critical</t>
+  </si>
+  <si>
+    <t>Scan-result ingestion: configure EyeQ to receive AI_CORE results through /api/ingest/scan-result</t>
+  </si>
+  <si>
+    <t>Configure EyeQ to receive AI_CORE results through /api/ingest/scan-result.</t>
+  </si>
+  <si>
+    <t>Missing height handling: allow width and length to be stored when height cannot be measured</t>
+  </si>
+  <si>
+    <t>Allow width and length to be stored when height cannot be measured.</t>
+  </si>
+  <si>
+    <t>Database scan storage: store AI_CORE scan results, products and measurements in PostgreSQL</t>
+  </si>
+  <si>
+    <t>Store AI_CORE scan results, products and measurements in PostgreSQL.</t>
+  </si>
+  <si>
+    <t>Trends integration: display product measurements, counts and recent images</t>
+  </si>
+  <si>
+    <t>Display product measurements, counts and recent images.</t>
+  </si>
+  <si>
+    <t>CSV measurement export: export stored product and recipe information</t>
+  </si>
+  <si>
+    <t>Export stored product and recipe information.</t>
+  </si>
+  <si>
+    <t>Duplicate scan investigation: investigate inflated boards and product counts</t>
+  </si>
+  <si>
+    <t>Investigate inflated boards and product counts.</t>
+  </si>
+  <si>
+    <t>PostgreSQL development setup: install/configure PostgreSQL and create EyeQ database for development</t>
+  </si>
+  <si>
+    <t>Install/configure PostgreSQL and create EyeQ database for development.</t>
+  </si>
+  <si>
+    <t>PostgreSQL port conflict: avoid conflict with an existing PostgreSQL 18 instance on port 5432</t>
+  </si>
+  <si>
+    <t>Avoid conflict with an existing PostgreSQL 18 instance on port 5432.</t>
+  </si>
+  <si>
+    <t>Database provisioner: bundle database creation and migration with the installer</t>
+  </si>
+  <si>
+    <t>Bundle database creation and migration with the installer.</t>
+  </si>
+  <si>
+    <t>AI_CORE service installation: package AI_CORE as a Windows service alongside EyeQ</t>
+  </si>
+  <si>
+    <t>Package AI_CORE as a Windows service alongside EyeQ.</t>
+  </si>
+  <si>
+    <t>AI_CORE writable data path: move .agent-data and runtime state outside Program Files</t>
+  </si>
+  <si>
+    <t>Move .agent-data and runtime state outside Program Files.</t>
+  </si>
+  <si>
+    <t>EyeQ Windows service: install EyeQ as an automatically starting service</t>
+  </si>
+  <si>
+    <t>Install EyeQ as an automatically starting service.</t>
+  </si>
+  <si>
+    <t>Recovery supervisor: add monitoring and automatic service recovery</t>
+  </si>
+  <si>
+    <t>Add monitoring and automatic service recovery.</t>
+  </si>
+  <si>
+    <t>EyeQ launcher: add desktop launcher for EyeQ and AI_CORE</t>
+  </si>
+  <si>
+    <t>Add desktop launcher for EyeQ and AI_CORE.</t>
+  </si>
+  <si>
+    <t>Launcher icon: add EyeQ icon to installed shortcut</t>
+  </si>
+  <si>
+    <t>Add EyeQ icon to installed shortcut.</t>
+  </si>
+  <si>
+    <t>Offline all-in-one installer: build installer containing EyeQ, AI_CORE and PostgreSQL</t>
+  </si>
+  <si>
+    <t>Build installer containing EyeQ, AI_CORE and PostgreSQL.</t>
+  </si>
+  <si>
+    <t>Clean uninstaller: provide removal of installed services and applications</t>
+  </si>
+  <si>
+    <t>Provide removal of installed services and applications.</t>
+  </si>
+  <si>
+    <t>Copy-and-run fallback: document manual folder-copy deployment</t>
+  </si>
+  <si>
+    <t>Document manual folder-copy deployment.</t>
+  </si>
+  <si>
+    <t>Installer documentation: write installation, update and recovery instructions in Obsidian</t>
+  </si>
+  <si>
+    <t>Write installation, update and recovery instructions in Obsidian.</t>
+  </si>
+  <si>
+    <t>Firewall access: allow external access to EyeQ on TCP port 5000</t>
+  </si>
+  <si>
+    <t>Allow external access to EyeQ on TCP port 5000.</t>
+  </si>
+  <si>
+    <t>Bind EyeQ externally: ensure EyeQ listens on all network interfaces</t>
+  </si>
+  <si>
+    <t>Ensure EyeQ listens on all network interfaces.</t>
+  </si>
+  <si>
+    <t>Tablet access diagnosis: diagnose why AI_CORE was reachable but EyeQ was not</t>
+  </si>
+  <si>
+    <t>Diagnose why AI_CORE was reachable but EyeQ was not.</t>
+  </si>
+  <si>
+    <t>API-key packaging: ensure packaged AI_CORE and EyeQ share an ingest API key</t>
+  </si>
+  <si>
+    <t>Ensure packaged AI_CORE and EyeQ share an ingest API key.</t>
+  </si>
+  <si>
+    <t>Client file selection: preserve browser-side image and video upload</t>
+  </si>
+  <si>
+    <t>Preserve browser-side image and video upload.</t>
+  </si>
+  <si>
+    <t>Server file selection: add server-side file browsing option</t>
+  </si>
+  <si>
+    <t>Add server-side file browsing option.</t>
+  </si>
+  <si>
+    <t>Missing Tkinter failure: remove reliance on Tkinter for packaged file browsing</t>
+  </si>
+  <si>
+    <t>Remove reliance on Tkinter for packaged file browsing.</t>
+  </si>
+  <si>
+    <t>RealSense camera deployment: diagnose RealSense discovery after installation</t>
+  </si>
+  <si>
+    <t>Diagnose RealSense discovery after installation.</t>
+  </si>
+  <si>
+    <t>Camera-network discovery: make RealSense detection independent of adapter name</t>
+  </si>
+  <si>
+    <t>Make RealSense detection independent of adapter name.</t>
+  </si>
+  <si>
+    <t>Jumbo packet configuration: configure compatible Ethernet jumbo frames</t>
+  </si>
+  <si>
+    <t>Configure compatible Ethernet jumbo frames.</t>
+  </si>
+  <si>
+    <t>Camera calibration source: allow 2D Metrology to consume saved camera calibration</t>
+  </si>
+  <si>
+    <t>Allow 2D Metrology to consume saved camera calibration.</t>
+  </si>
+  <si>
+    <t>Calibration discrepancy: fix displayed manual value remaining at 7.46 px/mm</t>
+  </si>
+  <si>
+    <t>Fix displayed manual value remaining at 7.46 px/mm.</t>
+  </si>
+  <si>
+    <t>Manual metrology UI: hide camera selector when manual pixels/mm is selected</t>
+  </si>
+  <si>
+    <t>Hide camera selector when manual pixels/mm is selected.</t>
+  </si>
+  <si>
+    <t>Recipe detector integration: receive AI-detected recipe information from AI_CORE</t>
+  </si>
+  <si>
+    <t>Receive AI-detected recipe information from AI_CORE.</t>
+  </si>
+  <si>
+    <t>AI recipe fields: store recipe detected by AI and its decision metadata</t>
+  </si>
+  <si>
+    <t>Store recipe detected by AI and its decision metadata.</t>
+  </si>
+  <si>
+    <t>Optional recipe input: allow publisher to operate when recipe detector port is disconnected</t>
+  </si>
+  <si>
+    <t>Allow publisher to operate when recipe detector port is disconnected.</t>
+  </si>
+  <si>
+    <t>Recipe-source policy: keep EyeQ as authoritative recipe source with optional AI recommendation</t>
+  </si>
+  <si>
+    <t>Keep EyeQ as authoritative recipe source with optional AI recommendation.</t>
+  </si>
+  <si>
+    <t>Recipe selection mode: document how to change recipe selection from PLC to manual</t>
+  </si>
+  <si>
+    <t>Document how to change recipe selection from PLC to manual.</t>
+  </si>
+  <si>
+    <t>AI view feature flags: diagnose missing AI/side-by-side controls</t>
+  </si>
+  <si>
+    <t>Diagnose missing AI/side-by-side controls.</t>
+  </si>
+  <si>
+    <t>PostgreSQL feature query: diagnose incorrect FeatureSettings SQL query</t>
+  </si>
+  <si>
+    <t>Diagnose incorrect FeatureSettings SQL query.</t>
+  </si>
+  <si>
+    <t>Recipes-page load reduction: remove expensive header calculation from /recipes</t>
+  </si>
+  <si>
+    <t>Remove expensive header calculation from /recipes.</t>
+  </si>
+  <si>
+    <t>Reviewer critical fixes: review 24 reported EyeQ issues and propose corrections</t>
+  </si>
+  <si>
+    <t>Review 24 reported EyeQ issues and propose corrections.</t>
+  </si>
+  <si>
+    <t>Scan-source statistics: restore 3D-only production-stat semantics</t>
+  </si>
+  <si>
+    <t>Restore 3D-only production-stat semantics.</t>
+  </si>
+  <si>
+    <t>Hardcoded ingest self-call: replace/plan removal of hardcoded localhost self-HTTP call</t>
+  </si>
+  <si>
+    <t>Replace/plan removal of hardcoded localhost self-HTTP call.</t>
+  </si>
+  <si>
+    <t>CSV injection protection: escape and quote AI recipe fields in CSV</t>
+  </si>
+  <si>
+    <t>Escape and quote AI recipe fields in CSV.</t>
+  </si>
+  <si>
+    <t>Machine ID attribution: remove hardcoded machine ID assumptions</t>
+  </si>
+  <si>
+    <t>Remove hardcoded machine ID assumptions.</t>
+  </si>
+  <si>
+    <t>Image retention risk: identify unbounded AI preview storage</t>
+  </si>
+  <si>
+    <t>Identify unbounded AI preview storage.</t>
+  </si>
+  <si>
+    <t>Ingest concurrency: identify process-wide serialization and missing distributed uniqueness</t>
+  </si>
+  <si>
+    <t>Identify process-wide serialization and missing distributed uniqueness.</t>
+  </si>
+  <si>
+    <t>EyeQ localization: synchronize EyeQ language with AI_CORE</t>
+  </si>
+  <si>
+    <t>Synchronize EyeQ language with AI_CORE.</t>
+  </si>
+  <si>
+    <t>Access-level model: implement Levels 0-4 while preserving legacy roles</t>
+  </si>
+  <si>
+    <t>Implement Levels 0-4 while preserving legacy roles.</t>
+  </si>
+  <si>
+    <t>Anonymous live access: allow logged-out users to view live data and charts</t>
+  </si>
+  <si>
+    <t>Allow logged-out users to view live data and charts.</t>
+  </si>
+  <si>
+    <t>Operator permissions: permit operators to load recipes</t>
+  </si>
+  <si>
+    <t>Permit operators to load recipes.</t>
+  </si>
+  <si>
+    <t>Supervisor permissions: permit supervisors to load and create recipes</t>
+  </si>
+  <si>
+    <t>Permit supervisors to load and create recipes.</t>
+  </si>
+  <si>
+    <t>DataViewer permissions: permit collected-data viewing and CSV download</t>
+  </si>
+  <si>
+    <t>Permit collected-data viewing and CSV download.</t>
+  </si>
+  <si>
+    <t>Admin permissions: permit recipe management, users and configuration</t>
+  </si>
+  <si>
+    <t>Permit recipe management, users and configuration.</t>
+  </si>
+  <si>
+    <t>Tech permissions: restrict Tech to routine camera/backup maintenance</t>
+  </si>
+  <si>
+    <t>Restrict Tech to routine camera/backup maintenance.</t>
+  </si>
+  <si>
+    <t>User account management: add Operator, Supervisor and DataViewer role choices</t>
+  </si>
+  <si>
+    <t>Add Operator, Supervisor and DataViewer role choices.</t>
+  </si>
+  <si>
+    <t>Access matrix: add capability-versus-role table to /UserAccounts</t>
+  </si>
+  <si>
+    <t>Add capability-versus-role table to /UserAccounts.</t>
+  </si>
+  <si>
+    <t>Remove Level 0 account creation: prevent creation of Level 0/User accounts</t>
+  </si>
+  <si>
+    <t>Prevent creation of Level 0/User accounts.</t>
+  </si>
+  <si>
+    <t>Password entry protection: require passwords and discourage browser credential storage</t>
+  </si>
+  <si>
+    <t>Require passwords and discourage browser credential storage.</t>
+  </si>
+  <si>
+    <t>EyeQ missing styles: diagnose oversized icons and missing component styling</t>
+  </si>
+  <si>
+    <t>Diagnose oversized icons and missing component styling.</t>
+  </si>
+  <si>
+    <t>Production-style local launch: launch EyeQ from published output to serve all static assets</t>
+  </si>
+  <si>
+    <t>Launch EyeQ from published output to serve all static assets.</t>
+  </si>
+  <si>
+    <t>Blank chart panels: fix ApexCharts localization lifecycle exception</t>
+  </si>
+  <si>
+    <t>Fix ApexCharts localization lifecycle exception.</t>
+  </si>
+  <si>
+    <t>Height chart overflow: make Height Profile chart responsive to viewport height</t>
+  </si>
+  <si>
+    <t>Make Height Profile chart responsive to viewport height.</t>
+  </si>
+  <si>
+    <t>Recipe statistics table: add independent daily Stats table</t>
+  </si>
+  <si>
+    <t>Add independent daily Stats table.</t>
+  </si>
+  <si>
+    <t>Statistics backfill: populate Stats from historical scans</t>
+  </si>
+  <si>
+    <t>Populate Stats from historical scans.</t>
+  </si>
+  <si>
+    <t>Atomic statistics updates: update daily counters as scans are stored</t>
+  </si>
+  <si>
+    <t>Update daily counters as scans are stored.</t>
+  </si>
+  <si>
+    <t>Separate defect metrics: store defective products separately from defect instances</t>
+  </si>
+  <si>
+    <t>Store defective products separately from defect instances.</t>
+  </si>
+  <si>
+    <t>Fast recipe statistics: change /recipes to read daily summary rows</t>
+  </si>
+  <si>
+    <t>Change /recipes to read daily summary rows.</t>
+  </si>
+  <si>
+    <t>Statistics migration verification: compare backfilled summary against source records</t>
+  </si>
+  <si>
+    <t>Compare backfilled summary against source records.</t>
+  </si>
+  <si>
+    <t>Nightly statistics reconciliation: periodically rebuild/check summary values</t>
+  </si>
+  <si>
+    <t>Periodically rebuild/check summary values.</t>
+  </si>
+  <si>
+    <t>Rebuild Statistics admin action: add administrator command to reconstruct summary rows</t>
+  </si>
+  <si>
+    <t>Add administrator command to reconstruct summary rows.</t>
+  </si>
+  <si>
+    <t>AI preview retention: add maximum age/size cleanup for AI images</t>
+  </si>
+  <si>
+    <t>Add maximum age/size cleanup for AI images.</t>
+  </si>
+  <si>
+    <t>Obsidian activity documentation: maintain architecture, installation and operating notes</t>
+  </si>
+  <si>
+    <t>Maintain architecture, installation and operating notes.</t>
   </si>
 </sst>
 </file>
@@ -5320,7 +5767,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N1077"/>
+  <dimension ref="A1:N1151"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.6640625" customWidth="1"/>
@@ -21715,6 +22162,2137 @@
       </c>
       <c r="M1077" t="s">
         <v>69</v>
+      </c>
+    </row>
+    <row r="1078" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1078">
+        <v>547</v>
+      </c>
+      <c r="B1078" s="3" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C1078" s="3" t="s">
+        <v>1135</v>
+      </c>
+      <c r="D1078" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1078" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1078" t="s">
+        <v>1136</v>
+      </c>
+      <c r="H1078">
+        <v>6</v>
+      </c>
+      <c r="J1078" s="42">
+        <v>46262</v>
+      </c>
+      <c r="M1078" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1079" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1079">
+        <v>548</v>
+      </c>
+      <c r="B1079" s="3" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C1079" s="3" t="s">
+        <v>1138</v>
+      </c>
+      <c r="D1079" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1079" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1079" t="s">
+        <v>1136</v>
+      </c>
+      <c r="H1079">
+        <v>8</v>
+      </c>
+      <c r="J1079" s="42">
+        <v>46262</v>
+      </c>
+      <c r="M1079" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1080" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1080">
+        <v>549</v>
+      </c>
+      <c r="B1080" s="3" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C1080" s="3" t="s">
+        <v>1140</v>
+      </c>
+      <c r="D1080" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1080" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1080" t="s">
+        <v>1136</v>
+      </c>
+      <c r="H1080">
+        <v>4</v>
+      </c>
+      <c r="J1080" s="42">
+        <v>46262</v>
+      </c>
+      <c r="M1080" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1081" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1081">
+        <v>550</v>
+      </c>
+      <c r="B1081" s="3" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C1081" s="3" t="s">
+        <v>1142</v>
+      </c>
+      <c r="D1081" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1081" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1081" t="s">
+        <v>1136</v>
+      </c>
+      <c r="H1081">
+        <v>8</v>
+      </c>
+      <c r="J1081" s="42">
+        <v>46262</v>
+      </c>
+      <c r="M1081" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1082" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1082">
+        <v>551</v>
+      </c>
+      <c r="B1082" s="3" t="s">
+        <v>1143</v>
+      </c>
+      <c r="C1082" s="3" t="s">
+        <v>1144</v>
+      </c>
+      <c r="D1082" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1082" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1082" t="s">
+        <v>1136</v>
+      </c>
+      <c r="H1082">
+        <v>8</v>
+      </c>
+      <c r="J1082" s="42">
+        <v>46262</v>
+      </c>
+      <c r="M1082" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1083" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1083">
+        <v>552</v>
+      </c>
+      <c r="B1083" s="3" t="s">
+        <v>1145</v>
+      </c>
+      <c r="C1083" s="3" t="s">
+        <v>1146</v>
+      </c>
+      <c r="D1083" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1083" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1083" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1083">
+        <v>4</v>
+      </c>
+      <c r="J1083" s="42">
+        <v>46262</v>
+      </c>
+      <c r="M1083" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1084" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1084">
+        <v>553</v>
+      </c>
+      <c r="B1084" s="3" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C1084" s="3" t="s">
+        <v>1148</v>
+      </c>
+      <c r="D1084" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1084" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1084" t="s">
+        <v>1136</v>
+      </c>
+      <c r="H1084">
+        <v>3</v>
+      </c>
+      <c r="J1084" s="42">
+        <v>46262</v>
+      </c>
+      <c r="M1084" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1085" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1085">
+        <v>554</v>
+      </c>
+      <c r="B1085" s="3" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C1085" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D1085" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1085" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1085" t="s">
+        <v>1136</v>
+      </c>
+      <c r="H1085">
+        <v>4</v>
+      </c>
+      <c r="J1085" s="42">
+        <v>46264</v>
+      </c>
+      <c r="M1085" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1086" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1086">
+        <v>555</v>
+      </c>
+      <c r="B1086" s="3" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C1086" s="3" t="s">
+        <v>1152</v>
+      </c>
+      <c r="D1086" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1086" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1086" t="s">
+        <v>1136</v>
+      </c>
+      <c r="H1086">
+        <v>4</v>
+      </c>
+      <c r="J1086" s="42">
+        <v>46263</v>
+      </c>
+      <c r="M1086" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1087" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1087">
+        <v>556</v>
+      </c>
+      <c r="B1087" s="3" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C1087" s="3" t="s">
+        <v>1154</v>
+      </c>
+      <c r="D1087" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1087" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1087" t="s">
+        <v>1136</v>
+      </c>
+      <c r="H1087">
+        <v>6</v>
+      </c>
+      <c r="J1087" s="42">
+        <v>46263</v>
+      </c>
+      <c r="M1087" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1088" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1088">
+        <v>557</v>
+      </c>
+      <c r="B1088" s="3" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C1088" s="3" t="s">
+        <v>1156</v>
+      </c>
+      <c r="D1088" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1088" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1088" t="s">
+        <v>1136</v>
+      </c>
+      <c r="H1088">
+        <v>10</v>
+      </c>
+      <c r="J1088" s="42">
+        <v>46263</v>
+      </c>
+      <c r="M1088" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1089" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1089">
+        <v>558</v>
+      </c>
+      <c r="B1089" s="3" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C1089" s="3" t="s">
+        <v>1158</v>
+      </c>
+      <c r="D1089" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1089" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1089" t="s">
+        <v>1136</v>
+      </c>
+      <c r="H1089">
+        <v>4</v>
+      </c>
+      <c r="J1089" s="42">
+        <v>46263</v>
+      </c>
+      <c r="M1089" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1090" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1090">
+        <v>559</v>
+      </c>
+      <c r="B1090" s="3" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C1090" s="3" t="s">
+        <v>1160</v>
+      </c>
+      <c r="D1090" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1090" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1090" t="s">
+        <v>1136</v>
+      </c>
+      <c r="H1090">
+        <v>6</v>
+      </c>
+      <c r="J1090" s="42">
+        <v>46263</v>
+      </c>
+      <c r="M1090" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1091" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1091">
+        <v>560</v>
+      </c>
+      <c r="B1091" s="3" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C1091" s="3" t="s">
+        <v>1162</v>
+      </c>
+      <c r="D1091" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1091" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1091" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1091">
+        <v>8</v>
+      </c>
+      <c r="J1091" s="42">
+        <v>46263</v>
+      </c>
+      <c r="M1091" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1092" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1092">
+        <v>561</v>
+      </c>
+      <c r="B1092" s="3" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C1092" s="3" t="s">
+        <v>1164</v>
+      </c>
+      <c r="D1092" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1092" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1092" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1092">
+        <v>8</v>
+      </c>
+      <c r="J1092" s="42">
+        <v>46263</v>
+      </c>
+      <c r="M1092" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1093" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1093">
+        <v>562</v>
+      </c>
+      <c r="B1093" s="3" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C1093" s="3" t="s">
+        <v>1166</v>
+      </c>
+      <c r="D1093" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1093" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1093" t="s">
+        <v>431</v>
+      </c>
+      <c r="H1093">
+        <v>2</v>
+      </c>
+      <c r="J1093" s="42">
+        <v>46263</v>
+      </c>
+      <c r="M1093" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1094" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1094">
+        <v>563</v>
+      </c>
+      <c r="B1094" s="3" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C1094" s="3" t="s">
+        <v>1168</v>
+      </c>
+      <c r="D1094" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1094" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1094" t="s">
+        <v>1136</v>
+      </c>
+      <c r="H1094">
+        <v>16</v>
+      </c>
+      <c r="J1094" s="42">
+        <v>46263</v>
+      </c>
+      <c r="M1094" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1095" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1095">
+        <v>564</v>
+      </c>
+      <c r="B1095" s="3" t="s">
+        <v>1169</v>
+      </c>
+      <c r="C1095" s="3" t="s">
+        <v>1170</v>
+      </c>
+      <c r="D1095" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1095" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1095" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1095">
+        <v>6</v>
+      </c>
+      <c r="J1095" s="42">
+        <v>46263</v>
+      </c>
+      <c r="M1095" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1096" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1096">
+        <v>565</v>
+      </c>
+      <c r="B1096" s="3" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C1096" s="3" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D1096" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1096" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1096" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1096">
+        <v>3</v>
+      </c>
+      <c r="J1096" s="42">
+        <v>46263</v>
+      </c>
+      <c r="M1096" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1097" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1097">
+        <v>566</v>
+      </c>
+      <c r="B1097" s="3" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C1097" s="3" t="s">
+        <v>1174</v>
+      </c>
+      <c r="D1097" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1097" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1097" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1097">
+        <v>4</v>
+      </c>
+      <c r="J1097" s="42">
+        <v>46263</v>
+      </c>
+      <c r="M1097" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1098" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1098">
+        <v>567</v>
+      </c>
+      <c r="B1098" s="3" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C1098" s="3" t="s">
+        <v>1176</v>
+      </c>
+      <c r="D1098" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1098" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1098" t="s">
+        <v>1136</v>
+      </c>
+      <c r="H1098">
+        <v>2</v>
+      </c>
+      <c r="J1098" s="42">
+        <v>46263</v>
+      </c>
+      <c r="M1098" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1099" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1099">
+        <v>568</v>
+      </c>
+      <c r="B1099" s="3" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C1099" s="3" t="s">
+        <v>1178</v>
+      </c>
+      <c r="D1099" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1099" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1099" t="s">
+        <v>1136</v>
+      </c>
+      <c r="H1099">
+        <v>2</v>
+      </c>
+      <c r="J1099" s="42">
+        <v>46263</v>
+      </c>
+      <c r="M1099" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1100" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1100">
+        <v>569</v>
+      </c>
+      <c r="B1100" s="3" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C1100" s="3" t="s">
+        <v>1180</v>
+      </c>
+      <c r="D1100" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1100" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1100" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1100">
+        <v>2</v>
+      </c>
+      <c r="J1100" s="42">
+        <v>46263</v>
+      </c>
+      <c r="M1100" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1101" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1101">
+        <v>570</v>
+      </c>
+      <c r="B1101" s="3" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C1101" s="3" t="s">
+        <v>1182</v>
+      </c>
+      <c r="D1101" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1101" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1101" t="s">
+        <v>1136</v>
+      </c>
+      <c r="H1101">
+        <v>5</v>
+      </c>
+      <c r="J1101" s="42">
+        <v>46263</v>
+      </c>
+      <c r="M1101" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1102" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1102">
+        <v>571</v>
+      </c>
+      <c r="B1102" s="3" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C1102" s="3" t="s">
+        <v>1184</v>
+      </c>
+      <c r="D1102" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1102" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1102" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1102">
+        <v>4</v>
+      </c>
+      <c r="J1102" s="42">
+        <v>46263</v>
+      </c>
+      <c r="M1102" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1103" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1103">
+        <v>572</v>
+      </c>
+      <c r="B1103" s="3" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C1103" s="3" t="s">
+        <v>1186</v>
+      </c>
+      <c r="D1103" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1103" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1103" t="s">
+        <v>431</v>
+      </c>
+      <c r="H1103">
+        <v>5</v>
+      </c>
+      <c r="J1103" s="42">
+        <v>46263</v>
+      </c>
+      <c r="M1103" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1104" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1104">
+        <v>573</v>
+      </c>
+      <c r="B1104" s="3" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C1104" s="3" t="s">
+        <v>1188</v>
+      </c>
+      <c r="D1104" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1104" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1104" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1104">
+        <v>3</v>
+      </c>
+      <c r="J1104" s="42">
+        <v>46263</v>
+      </c>
+      <c r="M1104" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1105" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1105">
+        <v>574</v>
+      </c>
+      <c r="B1105" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C1105" s="3" t="s">
+        <v>1190</v>
+      </c>
+      <c r="D1105" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1105" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1105" t="s">
+        <v>1136</v>
+      </c>
+      <c r="H1105">
+        <v>8</v>
+      </c>
+      <c r="J1105" s="42">
+        <v>46263</v>
+      </c>
+      <c r="M1105" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1106" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1106">
+        <v>575</v>
+      </c>
+      <c r="B1106" s="3" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C1106" s="3" t="s">
+        <v>1192</v>
+      </c>
+      <c r="D1106" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1106" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1106" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1106">
+        <v>6</v>
+      </c>
+      <c r="J1106" s="42">
+        <v>46263</v>
+      </c>
+      <c r="M1106" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1107" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1107">
+        <v>576</v>
+      </c>
+      <c r="B1107" s="3" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C1107" s="3" t="s">
+        <v>1194</v>
+      </c>
+      <c r="D1107" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1107" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1107" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1107">
+        <v>3</v>
+      </c>
+      <c r="J1107" s="42">
+        <v>46263</v>
+      </c>
+      <c r="M1107" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1108" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1108">
+        <v>577</v>
+      </c>
+      <c r="B1108" s="3" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C1108" s="3" t="s">
+        <v>1196</v>
+      </c>
+      <c r="D1108" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1108" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1108" t="s">
+        <v>1136</v>
+      </c>
+      <c r="H1108">
+        <v>6</v>
+      </c>
+      <c r="J1108" s="42">
+        <v>46264</v>
+      </c>
+      <c r="M1108" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1109" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1109">
+        <v>578</v>
+      </c>
+      <c r="B1109" s="3" t="s">
+        <v>1197</v>
+      </c>
+      <c r="C1109" s="3" t="s">
+        <v>1198</v>
+      </c>
+      <c r="D1109" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1109" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1109" t="s">
+        <v>1136</v>
+      </c>
+      <c r="H1109">
+        <v>4</v>
+      </c>
+      <c r="J1109" s="42">
+        <v>46264</v>
+      </c>
+      <c r="M1109" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1110" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1110">
+        <v>579</v>
+      </c>
+      <c r="B1110" s="3" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C1110" s="3" t="s">
+        <v>1200</v>
+      </c>
+      <c r="D1110" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1110" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1110" t="s">
+        <v>431</v>
+      </c>
+      <c r="H1110">
+        <v>2</v>
+      </c>
+      <c r="J1110" s="42">
+        <v>46264</v>
+      </c>
+      <c r="M1110" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1111" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1111">
+        <v>580</v>
+      </c>
+      <c r="B1111" s="3" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C1111" s="3" t="s">
+        <v>1202</v>
+      </c>
+      <c r="D1111" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1111" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1111" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1111">
+        <v>10</v>
+      </c>
+      <c r="J1111" s="42">
+        <v>46264</v>
+      </c>
+      <c r="M1111" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1112" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1112">
+        <v>581</v>
+      </c>
+      <c r="B1112" s="3" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C1112" s="3" t="s">
+        <v>1204</v>
+      </c>
+      <c r="D1112" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1112" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1112" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1112">
+        <v>6</v>
+      </c>
+      <c r="J1112" s="42">
+        <v>46264</v>
+      </c>
+      <c r="M1112" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1113" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1113">
+        <v>582</v>
+      </c>
+      <c r="B1113" s="3" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C1113" s="3" t="s">
+        <v>1206</v>
+      </c>
+      <c r="D1113" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1113" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1113" t="s">
+        <v>1136</v>
+      </c>
+      <c r="H1113">
+        <v>3</v>
+      </c>
+      <c r="J1113" s="42">
+        <v>46264</v>
+      </c>
+      <c r="M1113" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1114" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1114">
+        <v>583</v>
+      </c>
+      <c r="B1114" s="3" t="s">
+        <v>1207</v>
+      </c>
+      <c r="C1114" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="D1114" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1114" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1114" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1114">
+        <v>6</v>
+      </c>
+      <c r="J1114" s="42">
+        <v>46264</v>
+      </c>
+      <c r="M1114" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1115" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1115">
+        <v>584</v>
+      </c>
+      <c r="B1115" s="3" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C1115" s="3" t="s">
+        <v>1210</v>
+      </c>
+      <c r="D1115" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1115" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1115" t="s">
+        <v>431</v>
+      </c>
+      <c r="H1115">
+        <v>1</v>
+      </c>
+      <c r="J1115" s="42">
+        <v>46265</v>
+      </c>
+      <c r="M1115" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1116" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1116">
+        <v>585</v>
+      </c>
+      <c r="B1116" s="3" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C1116" s="3" t="s">
+        <v>1212</v>
+      </c>
+      <c r="D1116" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1116" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1116" t="s">
+        <v>1136</v>
+      </c>
+      <c r="H1116">
+        <v>3</v>
+      </c>
+      <c r="J1116" s="42">
+        <v>46263</v>
+      </c>
+      <c r="M1116" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1117" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1117">
+        <v>586</v>
+      </c>
+      <c r="B1117" s="3" t="s">
+        <v>1213</v>
+      </c>
+      <c r="C1117" s="3" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D1117" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1117" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1117" t="s">
+        <v>1136</v>
+      </c>
+      <c r="H1117">
+        <v>1</v>
+      </c>
+      <c r="J1117" s="42">
+        <v>46263</v>
+      </c>
+      <c r="M1117" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1118" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1118">
+        <v>587</v>
+      </c>
+      <c r="B1118" s="3" t="s">
+        <v>1215</v>
+      </c>
+      <c r="C1118" s="3" t="s">
+        <v>1216</v>
+      </c>
+      <c r="D1118" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1118" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1118" t="s">
+        <v>1136</v>
+      </c>
+      <c r="H1118">
+        <v>3</v>
+      </c>
+      <c r="J1118" s="42">
+        <v>46263</v>
+      </c>
+      <c r="M1118" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1119" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1119">
+        <v>588</v>
+      </c>
+      <c r="B1119" s="3" t="s">
+        <v>1217</v>
+      </c>
+      <c r="C1119" s="3" t="s">
+        <v>1218</v>
+      </c>
+      <c r="D1119" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1119" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1119" t="s">
+        <v>1136</v>
+      </c>
+      <c r="H1119">
+        <v>8</v>
+      </c>
+      <c r="J1119" s="42">
+        <v>46265</v>
+      </c>
+      <c r="M1119" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1120" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1120">
+        <v>589</v>
+      </c>
+      <c r="B1120" s="3" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C1120" s="3" t="s">
+        <v>1220</v>
+      </c>
+      <c r="D1120" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1120" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1120" t="s">
+        <v>1136</v>
+      </c>
+      <c r="H1120">
+        <v>5</v>
+      </c>
+      <c r="J1120" s="42">
+        <v>46265</v>
+      </c>
+      <c r="M1120" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1121" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1121">
+        <v>590</v>
+      </c>
+      <c r="B1121" s="3" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C1121" s="3" t="s">
+        <v>1222</v>
+      </c>
+      <c r="D1121" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1121" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1121" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1121">
+        <v>6</v>
+      </c>
+      <c r="J1121" s="42">
+        <v>46265</v>
+      </c>
+      <c r="M1121" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1122" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1122">
+        <v>591</v>
+      </c>
+      <c r="B1122" s="3" t="s">
+        <v>1223</v>
+      </c>
+      <c r="C1122" s="3" t="s">
+        <v>1224</v>
+      </c>
+      <c r="D1122" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1122" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1122" t="s">
+        <v>1136</v>
+      </c>
+      <c r="H1122">
+        <v>3</v>
+      </c>
+      <c r="J1122" s="42">
+        <v>46265</v>
+      </c>
+      <c r="M1122" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1123" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1123">
+        <v>592</v>
+      </c>
+      <c r="B1123" s="3" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C1123" s="3" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D1123" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1123" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1123" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1123">
+        <v>4</v>
+      </c>
+      <c r="J1123" s="42">
+        <v>46265</v>
+      </c>
+      <c r="M1123" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1124" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1124">
+        <v>593</v>
+      </c>
+      <c r="B1124" s="3" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1124" s="3" t="s">
+        <v>1228</v>
+      </c>
+      <c r="D1124" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1124" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1124" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1124">
+        <v>6</v>
+      </c>
+      <c r="M1124" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1125" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1125">
+        <v>594</v>
+      </c>
+      <c r="B1125" s="3" t="s">
+        <v>1229</v>
+      </c>
+      <c r="C1125" s="3" t="s">
+        <v>1230</v>
+      </c>
+      <c r="D1125" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1125" t="s">
+        <v>73</v>
+      </c>
+      <c r="F1125" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1125">
+        <v>6</v>
+      </c>
+      <c r="M1125" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1126" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1126">
+        <v>595</v>
+      </c>
+      <c r="B1126" s="3" t="s">
+        <v>1231</v>
+      </c>
+      <c r="C1126" s="3" t="s">
+        <v>1232</v>
+      </c>
+      <c r="D1126" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1126" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1126" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1126">
+        <v>8</v>
+      </c>
+      <c r="J1126" s="42">
+        <v>46264</v>
+      </c>
+      <c r="M1126" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1127" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1127">
+        <v>596</v>
+      </c>
+      <c r="B1127" s="3" t="s">
+        <v>1233</v>
+      </c>
+      <c r="C1127" s="3" t="s">
+        <v>1234</v>
+      </c>
+      <c r="D1127" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1127" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1127" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1127">
+        <v>12</v>
+      </c>
+      <c r="J1127" s="42">
+        <v>46267</v>
+      </c>
+      <c r="M1127" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1128" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1128">
+        <v>597</v>
+      </c>
+      <c r="B1128" s="3" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C1128" s="3" t="s">
+        <v>1236</v>
+      </c>
+      <c r="D1128" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1128" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1128" t="s">
+        <v>431</v>
+      </c>
+      <c r="H1128">
+        <v>4</v>
+      </c>
+      <c r="J1128" s="42">
+        <v>46267</v>
+      </c>
+      <c r="M1128" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1129" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1129">
+        <v>598</v>
+      </c>
+      <c r="B1129" s="3" t="s">
+        <v>1237</v>
+      </c>
+      <c r="C1129" s="3" t="s">
+        <v>1238</v>
+      </c>
+      <c r="D1129" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1129" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1129" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1129">
+        <v>3</v>
+      </c>
+      <c r="J1129" s="42">
+        <v>46267</v>
+      </c>
+      <c r="M1129" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1130" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1130">
+        <v>599</v>
+      </c>
+      <c r="B1130" s="3" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C1130" s="3" t="s">
+        <v>1240</v>
+      </c>
+      <c r="D1130" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1130" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1130" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1130">
+        <v>4</v>
+      </c>
+      <c r="J1130" s="42">
+        <v>46267</v>
+      </c>
+      <c r="M1130" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1131" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1131">
+        <v>600</v>
+      </c>
+      <c r="B1131" s="3" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C1131" s="3" t="s">
+        <v>1242</v>
+      </c>
+      <c r="D1131" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1131" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1131" t="s">
+        <v>431</v>
+      </c>
+      <c r="H1131">
+        <v>4</v>
+      </c>
+      <c r="J1131" s="42">
+        <v>46267</v>
+      </c>
+      <c r="M1131" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1132" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1132">
+        <v>601</v>
+      </c>
+      <c r="B1132" s="3" t="s">
+        <v>1243</v>
+      </c>
+      <c r="C1132" s="3" t="s">
+        <v>1244</v>
+      </c>
+      <c r="D1132" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1132" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1132" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1132">
+        <v>5</v>
+      </c>
+      <c r="J1132" s="42">
+        <v>46267</v>
+      </c>
+      <c r="M1132" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1133" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1133">
+        <v>602</v>
+      </c>
+      <c r="B1133" s="3" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C1133" s="3" t="s">
+        <v>1246</v>
+      </c>
+      <c r="D1133" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1133" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1133" t="s">
+        <v>431</v>
+      </c>
+      <c r="H1133">
+        <v>3</v>
+      </c>
+      <c r="J1133" s="42">
+        <v>46267</v>
+      </c>
+      <c r="M1133" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1134" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1134">
+        <v>603</v>
+      </c>
+      <c r="B1134" s="3" t="s">
+        <v>1247</v>
+      </c>
+      <c r="C1134" s="3" t="s">
+        <v>1248</v>
+      </c>
+      <c r="D1134" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1134" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1134" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1134">
+        <v>4</v>
+      </c>
+      <c r="J1134" s="42">
+        <v>46267</v>
+      </c>
+      <c r="M1134" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1135" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1135">
+        <v>604</v>
+      </c>
+      <c r="B1135" s="3" t="s">
+        <v>1249</v>
+      </c>
+      <c r="C1135" s="3" t="s">
+        <v>1250</v>
+      </c>
+      <c r="D1135" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1135" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1135" t="s">
+        <v>431</v>
+      </c>
+      <c r="H1135">
+        <v>3</v>
+      </c>
+      <c r="J1135" s="42">
+        <v>46267</v>
+      </c>
+      <c r="M1135" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1136" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1136">
+        <v>605</v>
+      </c>
+      <c r="B1136" s="3" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C1136" s="3" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D1136" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1136" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1136" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1136">
+        <v>2</v>
+      </c>
+      <c r="J1136" s="42">
+        <v>46267</v>
+      </c>
+      <c r="M1136" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1137" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1137">
+        <v>606</v>
+      </c>
+      <c r="B1137" s="3" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C1137" s="3" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D1137" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1137" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1137" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1137">
+        <v>3</v>
+      </c>
+      <c r="J1137" s="42">
+        <v>46267</v>
+      </c>
+      <c r="M1137" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1138" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1138">
+        <v>607</v>
+      </c>
+      <c r="B1138" s="3" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C1138" s="3" t="s">
+        <v>1256</v>
+      </c>
+      <c r="D1138" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1138" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1138" t="s">
+        <v>1136</v>
+      </c>
+      <c r="H1138">
+        <v>3</v>
+      </c>
+      <c r="J1138" s="42">
+        <v>46267</v>
+      </c>
+      <c r="M1138" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1139" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1139">
+        <v>608</v>
+      </c>
+      <c r="B1139" s="3" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C1139" s="3" t="s">
+        <v>1258</v>
+      </c>
+      <c r="D1139" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1139" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1139" t="s">
+        <v>1136</v>
+      </c>
+      <c r="H1139">
+        <v>3</v>
+      </c>
+      <c r="J1139" s="42">
+        <v>46267</v>
+      </c>
+      <c r="M1139" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1140" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1140">
+        <v>609</v>
+      </c>
+      <c r="B1140" s="3" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C1140" s="3" t="s">
+        <v>1260</v>
+      </c>
+      <c r="D1140" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1140" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1140" t="s">
+        <v>1136</v>
+      </c>
+      <c r="H1140">
+        <v>4</v>
+      </c>
+      <c r="J1140" s="42">
+        <v>46267</v>
+      </c>
+      <c r="M1140" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1141" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1141">
+        <v>610</v>
+      </c>
+      <c r="B1141" s="3" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C1141" s="3" t="s">
+        <v>1262</v>
+      </c>
+      <c r="D1141" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1141" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1141" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1141">
+        <v>2</v>
+      </c>
+      <c r="J1141" s="42">
+        <v>46267</v>
+      </c>
+      <c r="M1141" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1142" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1142">
+        <v>611</v>
+      </c>
+      <c r="B1142" s="3" t="s">
+        <v>1263</v>
+      </c>
+      <c r="C1142" s="3" t="s">
+        <v>1264</v>
+      </c>
+      <c r="D1142" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1142" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1142" t="s">
+        <v>1136</v>
+      </c>
+      <c r="H1142">
+        <v>8</v>
+      </c>
+      <c r="J1142" s="42">
+        <v>46267</v>
+      </c>
+      <c r="M1142" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1143" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1143">
+        <v>612</v>
+      </c>
+      <c r="B1143" s="3" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C1143" s="3" t="s">
+        <v>1266</v>
+      </c>
+      <c r="D1143" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1143" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1143" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1143">
+        <v>4</v>
+      </c>
+      <c r="J1143" s="42">
+        <v>46267</v>
+      </c>
+      <c r="M1143" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1144" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1144">
+        <v>613</v>
+      </c>
+      <c r="B1144" s="3" t="s">
+        <v>1267</v>
+      </c>
+      <c r="C1144" s="3" t="s">
+        <v>1268</v>
+      </c>
+      <c r="D1144" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1144" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1144" t="s">
+        <v>1136</v>
+      </c>
+      <c r="H1144">
+        <v>6</v>
+      </c>
+      <c r="J1144" s="42">
+        <v>46267</v>
+      </c>
+      <c r="M1144" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1145" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1145">
+        <v>614</v>
+      </c>
+      <c r="B1145" s="3" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C1145" s="3" t="s">
+        <v>1270</v>
+      </c>
+      <c r="D1145" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1145" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1145" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1145">
+        <v>3</v>
+      </c>
+      <c r="J1145" s="42">
+        <v>46267</v>
+      </c>
+      <c r="M1145" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1146" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1146">
+        <v>615</v>
+      </c>
+      <c r="B1146" s="3" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C1146" s="3" t="s">
+        <v>1272</v>
+      </c>
+      <c r="D1146" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1146" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1146" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1146">
+        <v>4</v>
+      </c>
+      <c r="J1146" s="42">
+        <v>46267</v>
+      </c>
+      <c r="M1146" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1147" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1147">
+        <v>616</v>
+      </c>
+      <c r="B1147" s="3" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C1147" s="3" t="s">
+        <v>1274</v>
+      </c>
+      <c r="D1147" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1147" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1147" t="s">
+        <v>1136</v>
+      </c>
+      <c r="H1147">
+        <v>2</v>
+      </c>
+      <c r="J1147" s="42">
+        <v>46267</v>
+      </c>
+      <c r="M1147" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1148" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1148">
+        <v>617</v>
+      </c>
+      <c r="B1148" s="3" t="s">
+        <v>1275</v>
+      </c>
+      <c r="C1148" s="3" t="s">
+        <v>1276</v>
+      </c>
+      <c r="D1148" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1148" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1148" t="s">
+        <v>431</v>
+      </c>
+      <c r="H1148">
+        <v>6</v>
+      </c>
+      <c r="M1148" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1149" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1149">
+        <v>618</v>
+      </c>
+      <c r="B1149" s="3" t="s">
+        <v>1277</v>
+      </c>
+      <c r="C1149" s="3" t="s">
+        <v>1278</v>
+      </c>
+      <c r="D1149" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1149" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1149" t="s">
+        <v>431</v>
+      </c>
+      <c r="H1149">
+        <v>5</v>
+      </c>
+      <c r="M1149" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1150" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1150">
+        <v>619</v>
+      </c>
+      <c r="B1150" s="3" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C1150" s="3" t="s">
+        <v>1280</v>
+      </c>
+      <c r="D1150" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1150" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1150" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1150">
+        <v>6</v>
+      </c>
+      <c r="M1150" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="1151" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1151">
+        <v>620</v>
+      </c>
+      <c r="B1151" s="3" t="s">
+        <v>1281</v>
+      </c>
+      <c r="C1151" s="3" t="s">
+        <v>1282</v>
+      </c>
+      <c r="D1151" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1151" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1151" t="s">
+        <v>431</v>
+      </c>
+      <c r="H1151">
+        <v>6</v>
+      </c>
+      <c r="J1151" s="42">
+        <v>46264</v>
+      </c>
+      <c r="M1151" t="s">
+        <v>182</v>
       </c>
     </row>
   </sheetData>
@@ -21843,15 +24421,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100959716F11FB6F9409089B98D1C11D330" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bc55ac45923017d94ee4534da3224188">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2e20d828-e3fd-41fd-921c-fbe0ff523ae8" xmlns:ns3="adfc7943-f9ee-4478-a01e-ebfcb6e54f53" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5bc17ad4f23ab8382a0bb5b03decca58" ns2:_="" ns3:_="">
     <xsd:import namespace="2e20d828-e3fd-41fd-921c-fbe0ff523ae8"/>
@@ -22106,6 +24675,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -22118,14 +24696,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{737DCCA1-99B2-40A5-A4E9-9FBBAC380C60}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CE6A3B7-F954-4629-B802-2205DECE6851}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -22144,6 +24714,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{737DCCA1-99B2-40A5-A4E9-9FBBAC380C60}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{407A8743-A532-48E3-9004-715BF423F4DA}">
   <ds:schemaRefs>

--- a/project_time_sheet.xlsx
+++ b/project_time_sheet.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{497D3D87-B10F-49BA-A317-4A6C351579D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA1341DD-930C-4E48-BC5B-1829C0698E01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="📋 Instructions" sheetId="3" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3565" uniqueCount="1283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3575" uniqueCount="1287">
   <si>
     <t xml:space="preserve">  Project Time Sheet — User Guide</t>
   </si>
@@ -3886,6 +3886,18 @@
   </si>
   <si>
     <t>Maintain architecture, installation and operating notes.</t>
+  </si>
+  <si>
+    <t>Safety / PLC Error Handling: door-open emergency error not shown in Katana</t>
+  </si>
+  <si>
+    <t>I opened the door; PLC was in Emergency error, but Katana was not showing any error.</t>
+  </si>
+  <si>
+    <t>Page freeze during phantom mode and on entering calibration offsets page</t>
+  </si>
+  <si>
+    <t>Page froze while phantom mode was running. Got stuck again after going into calibration offsets page.</t>
   </si>
 </sst>
 </file>
@@ -5468,7 +5480,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="1" width="438" row="1">
+  <wetp:taskpane dockstate="right" visibility="1" width="350" row="1">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -5767,7 +5779,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N1151"/>
+  <dimension ref="A1:N1153"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.6640625" customWidth="1"/>
@@ -24293,6 +24305,52 @@
       </c>
       <c r="M1151" t="s">
         <v>182</v>
+      </c>
+    </row>
+    <row r="1152" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1152">
+        <v>621</v>
+      </c>
+      <c r="B1152" s="3" t="s">
+        <v>1283</v>
+      </c>
+      <c r="C1152" s="3" t="s">
+        <v>1284</v>
+      </c>
+      <c r="E1152" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1152" t="s">
+        <v>1136</v>
+      </c>
+      <c r="H1152">
+        <v>4</v>
+      </c>
+      <c r="M1152" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1153" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1153">
+        <v>622</v>
+      </c>
+      <c r="B1153" s="3" t="s">
+        <v>1285</v>
+      </c>
+      <c r="C1153" s="3" t="s">
+        <v>1286</v>
+      </c>
+      <c r="E1153" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1153" t="s">
+        <v>431</v>
+      </c>
+      <c r="H1153">
+        <v>4</v>
+      </c>
+      <c r="M1153" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -24421,6 +24479,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100959716F11FB6F9409089B98D1C11D330" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bc55ac45923017d94ee4534da3224188">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2e20d828-e3fd-41fd-921c-fbe0ff523ae8" xmlns:ns3="adfc7943-f9ee-4478-a01e-ebfcb6e54f53" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5bc17ad4f23ab8382a0bb5b03decca58" ns2:_="" ns3:_="">
     <xsd:import namespace="2e20d828-e3fd-41fd-921c-fbe0ff523ae8"/>
@@ -24675,15 +24742,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -24696,6 +24754,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{737DCCA1-99B2-40A5-A4E9-9FBBAC380C60}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CE6A3B7-F954-4629-B802-2205DECE6851}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -24714,14 +24780,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{737DCCA1-99B2-40A5-A4E9-9FBBAC380C60}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{407A8743-A532-48E3-9004-715BF423F4DA}">
   <ds:schemaRefs>

--- a/project_time_sheet.xlsx
+++ b/project_time_sheet.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA1341DD-930C-4E48-BC5B-1829C0698E01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A491DD92-D752-4C4A-A4B2-1631F12C4029}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="37620" yWindow="615" windowWidth="17280" windowHeight="9960" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="📋 Instructions" sheetId="3" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3575" uniqueCount="1287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3655" uniqueCount="1304">
   <si>
     <t xml:space="preserve">  Project Time Sheet — User Guide</t>
   </si>
@@ -3898,6 +3898,57 @@
   </si>
   <si>
     <t>Page froze while phantom mode was running. Got stuck again after going into calibration offsets page.</t>
+  </si>
+  <si>
+    <t>Draw a right hand showing arrows for direction of travel and X, Y, Z axes.</t>
+  </si>
+  <si>
+    <t>Each robot should clearly display its state: starting, running, stuck in dip and clean, or stopped.</t>
+  </si>
+  <si>
+    <t>Standardize alarms and alerts across the UI.</t>
+  </si>
+  <si>
+    <t>Spell out abbreviated setting names in full (e.g. Approach H).</t>
+  </si>
+  <si>
+    <t>General UI/UX: Camera page - add Restart Cameras button</t>
+  </si>
+  <si>
+    <t>Camera page: add a Restart Cameras button.</t>
+  </si>
+  <si>
+    <t>Logs: remove all debug logs, show only alarms.</t>
+  </si>
+  <si>
+    <t>Add multi-line selection in Custom Cut Mode.</t>
+  </si>
+  <si>
+    <t>Custom Cut Mode is not touch-friendly; optimize for touch.</t>
+  </si>
+  <si>
+    <t>Custom Cut Mode: Lock/hide normal parameters when enabled</t>
+  </si>
+  <si>
+    <t>When enabled, all normal parameters should be locked/hidden, and the current recipe should indicate custom cut.</t>
+  </si>
+  <si>
+    <t>Reorganize and rename settings menu items.</t>
+  </si>
+  <si>
+    <t>Remove FGF from everywhere.</t>
+  </si>
+  <si>
+    <t>Robot assignment alignment is off in the home preview.</t>
+  </si>
+  <si>
+    <t>Can't change the values on Blazor.</t>
+  </si>
+  <si>
+    <t>Auto-scale the cut preview so it always displays clearly.</t>
+  </si>
+  <si>
+    <t>Phantom images: allow users to turn on saving of phantom images.</t>
   </si>
 </sst>
 </file>
@@ -5779,7 +5830,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N1153"/>
+  <dimension ref="A1:N1169"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.6640625" customWidth="1"/>
@@ -21595,7 +21646,7 @@
         <v>1087</v>
       </c>
       <c r="E1055" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="F1055" t="s">
         <v>431</v>
@@ -21621,7 +21672,7 @@
         <v>1091</v>
       </c>
       <c r="E1056" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="F1056" t="s">
         <v>431</v>
@@ -21647,7 +21698,7 @@
         <v>1092</v>
       </c>
       <c r="E1057" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="F1057" t="s">
         <v>431</v>
@@ -21673,7 +21724,7 @@
         <v>1095</v>
       </c>
       <c r="E1058" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="F1058" t="s">
         <v>431</v>
@@ -21699,7 +21750,7 @@
         <v>1096</v>
       </c>
       <c r="E1059" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="F1059" t="s">
         <v>431</v>
@@ -21725,7 +21776,7 @@
         <v>1098</v>
       </c>
       <c r="E1060" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="F1060" t="s">
         <v>431</v>
@@ -21751,7 +21802,7 @@
         <v>1100</v>
       </c>
       <c r="E1061" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="F1061" t="s">
         <v>431</v>
@@ -21777,7 +21828,7 @@
         <v>1103</v>
       </c>
       <c r="E1062" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="F1062" t="s">
         <v>431</v>
@@ -21803,7 +21854,7 @@
         <v>1104</v>
       </c>
       <c r="E1063" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="F1063" t="s">
         <v>431</v>
@@ -21829,7 +21880,7 @@
         <v>1106</v>
       </c>
       <c r="E1064" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="F1064" t="s">
         <v>431</v>
@@ -21855,7 +21906,7 @@
         <v>1107</v>
       </c>
       <c r="E1065" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="F1065" t="s">
         <v>431</v>
@@ -21881,7 +21932,7 @@
         <v>1109</v>
       </c>
       <c r="E1066" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="F1066" t="s">
         <v>431</v>
@@ -21907,7 +21958,7 @@
         <v>1110</v>
       </c>
       <c r="E1067" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="F1067" t="s">
         <v>431</v>
@@ -21959,7 +22010,7 @@
         <v>1115</v>
       </c>
       <c r="E1069" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="F1069" t="s">
         <v>431</v>
@@ -21985,7 +22036,7 @@
         <v>1118</v>
       </c>
       <c r="E1070" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="F1070" t="s">
         <v>431</v>
@@ -22011,7 +22062,7 @@
         <v>1120</v>
       </c>
       <c r="E1071" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="F1071" t="s">
         <v>431</v>
@@ -22037,7 +22088,7 @@
         <v>1122</v>
       </c>
       <c r="E1072" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="F1072" t="s">
         <v>431</v>
@@ -22063,7 +22114,7 @@
         <v>1124</v>
       </c>
       <c r="E1073" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="F1073" t="s">
         <v>431</v>
@@ -22089,7 +22140,7 @@
         <v>1125</v>
       </c>
       <c r="E1074" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="F1074" t="s">
         <v>431</v>
@@ -22115,7 +22166,7 @@
         <v>1127</v>
       </c>
       <c r="E1075" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="F1075" t="s">
         <v>431</v>
@@ -24341,7 +24392,7 @@
         <v>1286</v>
       </c>
       <c r="E1153" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="F1153" t="s">
         <v>431</v>
@@ -24350,6 +24401,338 @@
         <v>4</v>
       </c>
       <c r="M1153" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1154" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1154">
+        <v>307</v>
+      </c>
+      <c r="B1154" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="C1154" s="3" t="s">
+        <v>1287</v>
+      </c>
+      <c r="E1154" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1154" t="s">
+        <v>431</v>
+      </c>
+      <c r="M1154" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1155" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1155">
+        <v>316</v>
+      </c>
+      <c r="B1155" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="C1155" s="3" t="s">
+        <v>1288</v>
+      </c>
+      <c r="E1155" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1155" t="s">
+        <v>431</v>
+      </c>
+      <c r="M1155" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1156" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1156">
+        <v>320</v>
+      </c>
+      <c r="B1156" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="C1156" s="3" t="s">
+        <v>1289</v>
+      </c>
+      <c r="E1156" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1156" t="s">
+        <v>428</v>
+      </c>
+      <c r="M1156" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1157" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1157">
+        <v>325</v>
+      </c>
+      <c r="B1157" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="C1157" s="3" t="s">
+        <v>1290</v>
+      </c>
+      <c r="E1157" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1157" t="s">
+        <v>428</v>
+      </c>
+      <c r="M1157" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1158" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1158">
+        <v>336</v>
+      </c>
+      <c r="B1158" s="3" t="s">
+        <v>1291</v>
+      </c>
+      <c r="C1158" s="3" t="s">
+        <v>1292</v>
+      </c>
+      <c r="E1158" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1158" t="s">
+        <v>428</v>
+      </c>
+      <c r="M1158" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1159" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1159">
+        <v>338</v>
+      </c>
+      <c r="B1159" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="C1159" s="3" t="s">
+        <v>1293</v>
+      </c>
+      <c r="E1159" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1159" t="s">
+        <v>431</v>
+      </c>
+      <c r="H1159">
+        <v>2</v>
+      </c>
+      <c r="M1159" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1160" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1160">
+        <v>344</v>
+      </c>
+      <c r="B1160" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="C1160" s="3" t="s">
+        <v>1294</v>
+      </c>
+      <c r="E1160" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1160" t="s">
+        <v>431</v>
+      </c>
+      <c r="M1160" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1161" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1161">
+        <v>345</v>
+      </c>
+      <c r="B1161" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="C1161" s="3" t="s">
+        <v>1295</v>
+      </c>
+      <c r="E1161" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1161" t="s">
+        <v>431</v>
+      </c>
+      <c r="M1161" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1162" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1162">
+        <v>346</v>
+      </c>
+      <c r="B1162" s="3" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C1162" s="3" t="s">
+        <v>1297</v>
+      </c>
+      <c r="E1162" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1162" t="s">
+        <v>431</v>
+      </c>
+      <c r="M1162" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1163" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1163">
+        <v>348</v>
+      </c>
+      <c r="B1163" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="C1163" s="3" t="s">
+        <v>1298</v>
+      </c>
+      <c r="E1163" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1163" t="s">
+        <v>431</v>
+      </c>
+      <c r="M1163" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1164" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1164">
+        <v>349</v>
+      </c>
+      <c r="B1164" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="C1164" s="3" t="s">
+        <v>1299</v>
+      </c>
+      <c r="E1164" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1164" t="s">
+        <v>1136</v>
+      </c>
+      <c r="M1164" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1165" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1165">
+        <v>362</v>
+      </c>
+      <c r="B1165" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="C1165" s="3" t="s">
+        <v>651</v>
+      </c>
+      <c r="E1165" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1165" t="s">
+        <v>431</v>
+      </c>
+      <c r="H1165">
+        <v>3</v>
+      </c>
+      <c r="M1165" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1166" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1166">
+        <v>364</v>
+      </c>
+      <c r="B1166" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="C1166" s="3" t="s">
+        <v>1300</v>
+      </c>
+      <c r="E1166" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1166" t="s">
+        <v>431</v>
+      </c>
+      <c r="M1166" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1167" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1167">
+        <v>461</v>
+      </c>
+      <c r="B1167" s="3" t="s">
+        <v>869</v>
+      </c>
+      <c r="C1167" s="3" t="s">
+        <v>1301</v>
+      </c>
+      <c r="E1167" t="s">
+        <v>1068</v>
+      </c>
+      <c r="F1167" t="s">
+        <v>428</v>
+      </c>
+      <c r="H1167">
+        <v>1</v>
+      </c>
+      <c r="M1167" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1168" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1168">
+        <v>464</v>
+      </c>
+      <c r="B1168" s="3" t="s">
+        <v>877</v>
+      </c>
+      <c r="C1168" s="3" t="s">
+        <v>1302</v>
+      </c>
+      <c r="E1168" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1168" t="s">
+        <v>431</v>
+      </c>
+      <c r="H1168">
+        <v>3</v>
+      </c>
+      <c r="M1168" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1169" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1169">
+        <v>465</v>
+      </c>
+      <c r="B1169" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="C1169" s="3" t="s">
+        <v>1303</v>
+      </c>
+      <c r="E1169" t="s">
+        <v>1068</v>
+      </c>
+      <c r="F1169" t="s">
+        <v>428</v>
+      </c>
+      <c r="M1169" t="s">
         <v>69</v>
       </c>
     </row>

--- a/project_time_sheet.xlsx
+++ b/project_time_sheet.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A491DD92-D752-4C4A-A4B2-1631F12C4029}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94D1AB1E-C469-4E40-A1AA-4EFF035FF54C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="37620" yWindow="615" windowWidth="17280" windowHeight="9960" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="📋 Instructions" sheetId="3" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3655" uniqueCount="1304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3900" uniqueCount="1346">
   <si>
     <t xml:space="preserve">  Project Time Sheet — User Guide</t>
   </si>
@@ -3949,6 +3949,132 @@
   </si>
   <si>
     <t>Phantom images: allow users to turn on saving of phantom images.</t>
+  </si>
+  <si>
+    <t>Not Started</t>
+  </si>
+  <si>
+    <t>User Management Settings: configuration pending Controls team input</t>
+  </si>
+  <si>
+    <t>Recipes and Custom Cut Designer: no bounds for dimensions (can go negative or exceed recipe bounds)</t>
+  </si>
+  <si>
+    <t>Settings/3D Cameras: 90-second camera restart cooldown is aborted when switching pages</t>
+  </si>
+  <si>
+    <t>Creating Recipe: recipe can be saved without Product or SKU name despite being marked required</t>
+  </si>
+  <si>
+    <t>Maintenance: check disk space and auto-clean temp folder - points viewer generates unmanaged sidecar JSON files</t>
+  </si>
+  <si>
+    <t>General UI/UX: Home page - improve description for per-cut nozzle order and nozzle settings</t>
+  </si>
+  <si>
+    <t>General UI/UX: Tpointer should only be visible to Admins (for calibration use)</t>
+  </si>
+  <si>
+    <t>General UI/UX: Grey out conveyor start/stop when safety is on; add visual feedback for running state</t>
+  </si>
+  <si>
+    <t>General UI/UX: Remove View All shortcuts from home page - direct users to maintenance/alarms pages</t>
+  </si>
+  <si>
+    <t>General UI/UX: Remove notifications badge (9+) from UI</t>
+  </si>
+  <si>
+    <t>General UI/UX: Always show alarms on home page regardless of logged-in user; match Katana 1 format</t>
+  </si>
+  <si>
+    <t>General UI/UX: In home page, replace cut preview with current recipe settings on click</t>
+  </si>
+  <si>
+    <t>General UI/UX: Auto-size product in home page cut preview to fill the window</t>
+  </si>
+  <si>
+    <t>General UI/UX: Check cross-platform data consistency - WPF, Web Viewer, Katana 1 and Katana 2</t>
+  </si>
+  <si>
+    <t>General UI/UX: Home page layers - remove base, always enable bounding box and center points, rename scale to grid</t>
+  </si>
+  <si>
+    <t>General UI/UX: Point viewer - only show cut geometry not individual points; restrict to Admins</t>
+  </si>
+  <si>
+    <t>General UI/UX: Controls team as ABI level, dev team as SuperAdmin; make dev flag from access level</t>
+  </si>
+  <si>
+    <t>General UI/UX: Without login, allow only start, stop, and load recipe operations</t>
+  </si>
+  <si>
+    <t>General UI/UX: Creating recipes - remove client and product name fields</t>
+  </si>
+  <si>
+    <t>General UI/UX: Grey out save button when saving is not allowed (e.g. duplicate recipe name)</t>
+  </si>
+  <si>
+    <t>General UI/UX: Calendar accent color should change (currently static)</t>
+  </si>
+  <si>
+    <t>General UI/UX: Logs - add dynamic filtering so results update without pressing filter button</t>
+  </si>
+  <si>
+    <t>General UI/UX: Maintenance page - add Linear axis to Reset and Go Home action</t>
+  </si>
+  <si>
+    <t>General UI/UX: Move auto dip and clean cycle setting to recipe instead of maintenance page</t>
+  </si>
+  <si>
+    <t>General UI/UX: Maintenance page - replace Pickup Tool 1 with dropdown of all available tools</t>
+  </si>
+  <si>
+    <t>General UI/UX: Test reset counters feature in maintenance page</t>
+  </si>
+  <si>
+    <t>General UI/UX: Add RAPID module feedback if module does not exist instead of silently failing</t>
+  </si>
+  <si>
+    <t>General UI/UX: Maintenance page - remove both power options (restart and disable)</t>
+  </si>
+  <si>
+    <t>General UI/UX: Maintenance page - fix working actively status value display</t>
+  </si>
+  <si>
+    <t>General UI/UX: Ultrasonic button - make smaller and fix incorrect icon image</t>
+  </si>
+  <si>
+    <t>General UI/UX: Ultrasonic live test bug on demo cell (RobotStudio configuration issue, not software)</t>
+  </si>
+  <si>
+    <t>General UI/UX: Maintenance page - add pump card alongside robots, ultrasonics, and cameras</t>
+  </si>
+  <si>
+    <t>General UI/UX: Review and fix localization strings across all supported languages</t>
+  </si>
+  <si>
+    <t>General UI/UX: Incident reports - remove the resolved feature</t>
+  </si>
+  <si>
+    <t>General UI/UX: Documentation page - wider scroller and remove gesture control</t>
+  </si>
+  <si>
+    <t>General UI/UX: Documentation page - add flag to switch between embedded viewer and web PDF viewer</t>
+  </si>
+  <si>
+    <t>General UI/UX: User management - remove first and last name fields; add user archive feature</t>
+  </si>
+  <si>
+    <t>General UI/UX: Home page - remove seconds from live time display (top right)</t>
+  </si>
+  <si>
+    <t>General UI/UX: Adjust page size dynamically when window is resized</t>
+  </si>
+  <si>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <t>In Review</t>
   </si>
 </sst>
 </file>
@@ -5559,7 +5685,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:C38"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -5567,25 +5693,25 @@
     <col min="4" max="4" width="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="171" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="171"/>
     </row>
-    <row r="4" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="172" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="172"/>
     </row>
-    <row r="6" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="170" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="170"/>
     </row>
-    <row r="7" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>3</v>
       </c>
@@ -5593,7 +5719,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
         <v>5</v>
       </c>
@@ -5601,7 +5727,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
@@ -5609,13 +5735,13 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="170" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="170"/>
     </row>
-    <row r="12" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
         <v>10</v>
       </c>
@@ -5623,7 +5749,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
         <v>12</v>
       </c>
@@ -5631,7 +5757,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
         <v>14</v>
       </c>
@@ -5639,7 +5765,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="1" t="s">
         <v>16</v>
       </c>
@@ -5647,7 +5773,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
         <v>18</v>
       </c>
@@ -5655,7 +5781,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
         <v>20</v>
       </c>
@@ -5663,7 +5789,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="1" t="s">
         <v>22</v>
       </c>
@@ -5671,7 +5797,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
         <v>24</v>
       </c>
@@ -5679,7 +5805,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="1" t="s">
         <v>26</v>
       </c>
@@ -5687,7 +5813,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
         <v>28</v>
       </c>
@@ -5695,7 +5821,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="1" t="s">
         <v>30</v>
       </c>
@@ -5703,7 +5829,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="1" t="s">
         <v>32</v>
       </c>
@@ -5711,13 +5837,13 @@
         <v>33</v>
       </c>
     </row>
-    <row r="25" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="170" t="s">
         <v>34</v>
       </c>
       <c r="C25" s="170"/>
     </row>
-    <row r="26" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="1" t="s">
         <v>35</v>
       </c>
@@ -5725,7 +5851,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="27" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="1" t="s">
         <v>37</v>
       </c>
@@ -5733,7 +5859,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="28" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
         <v>39</v>
       </c>
@@ -5741,7 +5867,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="29" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
         <v>41</v>
       </c>
@@ -5749,7 +5875,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="30" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="1" t="s">
         <v>43</v>
       </c>
@@ -5757,7 +5883,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="31" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="1" t="s">
         <v>45</v>
       </c>
@@ -5765,13 +5891,13 @@
         <v>46</v>
       </c>
     </row>
-    <row r="33" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="170" t="s">
         <v>47</v>
       </c>
       <c r="C33" s="170"/>
     </row>
-    <row r="34" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="1" t="s">
         <v>48</v>
       </c>
@@ -5779,7 +5905,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="35" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="1" t="s">
         <v>50</v>
       </c>
@@ -5787,7 +5913,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="36" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="1" t="s">
         <v>52</v>
       </c>
@@ -5795,7 +5921,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="37" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="1" t="s">
         <v>54</v>
       </c>
@@ -5803,7 +5929,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="38" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="1" t="s">
         <v>56</v>
       </c>
@@ -5830,25 +5956,25 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N1169"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:N1215"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.6640625" customWidth="1"/>
-    <col min="2" max="2" width="51.88671875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="70.33203125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="37.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.33203125" customWidth="1"/>
-    <col min="6" max="6" width="16.6640625" customWidth="1"/>
-    <col min="7" max="7" width="11.109375" customWidth="1"/>
-    <col min="8" max="8" width="16.6640625" customWidth="1"/>
-    <col min="9" max="10" width="17.5546875" customWidth="1"/>
-    <col min="11" max="11" width="22.33203125" customWidth="1"/>
-    <col min="12" max="12" width="44.44140625" customWidth="1"/>
-    <col min="13" max="13" width="16.6640625" customWidth="1"/>
-    <col min="14" max="14" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.7109375" customWidth="1"/>
+    <col min="2" max="2" width="51.85546875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="70.28515625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="37.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.28515625" customWidth="1"/>
+    <col min="6" max="6" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" customWidth="1"/>
+    <col min="8" max="8" width="16.7109375" customWidth="1"/>
+    <col min="9" max="10" width="17.5703125" customWidth="1"/>
+    <col min="11" max="11" width="22.28515625" customWidth="1"/>
+    <col min="12" max="12" width="44.42578125" customWidth="1"/>
+    <col min="13" max="13" width="16.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="114" customFormat="1" ht="28.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" s="114" customFormat="1" ht="28.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="115" t="s">
         <v>10</v>
       </c>
@@ -5892,7 +6018,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="41"/>
       <c r="B2" s="5" t="s">
         <v>864</v>
@@ -5918,7 +6044,7 @@
       <c r="M2" s="64"/>
       <c r="N2" s="52"/>
     </row>
-    <row r="3" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="98"/>
       <c r="B3" s="104" t="s">
         <v>67</v>
@@ -5946,7 +6072,7 @@
       </c>
       <c r="N3" s="53"/>
     </row>
-    <row r="4" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="41"/>
       <c r="B4" s="9" t="s">
         <v>70</v>
@@ -5972,7 +6098,7 @@
       </c>
       <c r="N4" s="53"/>
     </row>
-    <row r="5" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="41"/>
       <c r="B5" s="9" t="s">
         <v>72</v>
@@ -5998,7 +6124,7 @@
       </c>
       <c r="N5" s="53"/>
     </row>
-    <row r="6" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="41"/>
       <c r="B6" s="9" t="s">
         <v>74</v>
@@ -6024,7 +6150,7 @@
       </c>
       <c r="N6" s="53"/>
     </row>
-    <row r="7" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="41"/>
       <c r="B7" s="9" t="s">
         <v>75</v>
@@ -6052,7 +6178,7 @@
       </c>
       <c r="N7" s="53"/>
     </row>
-    <row r="8" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="41"/>
       <c r="B8" s="28" t="s">
         <v>76</v>
@@ -6080,7 +6206,7 @@
       </c>
       <c r="N8" s="53"/>
     </row>
-    <row r="9" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="41"/>
       <c r="B9" s="22" t="s">
         <v>77</v>
@@ -6106,7 +6232,7 @@
       </c>
       <c r="N9" s="53"/>
     </row>
-    <row r="10" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="41"/>
       <c r="B10" s="28" t="s">
         <v>79</v>
@@ -6132,7 +6258,7 @@
       </c>
       <c r="N10" s="53"/>
     </row>
-    <row r="11" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="41"/>
       <c r="B11" s="22" t="s">
         <v>80</v>
@@ -6158,7 +6284,7 @@
       </c>
       <c r="N11" s="53"/>
     </row>
-    <row r="12" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="41"/>
       <c r="B12" s="65" t="s">
         <v>81</v>
@@ -6184,7 +6310,7 @@
       </c>
       <c r="N12" s="53"/>
     </row>
-    <row r="13" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="41"/>
       <c r="B13" s="66" t="s">
         <v>82</v>
@@ -6210,7 +6336,7 @@
       </c>
       <c r="N13" s="53"/>
     </row>
-    <row r="14" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="41"/>
       <c r="B14" s="65" t="s">
         <v>83</v>
@@ -6236,7 +6362,7 @@
       </c>
       <c r="N14" s="53"/>
     </row>
-    <row r="15" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="41"/>
       <c r="B15" s="66" t="s">
         <v>84</v>
@@ -6262,7 +6388,7 @@
       </c>
       <c r="N15" s="53"/>
     </row>
-    <row r="16" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="41"/>
       <c r="B16" s="66" t="s">
         <v>85</v>
@@ -6288,7 +6414,7 @@
       </c>
       <c r="N16" s="53"/>
     </row>
-    <row r="17" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="41"/>
       <c r="B17" s="9" t="s">
         <v>86</v>
@@ -6314,7 +6440,7 @@
       </c>
       <c r="N17" s="53"/>
     </row>
-    <row r="18" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="41"/>
       <c r="B18" s="9" t="s">
         <v>87</v>
@@ -6340,7 +6466,7 @@
       </c>
       <c r="N18" s="53"/>
     </row>
-    <row r="19" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="41"/>
       <c r="B19" s="9" t="s">
         <v>88</v>
@@ -6366,7 +6492,7 @@
       </c>
       <c r="N19" s="53"/>
     </row>
-    <row r="20" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="41"/>
       <c r="B20" s="9" t="s">
         <v>89</v>
@@ -6392,7 +6518,7 @@
       </c>
       <c r="N20" s="53"/>
     </row>
-    <row r="21" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="41"/>
       <c r="B21" s="9" t="s">
         <v>90</v>
@@ -6420,7 +6546,7 @@
       </c>
       <c r="N21" s="53"/>
     </row>
-    <row r="22" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="41"/>
       <c r="B22" s="9" t="s">
         <v>91</v>
@@ -6450,7 +6576,7 @@
       </c>
       <c r="N22" s="53"/>
     </row>
-    <row r="23" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="41"/>
       <c r="B23" s="9" t="s">
         <v>92</v>
@@ -6480,7 +6606,7 @@
       </c>
       <c r="N23" s="53"/>
     </row>
-    <row r="24" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="41"/>
       <c r="B24" s="65" t="s">
         <v>93</v>
@@ -6510,7 +6636,7 @@
       </c>
       <c r="N24" s="53"/>
     </row>
-    <row r="25" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="41"/>
       <c r="B25" s="66" t="s">
         <v>94</v>
@@ -6538,7 +6664,7 @@
       </c>
       <c r="N25" s="53"/>
     </row>
-    <row r="26" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="41"/>
       <c r="B26" s="65" t="s">
         <v>95</v>
@@ -6566,7 +6692,7 @@
       </c>
       <c r="N26" s="53"/>
     </row>
-    <row r="27" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="41"/>
       <c r="B27" s="66" t="s">
         <v>96</v>
@@ -6594,7 +6720,7 @@
       </c>
       <c r="N27" s="53"/>
     </row>
-    <row r="28" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="41"/>
       <c r="B28" s="9" t="s">
         <v>97</v>
@@ -6622,7 +6748,7 @@
       </c>
       <c r="N28" s="53"/>
     </row>
-    <row r="29" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="41"/>
       <c r="B29" s="9" t="s">
         <v>98</v>
@@ -6650,7 +6776,7 @@
       </c>
       <c r="N29" s="53"/>
     </row>
-    <row r="30" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="41"/>
       <c r="B30" s="9" t="s">
         <v>99</v>
@@ -6678,7 +6804,7 @@
       </c>
       <c r="N30" s="53"/>
     </row>
-    <row r="31" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="41"/>
       <c r="B31" s="9" t="s">
         <v>100</v>
@@ -6706,7 +6832,7 @@
       </c>
       <c r="N31" s="53"/>
     </row>
-    <row r="32" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="41"/>
       <c r="B32" s="9" t="s">
         <v>101</v>
@@ -6730,7 +6856,7 @@
       </c>
       <c r="N32" s="53"/>
     </row>
-    <row r="33" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="41"/>
       <c r="B33" s="9" t="s">
         <v>102</v>
@@ -6758,7 +6884,7 @@
       </c>
       <c r="N33" s="53"/>
     </row>
-    <row r="34" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="41"/>
       <c r="B34" s="9" t="s">
         <v>103</v>
@@ -6788,7 +6914,7 @@
       </c>
       <c r="N34" s="53"/>
     </row>
-    <row r="35" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="41"/>
       <c r="B35" s="9" t="s">
         <v>104</v>
@@ -6818,7 +6944,7 @@
       </c>
       <c r="N35" s="53"/>
     </row>
-    <row r="36" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="41"/>
       <c r="B36" s="9" t="s">
         <v>105</v>
@@ -6846,7 +6972,7 @@
       </c>
       <c r="N36" s="53"/>
     </row>
-    <row r="37" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="41"/>
       <c r="B37" s="9" t="s">
         <v>106</v>
@@ -6874,7 +7000,7 @@
       </c>
       <c r="N37" s="53"/>
     </row>
-    <row r="38" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="41"/>
       <c r="B38" s="9" t="s">
         <v>108</v>
@@ -6900,7 +7026,7 @@
       </c>
       <c r="N38" s="53"/>
     </row>
-    <row r="39" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="41"/>
       <c r="B39" s="22" t="s">
         <v>109</v>
@@ -6928,7 +7054,7 @@
       </c>
       <c r="N39" s="53"/>
     </row>
-    <row r="40" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="41"/>
       <c r="B40" s="28" t="s">
         <v>110</v>
@@ -6954,7 +7080,7 @@
       </c>
       <c r="N40" s="53"/>
     </row>
-    <row r="41" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="41"/>
       <c r="B41" s="22" t="s">
         <v>111</v>
@@ -6980,7 +7106,7 @@
       </c>
       <c r="N41" s="53"/>
     </row>
-    <row r="42" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="41"/>
       <c r="B42" s="66" t="s">
         <v>112</v>
@@ -7006,7 +7132,7 @@
       </c>
       <c r="N42" s="53"/>
     </row>
-    <row r="43" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="41"/>
       <c r="B43" s="65" t="s">
         <v>113</v>
@@ -7032,7 +7158,7 @@
       </c>
       <c r="N43" s="53"/>
     </row>
-    <row r="44" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="41"/>
       <c r="B44" s="9" t="s">
         <v>114</v>
@@ -7060,7 +7186,7 @@
       </c>
       <c r="N44" s="53"/>
     </row>
-    <row r="45" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="41"/>
       <c r="B45" s="9" t="s">
         <v>115</v>
@@ -7088,7 +7214,7 @@
       </c>
       <c r="N45" s="53"/>
     </row>
-    <row r="46" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="41"/>
       <c r="B46" s="66" t="s">
         <v>116</v>
@@ -7116,7 +7242,7 @@
       </c>
       <c r="N46" s="53"/>
     </row>
-    <row r="47" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="41"/>
       <c r="B47" s="9" t="s">
         <v>117</v>
@@ -7144,7 +7270,7 @@
       </c>
       <c r="N47" s="53"/>
     </row>
-    <row r="48" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="41"/>
       <c r="B48" s="9" t="s">
         <v>118</v>
@@ -7170,7 +7296,7 @@
       </c>
       <c r="N48" s="53"/>
     </row>
-    <row r="49" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="41"/>
       <c r="B49" s="9" t="s">
         <v>119</v>
@@ -7196,7 +7322,7 @@
       </c>
       <c r="N49" s="53"/>
     </row>
-    <row r="50" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="41"/>
       <c r="B50" s="9" t="s">
         <v>120</v>
@@ -7222,7 +7348,7 @@
       </c>
       <c r="N50" s="53"/>
     </row>
-    <row r="51" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="41"/>
       <c r="B51" s="9" t="s">
         <v>121</v>
@@ -7248,7 +7374,7 @@
       </c>
       <c r="N51" s="53"/>
     </row>
-    <row r="52" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="41"/>
       <c r="B52" s="9" t="s">
         <v>122</v>
@@ -7274,7 +7400,7 @@
       </c>
       <c r="N52" s="53"/>
     </row>
-    <row r="53" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="41"/>
       <c r="B53" s="9" t="s">
         <v>123</v>
@@ -7300,7 +7426,7 @@
       </c>
       <c r="N53" s="53"/>
     </row>
-    <row r="54" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="41"/>
       <c r="B54" s="9" t="s">
         <v>124</v>
@@ -7330,7 +7456,7 @@
       </c>
       <c r="N54" s="53"/>
     </row>
-    <row r="55" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="41"/>
       <c r="B55" s="9" t="s">
         <v>125</v>
@@ -7356,7 +7482,7 @@
       </c>
       <c r="N55" s="53"/>
     </row>
-    <row r="56" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="41"/>
       <c r="B56" s="9" t="s">
         <v>126</v>
@@ -7382,7 +7508,7 @@
       </c>
       <c r="N56" s="53"/>
     </row>
-    <row r="57" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="41"/>
       <c r="B57" s="9" t="s">
         <v>127</v>
@@ -7410,7 +7536,7 @@
       </c>
       <c r="N57" s="53"/>
     </row>
-    <row r="58" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="41"/>
       <c r="B58" s="9" t="s">
         <v>128</v>
@@ -7438,7 +7564,7 @@
       </c>
       <c r="N58" s="53"/>
     </row>
-    <row r="59" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="41"/>
       <c r="B59" s="9" t="s">
         <v>129</v>
@@ -7466,7 +7592,7 @@
       </c>
       <c r="N59" s="53"/>
     </row>
-    <row r="60" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="41"/>
       <c r="B60" s="9" t="s">
         <v>130</v>
@@ -7494,7 +7620,7 @@
       </c>
       <c r="N60" s="53"/>
     </row>
-    <row r="61" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="41"/>
       <c r="B61" s="9" t="s">
         <v>131</v>
@@ -7522,7 +7648,7 @@
       </c>
       <c r="N61" s="53"/>
     </row>
-    <row r="62" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="41"/>
       <c r="B62" s="9" t="s">
         <v>132</v>
@@ -7550,7 +7676,7 @@
       </c>
       <c r="N62" s="53"/>
     </row>
-    <row r="63" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="41"/>
       <c r="B63" s="9" t="s">
         <v>133</v>
@@ -7578,7 +7704,7 @@
       </c>
       <c r="N63" s="53"/>
     </row>
-    <row r="64" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="41"/>
       <c r="B64" s="9" t="s">
         <v>134</v>
@@ -7606,7 +7732,7 @@
       </c>
       <c r="N64" s="53"/>
     </row>
-    <row r="65" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="41"/>
       <c r="B65" s="9" t="s">
         <v>135</v>
@@ -7634,7 +7760,7 @@
       </c>
       <c r="N65" s="53"/>
     </row>
-    <row r="66" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="41"/>
       <c r="B66" s="28" t="s">
         <v>136</v>
@@ -7662,7 +7788,7 @@
       </c>
       <c r="N66" s="53"/>
     </row>
-    <row r="67" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="41"/>
       <c r="B67" s="22" t="s">
         <v>137</v>
@@ -7688,7 +7814,7 @@
       </c>
       <c r="N67" s="53"/>
     </row>
-    <row r="68" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="41"/>
       <c r="B68" s="28" t="s">
         <v>138</v>
@@ -7712,7 +7838,7 @@
       </c>
       <c r="N68" s="53"/>
     </row>
-    <row r="69" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="41"/>
       <c r="B69" s="22" t="s">
         <v>139</v>
@@ -7738,7 +7864,7 @@
       </c>
       <c r="N69" s="53"/>
     </row>
-    <row r="70" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="41"/>
       <c r="B70" s="28" t="s">
         <v>140</v>
@@ -7764,7 +7890,7 @@
       </c>
       <c r="N70" s="53"/>
     </row>
-    <row r="71" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="41"/>
       <c r="B71" s="22" t="s">
         <v>141</v>
@@ -7788,7 +7914,7 @@
       </c>
       <c r="N71" s="53"/>
     </row>
-    <row r="72" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="41"/>
       <c r="B72" s="28" t="s">
         <v>142</v>
@@ -7814,7 +7940,7 @@
       </c>
       <c r="N72" s="53"/>
     </row>
-    <row r="73" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="41"/>
       <c r="B73" s="22" t="s">
         <v>143</v>
@@ -7840,7 +7966,7 @@
       </c>
       <c r="N73" s="53"/>
     </row>
-    <row r="74" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="41"/>
       <c r="B74" s="28" t="s">
         <v>144</v>
@@ -7866,7 +7992,7 @@
       </c>
       <c r="N74" s="53"/>
     </row>
-    <row r="75" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="41"/>
       <c r="B75" s="22" t="s">
         <v>145</v>
@@ -7892,7 +8018,7 @@
       </c>
       <c r="N75" s="53"/>
     </row>
-    <row r="76" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="41"/>
       <c r="B76" s="28" t="s">
         <v>146</v>
@@ -7916,7 +8042,7 @@
       </c>
       <c r="N76" s="53"/>
     </row>
-    <row r="77" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="41"/>
       <c r="B77" s="22" t="s">
         <v>147</v>
@@ -7942,7 +8068,7 @@
       </c>
       <c r="N77" s="53"/>
     </row>
-    <row r="78" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="41"/>
       <c r="B78" s="28" t="s">
         <v>148</v>
@@ -7968,7 +8094,7 @@
       </c>
       <c r="N78" s="53"/>
     </row>
-    <row r="79" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="41"/>
       <c r="B79" s="22" t="s">
         <v>149</v>
@@ -7994,7 +8120,7 @@
       </c>
       <c r="N79" s="53"/>
     </row>
-    <row r="80" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="41"/>
       <c r="B80" s="22" t="s">
         <v>150</v>
@@ -8020,7 +8146,7 @@
       </c>
       <c r="N80" s="53"/>
     </row>
-    <row r="81" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="41"/>
       <c r="B81" s="22" t="s">
         <v>151</v>
@@ -8046,7 +8172,7 @@
       </c>
       <c r="N81" s="53"/>
     </row>
-    <row r="82" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="41"/>
       <c r="B82" s="28" t="s">
         <v>152</v>
@@ -8072,7 +8198,7 @@
       </c>
       <c r="N82" s="53"/>
     </row>
-    <row r="83" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="41"/>
       <c r="B83" s="68" t="s">
         <v>153</v>
@@ -8098,7 +8224,7 @@
       </c>
       <c r="N83" s="53"/>
     </row>
-    <row r="84" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="41"/>
       <c r="B84" s="65" t="s">
         <v>154</v>
@@ -8126,7 +8252,7 @@
       </c>
       <c r="N84" s="53"/>
     </row>
-    <row r="85" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="41"/>
       <c r="B85" s="9" t="s">
         <v>155</v>
@@ -8154,7 +8280,7 @@
       </c>
       <c r="N85" s="53"/>
     </row>
-    <row r="86" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="41"/>
       <c r="B86" s="9" t="s">
         <v>156</v>
@@ -8180,7 +8306,7 @@
       </c>
       <c r="N86" s="53"/>
     </row>
-    <row r="87" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="41"/>
       <c r="B87" s="9" t="s">
         <v>157</v>
@@ -8206,7 +8332,7 @@
       </c>
       <c r="N87" s="53"/>
     </row>
-    <row r="88" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="41"/>
       <c r="B88" s="9" t="s">
         <v>158</v>
@@ -8230,7 +8356,7 @@
       </c>
       <c r="N88" s="53"/>
     </row>
-    <row r="89" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="41"/>
       <c r="B89" s="9" t="s">
         <v>159</v>
@@ -8256,7 +8382,7 @@
       </c>
       <c r="N89" s="53"/>
     </row>
-    <row r="90" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="41"/>
       <c r="B90" s="9" t="s">
         <v>160</v>
@@ -8286,7 +8412,7 @@
       </c>
       <c r="N90" s="53"/>
     </row>
-    <row r="91" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="41"/>
       <c r="B91" s="9" t="s">
         <v>161</v>
@@ -8316,7 +8442,7 @@
       </c>
       <c r="N91" s="53"/>
     </row>
-    <row r="92" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="41"/>
       <c r="B92" s="9" t="s">
         <v>162</v>
@@ -8346,7 +8472,7 @@
       </c>
       <c r="N92" s="53"/>
     </row>
-    <row r="93" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="41"/>
       <c r="B93" s="9" t="s">
         <v>163</v>
@@ -8376,7 +8502,7 @@
       </c>
       <c r="N93" s="53"/>
     </row>
-    <row r="94" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="41"/>
       <c r="B94" s="9" t="s">
         <v>164</v>
@@ -8404,7 +8530,7 @@
       </c>
       <c r="N94" s="53"/>
     </row>
-    <row r="95" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="41"/>
       <c r="B95" s="9" t="s">
         <v>165</v>
@@ -8434,7 +8560,7 @@
       </c>
       <c r="N95" s="53"/>
     </row>
-    <row r="96" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="41"/>
       <c r="B96" s="28" t="s">
         <v>166</v>
@@ -8462,7 +8588,7 @@
       </c>
       <c r="N96" s="53"/>
     </row>
-    <row r="97" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="41"/>
       <c r="B97" s="28" t="s">
         <v>167</v>
@@ -8488,7 +8614,7 @@
       </c>
       <c r="N97" s="53"/>
     </row>
-    <row r="98" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="41"/>
       <c r="B98" s="28" t="s">
         <v>168</v>
@@ -8514,7 +8640,7 @@
       </c>
       <c r="N98" s="53"/>
     </row>
-    <row r="99" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="41"/>
       <c r="B99" s="22" t="s">
         <v>169</v>
@@ -8540,7 +8666,7 @@
       </c>
       <c r="N99" s="53"/>
     </row>
-    <row r="100" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="41"/>
       <c r="B100" s="28" t="s">
         <v>170</v>
@@ -8564,7 +8690,7 @@
       </c>
       <c r="N100" s="53"/>
     </row>
-    <row r="101" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="41"/>
       <c r="B101" s="9" t="s">
         <v>171</v>
@@ -8590,7 +8716,7 @@
       </c>
       <c r="N101" s="53"/>
     </row>
-    <row r="102" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="41"/>
       <c r="B102" s="9" t="s">
         <v>172</v>
@@ -8616,7 +8742,7 @@
       </c>
       <c r="N102" s="53"/>
     </row>
-    <row r="103" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="41"/>
       <c r="B103" s="9" t="s">
         <v>173</v>
@@ -8642,7 +8768,7 @@
       </c>
       <c r="N103" s="53"/>
     </row>
-    <row r="104" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="41"/>
       <c r="B104" s="9" t="s">
         <v>174</v>
@@ -8668,7 +8794,7 @@
       </c>
       <c r="N104" s="53"/>
     </row>
-    <row r="105" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A105" s="41"/>
       <c r="B105" s="9" t="s">
         <v>175</v>
@@ -8694,7 +8820,7 @@
       </c>
       <c r="N105" s="53"/>
     </row>
-    <row r="106" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" s="41"/>
       <c r="B106" s="9" t="s">
         <v>176</v>
@@ -8718,7 +8844,7 @@
       </c>
       <c r="N106" s="53"/>
     </row>
-    <row r="107" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="41"/>
       <c r="B107" s="9" t="s">
         <v>177</v>
@@ -8744,7 +8870,7 @@
       </c>
       <c r="N107" s="53"/>
     </row>
-    <row r="108" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="41"/>
       <c r="B108" s="9" t="s">
         <v>178</v>
@@ -8770,7 +8896,7 @@
       </c>
       <c r="N108" s="53"/>
     </row>
-    <row r="109" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="41"/>
       <c r="B109" s="9" t="s">
         <v>179</v>
@@ -8796,7 +8922,7 @@
       </c>
       <c r="N109" s="53"/>
     </row>
-    <row r="110" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="41"/>
       <c r="B110" s="9" t="s">
         <v>180</v>
@@ -8822,7 +8948,7 @@
       </c>
       <c r="N110" s="53"/>
     </row>
-    <row r="111" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A111" s="41"/>
       <c r="B111" s="9" t="s">
         <v>181</v>
@@ -8850,7 +8976,7 @@
       </c>
       <c r="N111" s="53"/>
     </row>
-    <row r="112" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="41"/>
       <c r="B112" s="9" t="s">
         <v>183</v>
@@ -8876,7 +9002,7 @@
       <c r="M112" s="11"/>
       <c r="N112" s="53"/>
     </row>
-    <row r="113" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="41"/>
       <c r="B113" s="9" t="s">
         <v>184</v>
@@ -8904,7 +9030,7 @@
       </c>
       <c r="N113" s="53"/>
     </row>
-    <row r="114" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A114" s="41"/>
       <c r="B114" s="9" t="s">
         <v>185</v>
@@ -8932,7 +9058,7 @@
       </c>
       <c r="N114" s="53"/>
     </row>
-    <row r="115" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A115" s="41"/>
       <c r="B115" s="9" t="s">
         <v>186</v>
@@ -8960,7 +9086,7 @@
       </c>
       <c r="N115" s="53"/>
     </row>
-    <row r="116" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A116" s="41"/>
       <c r="B116" s="9" t="s">
         <v>187</v>
@@ -8988,7 +9114,7 @@
       </c>
       <c r="N116" s="53"/>
     </row>
-    <row r="117" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A117" s="41"/>
       <c r="B117" s="9" t="s">
         <v>188</v>
@@ -9016,7 +9142,7 @@
       </c>
       <c r="N117" s="53"/>
     </row>
-    <row r="118" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A118" s="41"/>
       <c r="B118" s="9" t="s">
         <v>189</v>
@@ -9044,7 +9170,7 @@
       </c>
       <c r="N118" s="53"/>
     </row>
-    <row r="119" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="41"/>
       <c r="B119" s="9" t="s">
         <v>190</v>
@@ -9072,7 +9198,7 @@
       </c>
       <c r="N119" s="53"/>
     </row>
-    <row r="120" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A120" s="41"/>
       <c r="B120" s="9" t="s">
         <v>191</v>
@@ -9100,7 +9226,7 @@
       </c>
       <c r="N120" s="53"/>
     </row>
-    <row r="121" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A121" s="41"/>
       <c r="B121" s="9" t="s">
         <v>192</v>
@@ -9128,7 +9254,7 @@
       </c>
       <c r="N121" s="53"/>
     </row>
-    <row r="122" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="41"/>
       <c r="B122" s="9" t="s">
         <v>193</v>
@@ -9156,7 +9282,7 @@
       </c>
       <c r="N122" s="53"/>
     </row>
-    <row r="123" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A123" s="41"/>
       <c r="B123" s="9" t="s">
         <v>194</v>
@@ -9184,7 +9310,7 @@
       </c>
       <c r="N123" s="53"/>
     </row>
-    <row r="124" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A124" s="41"/>
       <c r="B124" s="9" t="s">
         <v>195</v>
@@ -9212,7 +9338,7 @@
       </c>
       <c r="N124" s="53"/>
     </row>
-    <row r="125" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A125" s="41"/>
       <c r="B125" s="9" t="s">
         <v>196</v>
@@ -9240,7 +9366,7 @@
       </c>
       <c r="N125" s="53"/>
     </row>
-    <row r="126" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A126" s="41"/>
       <c r="B126" s="9" t="s">
         <v>197</v>
@@ -9268,7 +9394,7 @@
       </c>
       <c r="N126" s="53"/>
     </row>
-    <row r="127" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A127" s="41"/>
       <c r="B127" s="9" t="s">
         <v>198</v>
@@ -9296,7 +9422,7 @@
       </c>
       <c r="N127" s="53"/>
     </row>
-    <row r="128" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A128" s="41"/>
       <c r="B128" s="9" t="s">
         <v>199</v>
@@ -9324,7 +9450,7 @@
       </c>
       <c r="N128" s="53"/>
     </row>
-    <row r="129" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A129" s="41"/>
       <c r="B129" s="9" t="s">
         <v>200</v>
@@ -9352,7 +9478,7 @@
       </c>
       <c r="N129" s="53"/>
     </row>
-    <row r="130" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A130" s="41"/>
       <c r="B130" s="9" t="s">
         <v>201</v>
@@ -9380,7 +9506,7 @@
       </c>
       <c r="N130" s="53"/>
     </row>
-    <row r="131" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A131" s="41"/>
       <c r="B131" s="9" t="s">
         <v>202</v>
@@ -9408,7 +9534,7 @@
       </c>
       <c r="N131" s="53"/>
     </row>
-    <row r="132" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A132" s="41"/>
       <c r="B132" s="9" t="s">
         <v>203</v>
@@ -9436,7 +9562,7 @@
       </c>
       <c r="N132" s="53"/>
     </row>
-    <row r="133" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A133" s="41"/>
       <c r="B133" s="9" t="s">
         <v>204</v>
@@ -9464,7 +9590,7 @@
       </c>
       <c r="N133" s="53"/>
     </row>
-    <row r="134" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A134" s="41"/>
       <c r="B134" s="9" t="s">
         <v>205</v>
@@ -9492,7 +9618,7 @@
       </c>
       <c r="N134" s="53"/>
     </row>
-    <row r="135" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A135" s="41"/>
       <c r="B135" s="9" t="s">
         <v>206</v>
@@ -9520,7 +9646,7 @@
       </c>
       <c r="N135" s="53"/>
     </row>
-    <row r="136" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A136" s="41"/>
       <c r="B136" s="9" t="s">
         <v>207</v>
@@ -9548,7 +9674,7 @@
       </c>
       <c r="N136" s="53"/>
     </row>
-    <row r="137" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" s="41"/>
       <c r="B137" s="9" t="s">
         <v>208</v>
@@ -9576,7 +9702,7 @@
       </c>
       <c r="N137" s="53"/>
     </row>
-    <row r="138" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A138" s="41"/>
       <c r="B138" s="9" t="s">
         <v>209</v>
@@ -9604,7 +9730,7 @@
       </c>
       <c r="N138" s="53"/>
     </row>
-    <row r="139" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A139" s="41"/>
       <c r="B139" s="28" t="s">
         <v>210</v>
@@ -9632,7 +9758,7 @@
       </c>
       <c r="N139" s="53"/>
     </row>
-    <row r="140" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A140" s="41"/>
       <c r="B140" s="22" t="s">
         <v>211</v>
@@ -9660,7 +9786,7 @@
       </c>
       <c r="N140" s="53"/>
     </row>
-    <row r="141" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A141" s="41"/>
       <c r="B141" s="28" t="s">
         <v>212</v>
@@ -9688,7 +9814,7 @@
       </c>
       <c r="N141" s="53"/>
     </row>
-    <row r="142" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A142" s="41"/>
       <c r="B142" s="22" t="s">
         <v>213</v>
@@ -9716,7 +9842,7 @@
       </c>
       <c r="N142" s="53"/>
     </row>
-    <row r="143" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A143" s="4"/>
       <c r="B143" s="9" t="s">
         <v>214</v>
@@ -9744,7 +9870,7 @@
       </c>
       <c r="N143" s="53"/>
     </row>
-    <row r="144" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A144" s="41"/>
       <c r="B144" s="9" t="s">
         <v>215</v>
@@ -9774,7 +9900,7 @@
       </c>
       <c r="N144" s="53"/>
     </row>
-    <row r="145" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A145" s="41"/>
       <c r="B145" s="9" t="s">
         <v>216</v>
@@ -9804,7 +9930,7 @@
       </c>
       <c r="N145" s="53"/>
     </row>
-    <row r="146" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A146" s="41"/>
       <c r="B146" s="9" t="s">
         <v>217</v>
@@ -9834,7 +9960,7 @@
       </c>
       <c r="N146" s="53"/>
     </row>
-    <row r="147" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A147" s="41"/>
       <c r="B147" s="9" t="s">
         <v>218</v>
@@ -9864,7 +9990,7 @@
       </c>
       <c r="N147" s="53"/>
     </row>
-    <row r="148" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A148" s="41"/>
       <c r="B148" s="9" t="s">
         <v>219</v>
@@ -9894,7 +10020,7 @@
       </c>
       <c r="N148" s="53"/>
     </row>
-    <row r="149" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A149" s="41"/>
       <c r="B149" s="9" t="s">
         <v>220</v>
@@ -9924,7 +10050,7 @@
       </c>
       <c r="N149" s="53"/>
     </row>
-    <row r="150" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A150" s="41"/>
       <c r="B150" s="9" t="s">
         <v>221</v>
@@ -9952,7 +10078,7 @@
       </c>
       <c r="N150" s="53"/>
     </row>
-    <row r="151" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A151" s="41"/>
       <c r="B151" s="9" t="s">
         <v>222</v>
@@ -9980,7 +10106,7 @@
       </c>
       <c r="N151" s="53"/>
     </row>
-    <row r="152" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A152" s="41"/>
       <c r="B152" s="9" t="s">
         <v>223</v>
@@ -10010,7 +10136,7 @@
       </c>
       <c r="N152" s="53"/>
     </row>
-    <row r="153" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A153" s="41"/>
       <c r="B153" s="9" t="s">
         <v>224</v>
@@ -10040,7 +10166,7 @@
       </c>
       <c r="N153" s="53"/>
     </row>
-    <row r="154" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A154" s="41"/>
       <c r="B154" s="9" t="s">
         <v>225</v>
@@ -10066,7 +10192,7 @@
       </c>
       <c r="N154" s="53"/>
     </row>
-    <row r="155" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A155" s="41"/>
       <c r="B155" s="9" t="s">
         <v>226</v>
@@ -10096,7 +10222,7 @@
       </c>
       <c r="N155" s="53"/>
     </row>
-    <row r="156" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A156" s="41"/>
       <c r="B156" s="9" t="s">
         <v>227</v>
@@ -10124,7 +10250,7 @@
       </c>
       <c r="N156" s="53"/>
     </row>
-    <row r="157" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A157" s="41"/>
       <c r="B157" s="9" t="s">
         <v>228</v>
@@ -10154,7 +10280,7 @@
       </c>
       <c r="N157" s="53"/>
     </row>
-    <row r="158" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A158" s="41"/>
       <c r="B158" s="9" t="s">
         <v>229</v>
@@ -10184,7 +10310,7 @@
       </c>
       <c r="N158" s="53"/>
     </row>
-    <row r="159" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A159" s="41"/>
       <c r="B159" s="22" t="s">
         <v>230</v>
@@ -10214,7 +10340,7 @@
       </c>
       <c r="N159" s="53"/>
     </row>
-    <row r="160" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A160" s="41"/>
       <c r="B160" s="28" t="s">
         <v>232</v>
@@ -10244,7 +10370,7 @@
       </c>
       <c r="N160" s="53"/>
     </row>
-    <row r="161" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A161" s="41"/>
       <c r="B161" s="22" t="s">
         <v>233</v>
@@ -10274,7 +10400,7 @@
       </c>
       <c r="N161" s="53"/>
     </row>
-    <row r="162" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A162" s="41"/>
       <c r="B162" s="28" t="s">
         <v>234</v>
@@ -10302,7 +10428,7 @@
       </c>
       <c r="N162" s="53"/>
     </row>
-    <row r="163" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A163" s="41"/>
       <c r="B163" s="28" t="s">
         <v>235</v>
@@ -10332,7 +10458,7 @@
       </c>
       <c r="N163" s="53"/>
     </row>
-    <row r="164" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A164" s="41"/>
       <c r="B164" s="28" t="s">
         <v>236</v>
@@ -10360,7 +10486,7 @@
       </c>
       <c r="N164" s="53"/>
     </row>
-    <row r="165" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A165" s="41"/>
       <c r="B165" s="22" t="s">
         <v>237</v>
@@ -10390,7 +10516,7 @@
       </c>
       <c r="N165" s="53"/>
     </row>
-    <row r="166" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A166" s="41"/>
       <c r="B166" s="22" t="s">
         <v>238</v>
@@ -10420,7 +10546,7 @@
       </c>
       <c r="N166" s="53"/>
     </row>
-    <row r="167" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A167" s="41"/>
       <c r="B167" s="9" t="s">
         <v>239</v>
@@ -10450,7 +10576,7 @@
       </c>
       <c r="N167" s="53"/>
     </row>
-    <row r="168" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A168" s="41"/>
       <c r="B168" s="9" t="s">
         <v>240</v>
@@ -10480,7 +10606,7 @@
       </c>
       <c r="N168" s="53"/>
     </row>
-    <row r="169" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A169" s="41"/>
       <c r="B169" s="9" t="s">
         <v>241</v>
@@ -10510,7 +10636,7 @@
       </c>
       <c r="N169" s="53"/>
     </row>
-    <row r="170" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A170" s="41"/>
       <c r="B170" s="9" t="s">
         <v>242</v>
@@ -10540,7 +10666,7 @@
       </c>
       <c r="N170" s="53"/>
     </row>
-    <row r="171" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A171" s="41"/>
       <c r="B171" s="9" t="s">
         <v>243</v>
@@ -10570,7 +10696,7 @@
       </c>
       <c r="N171" s="53"/>
     </row>
-    <row r="172" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A172" s="41"/>
       <c r="B172" s="9" t="s">
         <v>244</v>
@@ -10596,7 +10722,7 @@
       <c r="M172" s="11"/>
       <c r="N172" s="53"/>
     </row>
-    <row r="173" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A173" s="41"/>
       <c r="B173" s="9" t="s">
         <v>245</v>
@@ -10622,7 +10748,7 @@
       <c r="M173" s="11"/>
       <c r="N173" s="53"/>
     </row>
-    <row r="174" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A174" s="41"/>
       <c r="B174" s="9" t="s">
         <v>246</v>
@@ -10648,7 +10774,7 @@
       <c r="M174" s="11"/>
       <c r="N174" s="53"/>
     </row>
-    <row r="175" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A175" s="41"/>
       <c r="B175" s="9" t="s">
         <v>247</v>
@@ -10674,7 +10800,7 @@
       <c r="M175" s="11"/>
       <c r="N175" s="53"/>
     </row>
-    <row r="176" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A176" s="41"/>
       <c r="B176" s="9" t="s">
         <v>248</v>
@@ -10700,7 +10826,7 @@
       <c r="M176" s="11"/>
       <c r="N176" s="53"/>
     </row>
-    <row r="177" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A177" s="41"/>
       <c r="B177" s="9" t="s">
         <v>249</v>
@@ -10726,7 +10852,7 @@
       <c r="M177" s="11"/>
       <c r="N177" s="53"/>
     </row>
-    <row r="178" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A178" s="41"/>
       <c r="B178" s="9" t="s">
         <v>250</v>
@@ -10752,7 +10878,7 @@
       <c r="M178" s="11"/>
       <c r="N178" s="53"/>
     </row>
-    <row r="179" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A179" s="41"/>
       <c r="B179" s="9" t="s">
         <v>251</v>
@@ -10778,7 +10904,7 @@
       <c r="M179" s="11"/>
       <c r="N179" s="53"/>
     </row>
-    <row r="180" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A180" s="41"/>
       <c r="B180" s="18" t="s">
         <v>252</v>
@@ -10804,7 +10930,7 @@
       <c r="M180" s="20"/>
       <c r="N180" s="54"/>
     </row>
-    <row r="181" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A181" s="41"/>
       <c r="B181" s="9" t="s">
         <v>253</v>
@@ -10830,7 +10956,7 @@
       <c r="M181" s="11"/>
       <c r="N181" s="53"/>
     </row>
-    <row r="182" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A182" s="41"/>
       <c r="B182" s="69" t="s">
         <v>254</v>
@@ -10856,7 +10982,7 @@
       <c r="M182" s="64"/>
       <c r="N182" s="55"/>
     </row>
-    <row r="183" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A183" s="41"/>
       <c r="B183" s="9" t="s">
         <v>255</v>
@@ -10882,7 +11008,7 @@
       <c r="M183" s="11"/>
       <c r="N183" s="56"/>
     </row>
-    <row r="184" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A184" s="41"/>
       <c r="B184" s="9" t="s">
         <v>656</v>
@@ -10910,7 +11036,7 @@
       </c>
       <c r="N184" s="57"/>
     </row>
-    <row r="185" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A185" s="41"/>
       <c r="B185" s="9" t="s">
         <v>256</v>
@@ -10936,7 +11062,7 @@
       <c r="M185" s="11"/>
       <c r="N185" s="56"/>
     </row>
-    <row r="186" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A186" s="41"/>
       <c r="B186" s="9" t="s">
         <v>257</v>
@@ -10962,7 +11088,7 @@
       <c r="M186" s="11"/>
       <c r="N186" s="57"/>
     </row>
-    <row r="187" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A187" s="41"/>
       <c r="B187" s="9" t="s">
         <v>258</v>
@@ -10988,7 +11114,7 @@
       <c r="M187" s="11"/>
       <c r="N187" s="56"/>
     </row>
-    <row r="188" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A188" s="41"/>
       <c r="B188" s="9" t="s">
         <v>259</v>
@@ -11014,7 +11140,7 @@
       <c r="M188" s="11"/>
       <c r="N188" s="57"/>
     </row>
-    <row r="189" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A189" s="41"/>
       <c r="B189" s="9" t="s">
         <v>260</v>
@@ -11040,7 +11166,7 @@
       <c r="M189" s="11"/>
       <c r="N189" s="56"/>
     </row>
-    <row r="190" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A190" s="41"/>
       <c r="B190" s="9" t="s">
         <v>261</v>
@@ -11066,7 +11192,7 @@
       <c r="M190" s="11"/>
       <c r="N190" s="57"/>
     </row>
-    <row r="191" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A191" s="41"/>
       <c r="B191" s="9" t="s">
         <v>262</v>
@@ -11092,7 +11218,7 @@
       <c r="M191" s="11"/>
       <c r="N191" s="56"/>
     </row>
-    <row r="192" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A192" s="41"/>
       <c r="B192" s="9" t="s">
         <v>263</v>
@@ -11118,7 +11244,7 @@
       <c r="M192" s="11"/>
       <c r="N192" s="57"/>
     </row>
-    <row r="193" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A193" s="41"/>
       <c r="B193" s="9" t="s">
         <v>264</v>
@@ -11144,7 +11270,7 @@
       <c r="M193" s="11"/>
       <c r="N193" s="56"/>
     </row>
-    <row r="194" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A194" s="41"/>
       <c r="B194" s="9" t="s">
         <v>265</v>
@@ -11170,7 +11296,7 @@
       <c r="M194" s="11"/>
       <c r="N194" s="57"/>
     </row>
-    <row r="195" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A195" s="41"/>
       <c r="B195" s="9" t="s">
         <v>266</v>
@@ -11196,7 +11322,7 @@
       <c r="M195" s="11"/>
       <c r="N195" s="56"/>
     </row>
-    <row r="196" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A196" s="41"/>
       <c r="B196" s="28" t="s">
         <v>267</v>
@@ -11222,7 +11348,7 @@
       <c r="M196" s="62"/>
       <c r="N196" s="57"/>
     </row>
-    <row r="197" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A197" s="41"/>
       <c r="B197" s="22" t="s">
         <v>268</v>
@@ -11248,7 +11374,7 @@
       <c r="M197" s="62"/>
       <c r="N197" s="56"/>
     </row>
-    <row r="198" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A198" s="41"/>
       <c r="B198" s="28" t="s">
         <v>269</v>
@@ -11274,7 +11400,7 @@
       <c r="M198" s="62"/>
       <c r="N198" s="57"/>
     </row>
-    <row r="199" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A199" s="41"/>
       <c r="B199" s="22" t="s">
         <v>270</v>
@@ -11300,7 +11426,7 @@
       <c r="M199" s="62"/>
       <c r="N199" s="56"/>
     </row>
-    <row r="200" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A200" s="41"/>
       <c r="B200" s="28" t="s">
         <v>271</v>
@@ -11326,7 +11452,7 @@
       <c r="M200" s="62"/>
       <c r="N200" s="57"/>
     </row>
-    <row r="201" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A201" s="41"/>
       <c r="B201" s="22" t="s">
         <v>272</v>
@@ -11352,7 +11478,7 @@
       <c r="M201" s="62"/>
       <c r="N201" s="56"/>
     </row>
-    <row r="202" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A202" s="41"/>
       <c r="B202" s="22" t="s">
         <v>273</v>
@@ -11378,7 +11504,7 @@
       <c r="M202" s="62"/>
       <c r="N202" s="57"/>
     </row>
-    <row r="203" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A203" s="41"/>
       <c r="B203" s="9" t="s">
         <v>274</v>
@@ -11404,7 +11530,7 @@
       <c r="M203" s="11"/>
       <c r="N203" s="56"/>
     </row>
-    <row r="204" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A204" s="41"/>
       <c r="B204" s="9" t="s">
         <v>275</v>
@@ -11430,7 +11556,7 @@
       <c r="M204" s="11"/>
       <c r="N204" s="57"/>
     </row>
-    <row r="205" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A205" s="41"/>
       <c r="B205" s="9" t="s">
         <v>276</v>
@@ -11454,7 +11580,7 @@
       <c r="M205" s="11"/>
       <c r="N205" s="56"/>
     </row>
-    <row r="206" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A206" s="41"/>
       <c r="B206" s="9" t="s">
         <v>277</v>
@@ -11480,7 +11606,7 @@
       <c r="M206" s="11"/>
       <c r="N206" s="57"/>
     </row>
-    <row r="207" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A207" s="41"/>
       <c r="B207" s="9" t="s">
         <v>278</v>
@@ -11506,7 +11632,7 @@
       <c r="M207" s="11"/>
       <c r="N207" s="56"/>
     </row>
-    <row r="208" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A208" s="41"/>
       <c r="B208" s="9" t="s">
         <v>279</v>
@@ -11532,7 +11658,7 @@
       <c r="M208" s="11"/>
       <c r="N208" s="57"/>
     </row>
-    <row r="209" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A209" s="41"/>
       <c r="B209" s="9" t="s">
         <v>280</v>
@@ -11558,7 +11684,7 @@
       <c r="M209" s="11"/>
       <c r="N209" s="56"/>
     </row>
-    <row r="210" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A210" s="41"/>
       <c r="B210" s="9" t="s">
         <v>281</v>
@@ -11582,7 +11708,7 @@
       <c r="M210" s="11"/>
       <c r="N210" s="57"/>
     </row>
-    <row r="211" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A211" s="41"/>
       <c r="B211" s="9" t="s">
         <v>282</v>
@@ -11606,7 +11732,7 @@
       <c r="M211" s="11"/>
       <c r="N211" s="56"/>
     </row>
-    <row r="212" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A212" s="41"/>
       <c r="B212" s="9" t="s">
         <v>283</v>
@@ -11630,7 +11756,7 @@
       <c r="M212" s="11"/>
       <c r="N212" s="57"/>
     </row>
-    <row r="213" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A213" s="41"/>
       <c r="B213" s="9" t="s">
         <v>284</v>
@@ -11656,7 +11782,7 @@
       <c r="M213" s="11"/>
       <c r="N213" s="56"/>
     </row>
-    <row r="214" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A214" s="41"/>
       <c r="B214" s="9" t="s">
         <v>285</v>
@@ -11682,7 +11808,7 @@
       <c r="M214" s="11"/>
       <c r="N214" s="57"/>
     </row>
-    <row r="215" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A215" s="41"/>
       <c r="B215" s="9" t="s">
         <v>286</v>
@@ -11708,7 +11834,7 @@
       <c r="M215" s="11"/>
       <c r="N215" s="56"/>
     </row>
-    <row r="216" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A216" s="41"/>
       <c r="B216" s="9" t="s">
         <v>287</v>
@@ -11736,7 +11862,7 @@
       <c r="M216" s="11"/>
       <c r="N216" s="57"/>
     </row>
-    <row r="217" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A217" s="41"/>
       <c r="B217" s="9" t="s">
         <v>288</v>
@@ -11762,7 +11888,7 @@
       <c r="M217" s="11"/>
       <c r="N217" s="56"/>
     </row>
-    <row r="218" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A218" s="41"/>
       <c r="B218" s="9" t="s">
         <v>289</v>
@@ -11788,7 +11914,7 @@
       <c r="M218" s="11"/>
       <c r="N218" s="57"/>
     </row>
-    <row r="219" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A219" s="41"/>
       <c r="B219" s="9" t="s">
         <v>290</v>
@@ -11814,7 +11940,7 @@
       <c r="M219" s="11"/>
       <c r="N219" s="56"/>
     </row>
-    <row r="220" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A220" s="41"/>
       <c r="B220" s="9" t="s">
         <v>291</v>
@@ -11840,7 +11966,7 @@
       <c r="M220" s="11"/>
       <c r="N220" s="57"/>
     </row>
-    <row r="221" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A221" s="41"/>
       <c r="B221" s="9" t="s">
         <v>292</v>
@@ -11864,7 +11990,7 @@
       <c r="M221" s="11"/>
       <c r="N221" s="56"/>
     </row>
-    <row r="222" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A222" s="41"/>
       <c r="B222" s="9" t="s">
         <v>293</v>
@@ -11890,7 +12016,7 @@
       <c r="M222" s="11"/>
       <c r="N222" s="57"/>
     </row>
-    <row r="223" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A223" s="41"/>
       <c r="B223" s="9" t="s">
         <v>294</v>
@@ -11916,7 +12042,7 @@
       <c r="M223" s="11"/>
       <c r="N223" s="56"/>
     </row>
-    <row r="224" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A224" s="41"/>
       <c r="B224" s="9" t="s">
         <v>295</v>
@@ -11942,7 +12068,7 @@
       <c r="M224" s="11"/>
       <c r="N224" s="57"/>
     </row>
-    <row r="225" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A225" s="41"/>
       <c r="B225" s="9" t="s">
         <v>296</v>
@@ -11964,7 +12090,7 @@
       <c r="M225" s="11"/>
       <c r="N225" s="56"/>
     </row>
-    <row r="226" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A226" s="41"/>
       <c r="B226" s="9" t="s">
         <v>297</v>
@@ -11990,7 +12116,7 @@
       <c r="M226" s="11"/>
       <c r="N226" s="57"/>
     </row>
-    <row r="227" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A227" s="41"/>
       <c r="B227" s="9" t="s">
         <v>298</v>
@@ -12016,7 +12142,7 @@
       <c r="M227" s="11"/>
       <c r="N227" s="56"/>
     </row>
-    <row r="228" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A228" s="41"/>
       <c r="B228" s="9" t="s">
         <v>299</v>
@@ -12042,7 +12168,7 @@
       <c r="M228" s="11"/>
       <c r="N228" s="57"/>
     </row>
-    <row r="229" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A229" s="41"/>
       <c r="B229" s="9" t="s">
         <v>300</v>
@@ -12068,7 +12194,7 @@
       <c r="M229" s="11"/>
       <c r="N229" s="56"/>
     </row>
-    <row r="230" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A230" s="41"/>
       <c r="B230" s="9" t="s">
         <v>301</v>
@@ -12094,7 +12220,7 @@
       <c r="M230" s="11"/>
       <c r="N230" s="57"/>
     </row>
-    <row r="231" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A231" s="41"/>
       <c r="B231" s="9" t="s">
         <v>302</v>
@@ -12122,7 +12248,7 @@
       <c r="M231" s="11"/>
       <c r="N231" s="56"/>
     </row>
-    <row r="232" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A232" s="41"/>
       <c r="B232" s="9" t="s">
         <v>303</v>
@@ -12150,7 +12276,7 @@
       <c r="M232" s="11"/>
       <c r="N232" s="57"/>
     </row>
-    <row r="233" spans="1:14" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:14" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A233" s="41"/>
       <c r="B233" s="18" t="s">
         <v>304</v>
@@ -12176,7 +12302,7 @@
       <c r="M233" s="20"/>
       <c r="N233" s="58"/>
     </row>
-    <row r="234" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:14" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A234" s="41"/>
       <c r="B234" s="18" t="s">
         <v>305</v>
@@ -12200,7 +12326,7 @@
       <c r="M234" s="20"/>
       <c r="N234" s="59"/>
     </row>
-    <row r="235" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:14" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A235" s="41"/>
       <c r="B235" s="18" t="s">
         <v>306</v>
@@ -12226,7 +12352,7 @@
       <c r="M235" s="20"/>
       <c r="N235" s="60"/>
     </row>
-    <row r="236" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:14" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A236" s="41"/>
       <c r="B236" s="18" t="s">
         <v>307</v>
@@ -12248,7 +12374,7 @@
       <c r="M236" s="20"/>
       <c r="N236" s="61"/>
     </row>
-    <row r="237" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:14" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A237" s="41"/>
       <c r="B237" s="18" t="s">
         <v>308</v>
@@ -12270,7 +12396,7 @@
       <c r="M237" s="20"/>
       <c r="N237" s="60"/>
     </row>
-    <row r="238" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:14" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A238" s="41"/>
       <c r="B238" s="18" t="s">
         <v>309</v>
@@ -12298,7 +12424,7 @@
       <c r="M238" s="20"/>
       <c r="N238" s="61"/>
     </row>
-    <row r="239" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A239" s="41"/>
       <c r="B239" s="18" t="s">
         <v>310</v>
@@ -12320,7 +12446,7 @@
       <c r="M239" s="20"/>
       <c r="N239" s="60"/>
     </row>
-    <row r="240" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:14" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A240" s="41"/>
       <c r="B240" s="18" t="s">
         <v>311</v>
@@ -12342,7 +12468,7 @@
       <c r="M240" s="20"/>
       <c r="N240" s="61"/>
     </row>
-    <row r="241" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:14" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A241" s="41"/>
       <c r="B241" s="18" t="s">
         <v>312</v>
@@ -12368,7 +12494,7 @@
       <c r="M241" s="20"/>
       <c r="N241" s="60"/>
     </row>
-    <row r="242" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:14" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A242" s="41"/>
       <c r="B242" s="18" t="s">
         <v>313</v>
@@ -12394,7 +12520,7 @@
       <c r="M242" s="20"/>
       <c r="N242" s="61"/>
     </row>
-    <row r="243" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:14" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A243" s="41"/>
       <c r="B243" s="18" t="s">
         <v>314</v>
@@ -12420,7 +12546,7 @@
       <c r="M243" s="20"/>
       <c r="N243" s="60"/>
     </row>
-    <row r="244" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:14" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A244" s="41"/>
       <c r="B244" s="18" t="s">
         <v>315</v>
@@ -12446,7 +12572,7 @@
       <c r="M244" s="20"/>
       <c r="N244" s="61"/>
     </row>
-    <row r="245" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A245" s="41"/>
       <c r="B245" s="67" t="s">
         <v>316</v>
@@ -12472,7 +12598,7 @@
       <c r="M245" s="63"/>
       <c r="N245" s="60"/>
     </row>
-    <row r="246" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A246" s="150"/>
       <c r="B246" s="36" t="s">
         <v>317</v>
@@ -12496,7 +12622,7 @@
       <c r="M246" s="63"/>
       <c r="N246" s="61"/>
     </row>
-    <row r="247" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:14" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A247" s="151"/>
       <c r="B247" s="53" t="s">
         <v>318</v>
@@ -12522,7 +12648,7 @@
       <c r="M247" s="148"/>
       <c r="N247" s="152"/>
     </row>
-    <row r="248" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A248" s="151"/>
       <c r="B248" s="53" t="s">
         <v>319</v>
@@ -12548,7 +12674,7 @@
       <c r="M248" s="148"/>
       <c r="N248" s="152"/>
     </row>
-    <row r="249" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:14" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A249" s="150"/>
       <c r="B249" s="103" t="s">
         <v>320</v>
@@ -12573,7 +12699,7 @@
       <c r="L249" s="106"/>
       <c r="M249" s="112"/>
     </row>
-    <row r="250" spans="1:14" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:14" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A250" s="151"/>
       <c r="B250" s="153" t="s">
         <v>321</v>
@@ -12599,7 +12725,7 @@
       <c r="M250" s="155"/>
       <c r="N250" s="152"/>
     </row>
-    <row r="251" spans="1:14" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:14" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A251" s="151"/>
       <c r="B251" s="153" t="s">
         <v>322</v>
@@ -12625,7 +12751,7 @@
       <c r="M251" s="155"/>
       <c r="N251" s="152"/>
     </row>
-    <row r="252" spans="1:14" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:14" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A252" s="41"/>
       <c r="B252" s="3" t="s">
         <v>323</v>
@@ -12645,7 +12771,7 @@
       <c r="I252" s="42"/>
       <c r="J252" s="42"/>
     </row>
-    <row r="253" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:14" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A253" s="150"/>
       <c r="B253" s="3" t="s">
         <v>324</v>
@@ -12666,7 +12792,7 @@
       <c r="I253" s="42"/>
       <c r="J253" s="42"/>
     </row>
-    <row r="254" spans="1:14" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:14" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A254" s="151"/>
       <c r="B254" s="153" t="s">
         <v>325</v>
@@ -12692,7 +12818,7 @@
       <c r="M254" s="155"/>
       <c r="N254" s="152"/>
     </row>
-    <row r="255" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A255" s="151"/>
       <c r="B255" s="153" t="s">
         <v>326</v>
@@ -12716,7 +12842,7 @@
       <c r="M255" s="155"/>
       <c r="N255" s="152"/>
     </row>
-    <row r="256" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A256" s="151"/>
       <c r="B256" s="153" t="s">
         <v>327</v>
@@ -12742,7 +12868,7 @@
       <c r="M256" s="155"/>
       <c r="N256" s="152"/>
     </row>
-    <row r="257" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A257" s="151"/>
       <c r="B257" s="153" t="s">
         <v>328</v>
@@ -12768,7 +12894,7 @@
       <c r="M257" s="155"/>
       <c r="N257" s="152"/>
     </row>
-    <row r="258" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A258" s="151"/>
       <c r="B258" s="134" t="s">
         <v>329</v>
@@ -12794,7 +12920,7 @@
       <c r="M258" s="12"/>
       <c r="N258" s="136"/>
     </row>
-    <row r="259" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A259" s="41"/>
       <c r="B259" s="126" t="s">
         <v>330</v>
@@ -12822,7 +12948,7 @@
       <c r="M259" s="119"/>
       <c r="N259" s="123"/>
     </row>
-    <row r="260" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A260" s="41"/>
       <c r="B260" s="125" t="s">
         <v>331</v>
@@ -12846,7 +12972,7 @@
       <c r="M260" s="124"/>
       <c r="N260" s="121"/>
     </row>
-    <row r="261" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A261" s="41"/>
       <c r="B261" s="126" t="s">
         <v>332</v>
@@ -12870,7 +12996,7 @@
       <c r="M261" s="119"/>
       <c r="N261" s="123"/>
     </row>
-    <row r="262" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A262" s="41"/>
       <c r="B262" s="125" t="s">
         <v>333</v>
@@ -12896,7 +13022,7 @@
       <c r="M262" s="124"/>
       <c r="N262" s="121"/>
     </row>
-    <row r="263" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A263" s="41"/>
       <c r="B263" s="127" t="s">
         <v>334</v>
@@ -12924,7 +13050,7 @@
       <c r="M263" s="119"/>
       <c r="N263" s="123"/>
     </row>
-    <row r="264" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A264" s="41"/>
       <c r="B264" s="128" t="s">
         <v>335</v>
@@ -12952,7 +13078,7 @@
       <c r="M264" s="124"/>
       <c r="N264" s="121"/>
     </row>
-    <row r="265" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A265" s="41"/>
       <c r="B265" s="127" t="s">
         <v>336</v>
@@ -12980,7 +13106,7 @@
       <c r="M265" s="119"/>
       <c r="N265" s="123"/>
     </row>
-    <row r="266" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A266" s="41"/>
       <c r="B266" s="128" t="s">
         <v>337</v>
@@ -13008,7 +13134,7 @@
       <c r="M266" s="124"/>
       <c r="N266" s="121"/>
     </row>
-    <row r="267" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A267" s="41"/>
       <c r="B267" s="127" t="s">
         <v>338</v>
@@ -13036,7 +13162,7 @@
       <c r="M267" s="119"/>
       <c r="N267" s="123"/>
     </row>
-    <row r="268" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A268" s="41"/>
       <c r="B268" s="125" t="s">
         <v>339</v>
@@ -13064,7 +13190,7 @@
       <c r="M268" s="124"/>
       <c r="N268" s="121"/>
     </row>
-    <row r="269" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A269" s="41"/>
       <c r="B269" s="127" t="s">
         <v>340</v>
@@ -13092,7 +13218,7 @@
       <c r="M269" s="119"/>
       <c r="N269" s="123"/>
     </row>
-    <row r="270" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A270" s="41"/>
       <c r="B270" s="125" t="s">
         <v>341</v>
@@ -13118,7 +13244,7 @@
       <c r="M270" s="124"/>
       <c r="N270" s="121"/>
     </row>
-    <row r="271" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A271" s="41"/>
       <c r="B271" s="126" t="s">
         <v>342</v>
@@ -13144,7 +13270,7 @@
       <c r="M271" s="119"/>
       <c r="N271" s="123"/>
     </row>
-    <row r="272" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A272" s="150"/>
       <c r="B272" s="142" t="s">
         <v>343</v>
@@ -13170,7 +13296,7 @@
       <c r="M272" s="145"/>
       <c r="N272" s="144"/>
     </row>
-    <row r="273" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A273" s="166"/>
       <c r="B273" s="157" t="s">
         <v>344</v>
@@ -13198,7 +13324,7 @@
       <c r="M273" s="159"/>
       <c r="N273" s="162"/>
     </row>
-    <row r="274" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A274" s="167"/>
       <c r="B274" s="165" t="s">
         <v>345</v>
@@ -13230,7 +13356,7 @@
       </c>
       <c r="N274" s="163"/>
     </row>
-    <row r="275" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A275" s="167"/>
       <c r="B275" s="165" t="s">
         <v>346</v>
@@ -13258,7 +13384,7 @@
       <c r="M275" s="164"/>
       <c r="N275" s="163"/>
     </row>
-    <row r="276" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A276" s="167"/>
       <c r="B276" s="165" t="s">
         <v>347</v>
@@ -13290,7 +13416,7 @@
       </c>
       <c r="N276" s="163"/>
     </row>
-    <row r="277" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A277" s="168"/>
       <c r="B277" s="165" t="s">
         <v>348</v>
@@ -13322,7 +13448,7 @@
       </c>
       <c r="N277" s="163"/>
     </row>
-    <row r="278" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B278" s="3" t="s">
         <v>349</v>
       </c>
@@ -13347,7 +13473,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="279" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="B279" s="3" t="s">
         <v>350</v>
       </c>
@@ -13375,7 +13501,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="280" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="B280" s="3" t="s">
         <v>351</v>
       </c>
@@ -13400,7 +13526,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="281" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="B281" s="3" t="s">
         <v>352</v>
       </c>
@@ -13422,7 +13548,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="282" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B282" s="3" t="s">
         <v>353</v>
       </c>
@@ -13447,7 +13573,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="283" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B283" s="3" t="s">
         <v>354</v>
       </c>
@@ -13472,7 +13598,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="284" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B284" s="3" t="s">
         <v>355</v>
       </c>
@@ -13497,7 +13623,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="285" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B285" s="3" t="s">
         <v>356</v>
       </c>
@@ -13530,7 +13656,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="286" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="B286" s="3" t="s">
         <v>357</v>
       </c>
@@ -13555,7 +13681,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="287" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B287" s="3" t="s">
         <v>358</v>
       </c>
@@ -13585,7 +13711,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="288" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B288" s="3" t="s">
         <v>359</v>
       </c>
@@ -13607,7 +13733,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="289" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="289" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B289" s="3" t="s">
         <v>360</v>
       </c>
@@ -13635,7 +13761,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="290" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="290" spans="2:13" ht="45" x14ac:dyDescent="0.25">
       <c r="B290" s="3" t="s">
         <v>361</v>
       </c>
@@ -13663,7 +13789,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="291" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="291" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B291" s="3" t="s">
         <v>362</v>
       </c>
@@ -13688,7 +13814,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="292" spans="2:13" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="292" spans="2:13" ht="45" x14ac:dyDescent="0.25">
       <c r="B292" s="3" t="s">
         <v>363</v>
       </c>
@@ -13719,7 +13845,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="293" spans="2:13" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="293" spans="2:13" ht="45" x14ac:dyDescent="0.25">
       <c r="B293" s="3" t="s">
         <v>364</v>
       </c>
@@ -13744,7 +13870,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="294" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="294" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B294" s="3" t="s">
         <v>365</v>
       </c>
@@ -13772,7 +13898,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="295" spans="2:13" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="295" spans="2:13" ht="45" x14ac:dyDescent="0.25">
       <c r="B295" s="3" t="s">
         <v>366</v>
       </c>
@@ -13800,7 +13926,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="296" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="296" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B296" s="3" t="s">
         <v>367</v>
       </c>
@@ -13828,7 +13954,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="297" spans="2:13" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="297" spans="2:13" ht="45" x14ac:dyDescent="0.25">
       <c r="B297" s="3" t="s">
         <v>368</v>
       </c>
@@ -13856,7 +13982,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="298" spans="2:13" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="298" spans="2:13" ht="45" x14ac:dyDescent="0.25">
       <c r="B298" s="3" t="s">
         <v>369</v>
       </c>
@@ -13886,7 +14012,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="299" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="299" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B299" s="3" t="s">
         <v>370</v>
       </c>
@@ -13911,7 +14037,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="300" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="300" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B300" s="3" t="s">
         <v>371</v>
       </c>
@@ -13939,7 +14065,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="301" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="301" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B301" s="3" t="s">
         <v>372</v>
       </c>
@@ -13961,7 +14087,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="302" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="302" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B302" s="3" t="s">
         <v>373</v>
       </c>
@@ -13989,7 +14115,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="303" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="303" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B303" s="3" t="s">
         <v>374</v>
       </c>
@@ -14011,7 +14137,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="304" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="304" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B304" s="3" t="s">
         <v>375</v>
       </c>
@@ -14036,7 +14162,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="305" spans="2:13" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="305" spans="2:13" ht="60" x14ac:dyDescent="0.25">
       <c r="B305" s="3" t="s">
         <v>376</v>
       </c>
@@ -14061,7 +14187,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="306" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="306" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B306" s="3" t="s">
         <v>377</v>
       </c>
@@ -14089,7 +14215,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="307" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="307" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B307" s="3" t="s">
         <v>378</v>
       </c>
@@ -14114,7 +14240,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="308" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="308" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B308" s="3" t="s">
         <v>379</v>
       </c>
@@ -14136,7 +14262,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="309" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="309" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B309" s="3" t="s">
         <v>380</v>
       </c>
@@ -14161,7 +14287,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="310" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="310" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B310" s="3" t="s">
         <v>381</v>
       </c>
@@ -14194,7 +14320,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="311" spans="2:13" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="311" spans="2:13" ht="45" x14ac:dyDescent="0.25">
       <c r="B311" s="3" t="s">
         <v>382</v>
       </c>
@@ -14219,7 +14345,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="312" spans="2:13" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="312" spans="2:13" ht="45" x14ac:dyDescent="0.25">
       <c r="B312" s="3" t="s">
         <v>383</v>
       </c>
@@ -14247,7 +14373,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="313" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="313" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B313" s="3" t="s">
         <v>384</v>
       </c>
@@ -14272,7 +14398,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="314" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="314" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B314" s="3" t="s">
         <v>385</v>
       </c>
@@ -14300,7 +14426,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="315" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="315" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B315" s="3" t="s">
         <v>386</v>
       </c>
@@ -14325,7 +14451,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="316" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="316" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B316" s="3" t="s">
         <v>387</v>
       </c>
@@ -14353,7 +14479,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="317" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="317" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B317" s="3" t="s">
         <v>388</v>
       </c>
@@ -14381,7 +14507,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="318" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="318" spans="2:13" ht="45" x14ac:dyDescent="0.25">
       <c r="B318" s="3" t="s">
         <v>389</v>
       </c>
@@ -14409,7 +14535,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="319" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="319" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B319" s="3" t="s">
         <v>390</v>
       </c>
@@ -14431,7 +14557,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="320" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="320" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B320" s="3" t="s">
         <v>391</v>
       </c>
@@ -14459,7 +14585,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="321" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="321" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B321" s="3" t="s">
         <v>392</v>
       </c>
@@ -14489,7 +14615,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="322" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="322" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B322" s="3" t="s">
         <v>393</v>
       </c>
@@ -14520,7 +14646,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="323" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="323" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B323" s="3" t="s">
         <v>394</v>
       </c>
@@ -14545,7 +14671,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="324" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="324" spans="2:13" ht="45" x14ac:dyDescent="0.25">
       <c r="B324" s="3" t="s">
         <v>395</v>
       </c>
@@ -14567,7 +14693,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="325" spans="2:13" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="325" spans="2:13" ht="60" x14ac:dyDescent="0.25">
       <c r="B325" s="3" t="s">
         <v>396</v>
       </c>
@@ -14595,7 +14721,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="326" spans="2:13" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="326" spans="2:13" ht="45" x14ac:dyDescent="0.25">
       <c r="B326" s="3" t="s">
         <v>397</v>
       </c>
@@ -14623,7 +14749,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="327" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="327" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B327" s="3" t="s">
         <v>398</v>
       </c>
@@ -14645,7 +14771,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="328" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="328" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B328" s="3" t="s">
         <v>399</v>
       </c>
@@ -14670,7 +14796,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="329" spans="2:13" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="329" spans="2:13" ht="45" x14ac:dyDescent="0.25">
       <c r="B329" s="3" t="s">
         <v>400</v>
       </c>
@@ -14695,7 +14821,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="330" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="330" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B330" s="3" t="s">
         <v>401</v>
       </c>
@@ -14723,7 +14849,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="331" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="331" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B331" s="3" t="s">
         <v>402</v>
       </c>
@@ -14751,7 +14877,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="332" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="332" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B332" s="3" t="s">
         <v>403</v>
       </c>
@@ -14776,7 +14902,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="333" spans="2:13" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="333" spans="2:13" ht="45" x14ac:dyDescent="0.25">
       <c r="B333" s="3" t="s">
         <v>404</v>
       </c>
@@ -14801,7 +14927,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="334" spans="2:13" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="334" spans="2:13" ht="60" x14ac:dyDescent="0.25">
       <c r="B334" s="3" t="s">
         <v>405</v>
       </c>
@@ -14826,7 +14952,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="335" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="335" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B335" s="3" t="s">
         <v>406</v>
       </c>
@@ -14851,7 +14977,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="336" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="336" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B336" s="3" t="s">
         <v>407</v>
       </c>
@@ -14876,7 +15002,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="337" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="337" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B337" s="3" t="s">
         <v>408</v>
       </c>
@@ -14906,7 +15032,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="338" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="338" spans="2:13" ht="45" x14ac:dyDescent="0.25">
       <c r="B338" s="3" t="s">
         <v>409</v>
       </c>
@@ -14931,7 +15057,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="339" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="339" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B339" s="3" t="s">
         <v>410</v>
       </c>
@@ -14959,7 +15085,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="340" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="340" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B340" s="3" t="s">
         <v>411</v>
       </c>
@@ -14981,7 +15107,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="341" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="341" spans="2:13" ht="45" x14ac:dyDescent="0.25">
       <c r="B341" s="3" t="s">
         <v>412</v>
       </c>
@@ -15006,7 +15132,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="342" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="342" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B342" s="3" t="s">
         <v>413</v>
       </c>
@@ -15037,7 +15163,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="343" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="343" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B343" s="3" t="s">
         <v>421</v>
       </c>
@@ -15056,7 +15182,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="344" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="344" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B344" s="3" t="s">
         <v>422</v>
       </c>
@@ -15078,7 +15204,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="345" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="345" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B345" s="3" t="s">
         <v>423</v>
       </c>
@@ -15103,7 +15229,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="346" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="346" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B346" s="3" t="s">
         <v>424</v>
       </c>
@@ -15125,7 +15251,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="347" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="347" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B347" s="3" t="s">
         <v>425</v>
       </c>
@@ -15147,7 +15273,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="348" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="348" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B348" s="3" t="s">
         <v>702</v>
       </c>
@@ -15177,7 +15303,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="349" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="349" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B349" s="3" t="s">
         <v>654</v>
       </c>
@@ -15202,7 +15328,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="350" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="350" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B350" s="3" t="s">
         <v>705</v>
       </c>
@@ -15221,7 +15347,7 @@
       <c r="I350" s="42"/>
       <c r="J350" s="42"/>
     </row>
-    <row r="351" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="351" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B351" s="3" t="s">
         <v>707</v>
       </c>
@@ -15237,7 +15363,7 @@
       <c r="I351" s="42"/>
       <c r="J351" s="42"/>
     </row>
-    <row r="352" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="352" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B352" s="3" t="s">
         <v>709</v>
       </c>
@@ -15259,7 +15385,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="353" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="353" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B353" s="3" t="s">
         <v>711</v>
       </c>
@@ -15281,7 +15407,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="354" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="354" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B354" s="3" t="s">
         <v>713</v>
       </c>
@@ -15297,7 +15423,7 @@
       <c r="I354" s="42"/>
       <c r="J354" s="42"/>
     </row>
-    <row r="355" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="355" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B355" s="3" t="s">
         <v>714</v>
       </c>
@@ -15316,7 +15442,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="356" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="356" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B356" s="3" t="s">
         <v>716</v>
       </c>
@@ -15335,7 +15461,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="357" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="357" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B357" s="3" t="s">
         <v>718</v>
       </c>
@@ -15354,7 +15480,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="358" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="358" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B358" s="3" t="s">
         <v>720</v>
       </c>
@@ -15370,7 +15496,7 @@
       <c r="I358" s="42"/>
       <c r="J358" s="42"/>
     </row>
-    <row r="359" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="359" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B359" s="3" t="s">
         <v>721</v>
       </c>
@@ -15386,7 +15512,7 @@
       <c r="I359" s="42"/>
       <c r="J359" s="42"/>
     </row>
-    <row r="360" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="360" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B360" s="3" t="s">
         <v>722</v>
       </c>
@@ -15402,7 +15528,7 @@
       <c r="I360" s="42"/>
       <c r="J360" s="42"/>
     </row>
-    <row r="361" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="361" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B361" s="3" t="s">
         <v>723</v>
       </c>
@@ -15418,7 +15544,7 @@
       <c r="I361" s="42"/>
       <c r="J361" s="42"/>
     </row>
-    <row r="362" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="362" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B362" s="3" t="s">
         <v>724</v>
       </c>
@@ -15434,7 +15560,7 @@
       <c r="I362" s="42"/>
       <c r="J362" s="42"/>
     </row>
-    <row r="363" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="363" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B363" s="3" t="s">
         <v>725</v>
       </c>
@@ -15450,7 +15576,7 @@
       <c r="I363" s="42"/>
       <c r="J363" s="42"/>
     </row>
-    <row r="364" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="364" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B364" s="3" t="s">
         <v>726</v>
       </c>
@@ -15466,7 +15592,7 @@
       <c r="I364" s="42"/>
       <c r="J364" s="42"/>
     </row>
-    <row r="365" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="365" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B365" s="3" t="s">
         <v>765</v>
       </c>
@@ -15482,7 +15608,7 @@
       <c r="I365" s="42"/>
       <c r="J365" s="42"/>
     </row>
-    <row r="366" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="366" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B366" s="3" t="s">
         <v>727</v>
       </c>
@@ -15498,7 +15624,7 @@
       <c r="I366" s="42"/>
       <c r="J366" s="42"/>
     </row>
-    <row r="367" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="367" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B367" s="3" t="s">
         <v>728</v>
       </c>
@@ -15514,7 +15640,7 @@
       <c r="I367" s="42"/>
       <c r="J367" s="42"/>
     </row>
-    <row r="368" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="368" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B368" s="3" t="s">
         <v>729</v>
       </c>
@@ -15527,7 +15653,7 @@
       <c r="I368" s="42"/>
       <c r="J368" s="42"/>
     </row>
-    <row r="369" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="369" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B369" s="3" t="s">
         <v>730</v>
       </c>
@@ -15540,7 +15666,7 @@
       <c r="I369" s="42"/>
       <c r="J369" s="42"/>
     </row>
-    <row r="370" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="370" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B370" s="3" t="s">
         <v>731</v>
       </c>
@@ -15556,7 +15682,7 @@
       <c r="I370" s="42"/>
       <c r="J370" s="42"/>
     </row>
-    <row r="371" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="371" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B371" s="3" t="s">
         <v>732</v>
       </c>
@@ -15578,7 +15704,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="372" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="372" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B372" s="3" t="s">
         <v>733</v>
       </c>
@@ -15600,7 +15726,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="373" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="373" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B373" s="3" t="s">
         <v>734</v>
       </c>
@@ -15622,7 +15748,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="374" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="374" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B374" s="3" t="s">
         <v>735</v>
       </c>
@@ -15644,7 +15770,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="375" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="375" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B375" s="3" t="s">
         <v>736</v>
       </c>
@@ -15666,7 +15792,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="376" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="376" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B376" s="3" t="s">
         <v>737</v>
       </c>
@@ -15688,7 +15814,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="377" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="377" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B377" s="3" t="s">
         <v>738</v>
       </c>
@@ -15710,7 +15836,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="378" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="378" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B378" s="3" t="s">
         <v>739</v>
       </c>
@@ -15732,7 +15858,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="379" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="379" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B379" s="3" t="s">
         <v>740</v>
       </c>
@@ -15754,7 +15880,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="380" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="380" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B380" s="3" t="s">
         <v>741</v>
       </c>
@@ -15776,7 +15902,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="381" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="381" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B381" s="3" t="s">
         <v>742</v>
       </c>
@@ -15798,7 +15924,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="382" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="382" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B382" s="3" t="s">
         <v>743</v>
       </c>
@@ -15820,7 +15946,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="383" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="383" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B383" s="3" t="s">
         <v>744</v>
       </c>
@@ -15842,7 +15968,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="384" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="384" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B384" s="3" t="s">
         <v>745</v>
       </c>
@@ -15864,7 +15990,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="385" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="385" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B385" s="3" t="s">
         <v>746</v>
       </c>
@@ -15886,7 +16012,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="386" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="386" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B386" s="3" t="s">
         <v>747</v>
       </c>
@@ -15908,7 +16034,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="387" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="387" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B387" s="3" t="s">
         <v>748</v>
       </c>
@@ -15930,7 +16056,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="388" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="388" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B388" s="3" t="s">
         <v>749</v>
       </c>
@@ -15952,7 +16078,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="389" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="389" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B389" s="3" t="s">
         <v>750</v>
       </c>
@@ -15974,7 +16100,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="390" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="390" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B390" s="3" t="s">
         <v>751</v>
       </c>
@@ -15996,7 +16122,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="391" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="391" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B391" s="3" t="s">
         <v>752</v>
       </c>
@@ -16018,7 +16144,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="392" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="392" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B392" s="3" t="s">
         <v>753</v>
       </c>
@@ -16040,7 +16166,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="393" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="393" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B393" s="3" t="s">
         <v>754</v>
       </c>
@@ -16062,7 +16188,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="394" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="394" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B394" s="3" t="s">
         <v>755</v>
       </c>
@@ -16084,7 +16210,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="395" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="395" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B395" s="3" t="s">
         <v>756</v>
       </c>
@@ -16106,7 +16232,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="396" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="396" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B396" s="3" t="s">
         <v>757</v>
       </c>
@@ -16128,7 +16254,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="397" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="397" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B397" s="3" t="s">
         <v>758</v>
       </c>
@@ -16150,7 +16276,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="398" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="398" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B398" s="3" t="s">
         <v>759</v>
       </c>
@@ -16172,7 +16298,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="399" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="399" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B399" s="3" t="s">
         <v>760</v>
       </c>
@@ -16194,7 +16320,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="400" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="400" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B400" s="3" t="s">
         <v>761</v>
       </c>
@@ -16216,7 +16342,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="401" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="401" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B401" s="3" t="s">
         <v>762</v>
       </c>
@@ -16232,7 +16358,7 @@
       <c r="I401" s="42"/>
       <c r="J401" s="42"/>
     </row>
-    <row r="402" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="402" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B402" s="3" t="s">
         <v>763</v>
       </c>
@@ -16248,7 +16374,7 @@
       <c r="I402" s="42"/>
       <c r="J402" s="42"/>
     </row>
-    <row r="403" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="403" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B403" s="3" t="s">
         <v>764</v>
       </c>
@@ -16264,7 +16390,7 @@
       <c r="I403" s="42"/>
       <c r="J403" s="42"/>
     </row>
-    <row r="404" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="404" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B404" s="3" t="s">
         <v>735</v>
       </c>
@@ -16294,7 +16420,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="405" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="405" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B405" s="3" t="s">
         <v>768</v>
       </c>
@@ -16324,7 +16450,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="406" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="406" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B406" s="3" t="s">
         <v>771</v>
       </c>
@@ -16354,7 +16480,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="407" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="407" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B407" s="3" t="s">
         <v>774</v>
       </c>
@@ -16384,7 +16510,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="408" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="408" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B408" s="3" t="s">
         <v>777</v>
       </c>
@@ -16414,7 +16540,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="409" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="409" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B409" s="3" t="s">
         <v>780</v>
       </c>
@@ -16444,7 +16570,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="410" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="410" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B410" s="3" t="s">
         <v>783</v>
       </c>
@@ -16474,7 +16600,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="411" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="411" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B411" s="3" t="s">
         <v>786</v>
       </c>
@@ -16504,7 +16630,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="412" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="412" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B412" s="3" t="s">
         <v>789</v>
       </c>
@@ -16534,7 +16660,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="413" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="413" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B413" s="3" t="s">
         <v>792</v>
       </c>
@@ -16564,7 +16690,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="414" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="414" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B414" s="3" t="s">
         <v>795</v>
       </c>
@@ -16594,7 +16720,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="415" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="415" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B415" s="3" t="s">
         <v>797</v>
       </c>
@@ -16624,7 +16750,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="416" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="416" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B416" s="3" t="s">
         <v>750</v>
       </c>
@@ -16654,7 +16780,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="417" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="417" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B417" s="3" t="s">
         <v>800</v>
       </c>
@@ -16684,7 +16810,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="418" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="418" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B418" s="3" t="s">
         <v>803</v>
       </c>
@@ -16714,7 +16840,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="419" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="419" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B419" s="3" t="s">
         <v>806</v>
       </c>
@@ -16744,7 +16870,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="420" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="420" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B420" s="3" t="s">
         <v>754</v>
       </c>
@@ -16774,7 +16900,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="421" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="421" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B421" s="3" t="s">
         <v>810</v>
       </c>
@@ -16804,7 +16930,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="422" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="422" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B422" s="3" t="s">
         <v>813</v>
       </c>
@@ -16834,7 +16960,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="423" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="423" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B423" s="3" t="s">
         <v>815</v>
       </c>
@@ -16864,7 +16990,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="424" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="424" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B424" s="3" t="s">
         <v>817</v>
       </c>
@@ -16894,7 +17020,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="425" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="425" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B425" s="3" t="s">
         <v>819</v>
       </c>
@@ -16924,7 +17050,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="426" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="426" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B426" s="3" t="s">
         <v>822</v>
       </c>
@@ -16954,7 +17080,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="427" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="427" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B427" s="3" t="s">
         <v>824</v>
       </c>
@@ -16984,7 +17110,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="428" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="428" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B428" s="3" t="s">
         <v>826</v>
       </c>
@@ -17014,7 +17140,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="429" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="429" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B429" s="3" t="s">
         <v>828</v>
       </c>
@@ -17044,7 +17170,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="430" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="430" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B430" s="3" t="s">
         <v>830</v>
       </c>
@@ -17074,7 +17200,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="431" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="431" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B431" s="3" t="s">
         <v>833</v>
       </c>
@@ -17104,7 +17230,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="432" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="432" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B432" s="3" t="s">
         <v>835</v>
       </c>
@@ -17134,7 +17260,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="433" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="433" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B433" s="3" t="s">
         <v>838</v>
       </c>
@@ -17164,7 +17290,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="434" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="434" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B434" s="3" t="s">
         <v>840</v>
       </c>
@@ -17194,7 +17320,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="435" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="435" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B435" s="3" t="s">
         <v>843</v>
       </c>
@@ -17224,7 +17350,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="436" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="436" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B436" s="3" t="s">
         <v>846</v>
       </c>
@@ -17254,7 +17380,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="437" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="437" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B437" s="3" t="s">
         <v>849</v>
       </c>
@@ -17284,7 +17410,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="438" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="438" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B438" s="3" t="s">
         <v>851</v>
       </c>
@@ -17314,7 +17440,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="439" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="439" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B439" s="3" t="s">
         <v>853</v>
       </c>
@@ -17344,7 +17470,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="440" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="440" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B440" s="3" t="s">
         <v>855</v>
       </c>
@@ -17374,7 +17500,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="441" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="441" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B441" s="3" t="s">
         <v>857</v>
       </c>
@@ -17404,7 +17530,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="442" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="442" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B442" s="3" t="s">
         <v>859</v>
       </c>
@@ -17434,7 +17560,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="443" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="443" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B443" s="3" t="s">
         <v>862</v>
       </c>
@@ -17464,7 +17590,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="444" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="444" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B444" s="3" t="s">
         <v>869</v>
       </c>
@@ -17491,7 +17617,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="445" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="445" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B445" s="3" t="s">
         <v>872</v>
       </c>
@@ -17513,7 +17639,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="446" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="446" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B446" s="3" t="s">
         <v>875</v>
       </c>
@@ -17541,7 +17667,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="447" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="447" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B447" s="3" t="s">
         <v>877</v>
       </c>
@@ -17566,7 +17692,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="448" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="448" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B448" s="3" t="s">
         <v>879</v>
       </c>
@@ -17591,2203 +17717,2203 @@
         <v>69</v>
       </c>
     </row>
-    <row r="449" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="449" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I449" s="42"/>
       <c r="J449" s="42"/>
     </row>
-    <row r="450" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="450" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I450" s="42"/>
       <c r="J450" s="42"/>
     </row>
-    <row r="451" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="451" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I451" s="42"/>
       <c r="J451" s="42"/>
     </row>
-    <row r="452" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="452" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I452" s="42"/>
       <c r="J452" s="42"/>
     </row>
-    <row r="453" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="453" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I453" s="42"/>
       <c r="J453" s="42"/>
     </row>
-    <row r="454" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="454" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I454" s="42"/>
       <c r="J454" s="42"/>
     </row>
-    <row r="455" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="455" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I455" s="42"/>
       <c r="J455" s="42"/>
     </row>
-    <row r="456" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="456" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I456" s="42"/>
       <c r="J456" s="42"/>
     </row>
-    <row r="457" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="457" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I457" s="42"/>
       <c r="J457" s="42"/>
     </row>
-    <row r="458" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="458" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I458" s="42"/>
       <c r="J458" s="42"/>
     </row>
-    <row r="459" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="459" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I459" s="42"/>
       <c r="J459" s="42"/>
     </row>
-    <row r="460" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="460" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I460" s="42"/>
       <c r="J460" s="42"/>
     </row>
-    <row r="461" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="461" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I461" s="42"/>
       <c r="J461" s="42"/>
     </row>
-    <row r="462" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="462" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I462" s="42"/>
       <c r="J462" s="42"/>
     </row>
-    <row r="463" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="463" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I463" s="42"/>
       <c r="J463" s="42"/>
     </row>
-    <row r="464" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="464" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I464" s="42"/>
       <c r="J464" s="42"/>
     </row>
-    <row r="465" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="465" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I465" s="42"/>
       <c r="J465" s="42"/>
     </row>
-    <row r="466" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="466" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I466" s="42"/>
       <c r="J466" s="42"/>
     </row>
-    <row r="467" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="467" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I467" s="42"/>
       <c r="J467" s="42"/>
     </row>
-    <row r="468" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="468" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I468" s="42"/>
       <c r="J468" s="42"/>
     </row>
-    <row r="469" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="469" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I469" s="42"/>
       <c r="J469" s="42"/>
     </row>
-    <row r="470" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="470" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I470" s="42"/>
       <c r="J470" s="42"/>
     </row>
-    <row r="471" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="471" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I471" s="42"/>
       <c r="J471" s="42"/>
     </row>
-    <row r="472" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="472" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I472" s="42"/>
       <c r="J472" s="42"/>
     </row>
-    <row r="473" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="473" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I473" s="42"/>
       <c r="J473" s="42"/>
     </row>
-    <row r="474" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="474" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I474" s="42"/>
       <c r="J474" s="42"/>
     </row>
-    <row r="475" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="475" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I475" s="42"/>
       <c r="J475" s="42"/>
     </row>
-    <row r="476" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="476" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I476" s="42"/>
       <c r="J476" s="42"/>
     </row>
-    <row r="477" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="477" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I477" s="42"/>
       <c r="J477" s="42"/>
     </row>
-    <row r="478" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="478" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I478" s="42"/>
       <c r="J478" s="42"/>
     </row>
-    <row r="479" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="479" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I479" s="42"/>
       <c r="J479" s="42"/>
     </row>
-    <row r="480" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="480" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I480" s="42"/>
       <c r="J480" s="42"/>
     </row>
-    <row r="481" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="481" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I481" s="42"/>
       <c r="J481" s="42"/>
     </row>
-    <row r="482" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="482" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I482" s="42"/>
       <c r="J482" s="42"/>
     </row>
-    <row r="483" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="483" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I483" s="42"/>
       <c r="J483" s="42"/>
     </row>
-    <row r="484" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="484" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I484" s="42"/>
       <c r="J484" s="42"/>
     </row>
-    <row r="485" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="485" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I485" s="42"/>
       <c r="J485" s="42"/>
     </row>
-    <row r="486" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="486" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I486" s="42"/>
       <c r="J486" s="42"/>
     </row>
-    <row r="487" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="487" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I487" s="42"/>
       <c r="J487" s="42"/>
     </row>
-    <row r="488" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="488" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I488" s="42"/>
       <c r="J488" s="42"/>
     </row>
-    <row r="489" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="489" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I489" s="42"/>
       <c r="J489" s="42"/>
     </row>
-    <row r="490" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="490" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I490" s="42"/>
       <c r="J490" s="42"/>
     </row>
-    <row r="491" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="491" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I491" s="42"/>
       <c r="J491" s="42"/>
     </row>
-    <row r="492" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="492" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I492" s="42"/>
       <c r="J492" s="42"/>
     </row>
-    <row r="493" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="493" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I493" s="42"/>
       <c r="J493" s="42"/>
     </row>
-    <row r="494" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="494" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I494" s="42"/>
       <c r="J494" s="42"/>
     </row>
-    <row r="495" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="495" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I495" s="42"/>
       <c r="J495" s="42"/>
     </row>
-    <row r="496" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="496" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I496" s="42"/>
       <c r="J496" s="42"/>
     </row>
-    <row r="497" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="497" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I497" s="42"/>
       <c r="J497" s="42"/>
     </row>
-    <row r="498" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="498" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I498" s="42"/>
       <c r="J498" s="42"/>
     </row>
-    <row r="499" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="499" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I499" s="42"/>
       <c r="J499" s="42"/>
     </row>
-    <row r="500" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="500" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I500" s="42"/>
       <c r="J500" s="42"/>
     </row>
-    <row r="501" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="501" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I501" s="42"/>
       <c r="J501" s="42"/>
     </row>
-    <row r="502" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="502" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I502" s="42"/>
       <c r="J502" s="42"/>
     </row>
-    <row r="503" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="503" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I503" s="42"/>
       <c r="J503" s="42"/>
     </row>
-    <row r="504" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="504" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I504" s="42"/>
       <c r="J504" s="42"/>
     </row>
-    <row r="505" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="505" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I505" s="42"/>
       <c r="J505" s="42"/>
     </row>
-    <row r="506" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="506" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I506" s="42"/>
       <c r="J506" s="42"/>
     </row>
-    <row r="507" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="507" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I507" s="42"/>
       <c r="J507" s="42"/>
     </row>
-    <row r="508" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="508" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I508" s="42"/>
       <c r="J508" s="42"/>
     </row>
-    <row r="509" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="509" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I509" s="42"/>
       <c r="J509" s="42"/>
     </row>
-    <row r="510" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="510" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I510" s="42"/>
       <c r="J510" s="42"/>
     </row>
-    <row r="511" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="511" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I511" s="42"/>
       <c r="J511" s="42"/>
     </row>
-    <row r="512" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="512" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I512" s="42"/>
       <c r="J512" s="42"/>
     </row>
-    <row r="513" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="513" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I513" s="42"/>
       <c r="J513" s="42"/>
     </row>
-    <row r="514" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="514" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I514" s="42"/>
       <c r="J514" s="42"/>
     </row>
-    <row r="515" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="515" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I515" s="42"/>
       <c r="J515" s="42"/>
     </row>
-    <row r="516" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="516" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I516" s="42"/>
       <c r="J516" s="42"/>
     </row>
-    <row r="517" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="517" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I517" s="42"/>
       <c r="J517" s="42"/>
     </row>
-    <row r="518" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="518" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I518" s="42"/>
       <c r="J518" s="42"/>
     </row>
-    <row r="519" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="519" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I519" s="42"/>
       <c r="J519" s="42"/>
     </row>
-    <row r="520" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="520" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I520" s="42"/>
       <c r="J520" s="42"/>
     </row>
-    <row r="521" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="521" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I521" s="42"/>
       <c r="J521" s="42"/>
     </row>
-    <row r="522" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="522" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I522" s="42"/>
       <c r="J522" s="42"/>
     </row>
-    <row r="523" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="523" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I523" s="42"/>
       <c r="J523" s="42"/>
     </row>
-    <row r="524" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="524" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I524" s="42"/>
       <c r="J524" s="42"/>
     </row>
-    <row r="525" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="525" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I525" s="42"/>
       <c r="J525" s="42"/>
     </row>
-    <row r="526" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="526" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I526" s="42"/>
       <c r="J526" s="42"/>
     </row>
-    <row r="527" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="527" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I527" s="42"/>
       <c r="J527" s="42"/>
     </row>
-    <row r="528" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="528" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I528" s="42"/>
       <c r="J528" s="42"/>
     </row>
-    <row r="529" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="529" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I529" s="42"/>
       <c r="J529" s="42"/>
     </row>
-    <row r="530" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="530" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I530" s="42"/>
       <c r="J530" s="42"/>
     </row>
-    <row r="531" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="531" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I531" s="42"/>
       <c r="J531" s="42"/>
     </row>
-    <row r="532" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="532" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I532" s="42"/>
       <c r="J532" s="42"/>
     </row>
-    <row r="533" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="533" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I533" s="42"/>
       <c r="J533" s="42"/>
     </row>
-    <row r="534" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="534" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I534" s="42"/>
       <c r="J534" s="42"/>
     </row>
-    <row r="535" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="535" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I535" s="42"/>
       <c r="J535" s="42"/>
     </row>
-    <row r="536" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="536" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I536" s="42"/>
       <c r="J536" s="42"/>
     </row>
-    <row r="537" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="537" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I537" s="42"/>
       <c r="J537" s="42"/>
     </row>
-    <row r="538" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="538" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I538" s="42"/>
       <c r="J538" s="42"/>
     </row>
-    <row r="539" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="539" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I539" s="42"/>
       <c r="J539" s="42"/>
     </row>
-    <row r="540" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="540" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I540" s="42"/>
       <c r="J540" s="42"/>
     </row>
-    <row r="541" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="541" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I541" s="42"/>
       <c r="J541" s="42"/>
     </row>
-    <row r="542" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="542" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I542" s="42"/>
       <c r="J542" s="42"/>
     </row>
-    <row r="543" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="543" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I543" s="42"/>
       <c r="J543" s="42"/>
     </row>
-    <row r="544" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="544" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I544" s="42"/>
       <c r="J544" s="42"/>
     </row>
-    <row r="545" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="545" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I545" s="42"/>
       <c r="J545" s="42"/>
     </row>
-    <row r="546" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="546" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I546" s="42"/>
       <c r="J546" s="42"/>
     </row>
-    <row r="547" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="547" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I547" s="42"/>
       <c r="J547" s="42"/>
     </row>
-    <row r="548" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="548" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I548" s="42"/>
       <c r="J548" s="42"/>
     </row>
-    <row r="549" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="549" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I549" s="42"/>
       <c r="J549" s="42"/>
     </row>
-    <row r="550" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="550" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I550" s="42"/>
       <c r="J550" s="42"/>
     </row>
-    <row r="551" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="551" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I551" s="42"/>
       <c r="J551" s="42"/>
     </row>
-    <row r="552" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="552" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I552" s="42"/>
       <c r="J552" s="42"/>
     </row>
-    <row r="553" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="553" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I553" s="42"/>
       <c r="J553" s="42"/>
     </row>
-    <row r="554" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="554" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I554" s="42"/>
       <c r="J554" s="42"/>
     </row>
-    <row r="555" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="555" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I555" s="42"/>
       <c r="J555" s="42"/>
     </row>
-    <row r="556" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="556" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I556" s="42"/>
       <c r="J556" s="42"/>
     </row>
-    <row r="557" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="557" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I557" s="42"/>
       <c r="J557" s="42"/>
     </row>
-    <row r="558" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="558" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I558" s="42"/>
       <c r="J558" s="42"/>
     </row>
-    <row r="559" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="559" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I559" s="42"/>
       <c r="J559" s="42"/>
     </row>
-    <row r="560" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="560" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I560" s="42"/>
       <c r="J560" s="42"/>
     </row>
-    <row r="561" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="561" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I561" s="42"/>
       <c r="J561" s="42"/>
     </row>
-    <row r="562" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="562" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I562" s="42"/>
       <c r="J562" s="42"/>
     </row>
-    <row r="563" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="563" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I563" s="42"/>
       <c r="J563" s="42"/>
     </row>
-    <row r="564" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="564" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I564" s="42"/>
       <c r="J564" s="42"/>
     </row>
-    <row r="565" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="565" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I565" s="42"/>
       <c r="J565" s="42"/>
     </row>
-    <row r="566" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="566" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I566" s="42"/>
       <c r="J566" s="42"/>
     </row>
-    <row r="567" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="567" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I567" s="42"/>
       <c r="J567" s="42"/>
     </row>
-    <row r="568" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="568" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I568" s="42"/>
       <c r="J568" s="42"/>
     </row>
-    <row r="569" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="569" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I569" s="42"/>
       <c r="J569" s="42"/>
     </row>
-    <row r="570" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="570" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I570" s="42"/>
       <c r="J570" s="42"/>
     </row>
-    <row r="571" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="571" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I571" s="42"/>
       <c r="J571" s="42"/>
     </row>
-    <row r="572" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="572" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I572" s="42"/>
       <c r="J572" s="42"/>
     </row>
-    <row r="573" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="573" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I573" s="42"/>
       <c r="J573" s="42"/>
     </row>
-    <row r="574" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="574" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I574" s="42"/>
       <c r="J574" s="42"/>
     </row>
-    <row r="575" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="575" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I575" s="42"/>
       <c r="J575" s="42"/>
     </row>
-    <row r="576" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="576" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I576" s="42"/>
       <c r="J576" s="42"/>
     </row>
-    <row r="577" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="577" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I577" s="42"/>
       <c r="J577" s="42"/>
     </row>
-    <row r="578" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="578" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I578" s="42"/>
       <c r="J578" s="42"/>
     </row>
-    <row r="579" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="579" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I579" s="42"/>
       <c r="J579" s="42"/>
     </row>
-    <row r="580" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="580" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I580" s="42"/>
       <c r="J580" s="42"/>
     </row>
-    <row r="581" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="581" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I581" s="42"/>
       <c r="J581" s="42"/>
     </row>
-    <row r="582" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="582" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I582" s="42"/>
       <c r="J582" s="42"/>
     </row>
-    <row r="583" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="583" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I583" s="42"/>
       <c r="J583" s="42"/>
     </row>
-    <row r="584" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="584" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I584" s="42"/>
       <c r="J584" s="42"/>
     </row>
-    <row r="585" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="585" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I585" s="42"/>
       <c r="J585" s="42"/>
     </row>
-    <row r="586" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="586" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I586" s="42"/>
       <c r="J586" s="42"/>
     </row>
-    <row r="587" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="587" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I587" s="42"/>
       <c r="J587" s="42"/>
     </row>
-    <row r="588" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="588" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I588" s="42"/>
       <c r="J588" s="42"/>
     </row>
-    <row r="589" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="589" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I589" s="42"/>
       <c r="J589" s="42"/>
     </row>
-    <row r="590" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="590" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I590" s="42"/>
       <c r="J590" s="42"/>
     </row>
-    <row r="591" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="591" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I591" s="42"/>
       <c r="J591" s="42"/>
     </row>
-    <row r="592" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="592" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I592" s="42"/>
       <c r="J592" s="42"/>
     </row>
-    <row r="593" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="593" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I593" s="42"/>
       <c r="J593" s="42"/>
     </row>
-    <row r="594" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="594" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I594" s="42"/>
       <c r="J594" s="42"/>
     </row>
-    <row r="595" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="595" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I595" s="42"/>
       <c r="J595" s="42"/>
     </row>
-    <row r="596" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="596" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I596" s="42"/>
       <c r="J596" s="42"/>
     </row>
-    <row r="597" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="597" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I597" s="42"/>
       <c r="J597" s="42"/>
     </row>
-    <row r="598" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="598" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I598" s="42"/>
       <c r="J598" s="42"/>
     </row>
-    <row r="599" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="599" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I599" s="42"/>
       <c r="J599" s="42"/>
     </row>
-    <row r="600" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="600" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I600" s="42"/>
       <c r="J600" s="42"/>
     </row>
-    <row r="601" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="601" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I601" s="42"/>
       <c r="J601" s="42"/>
     </row>
-    <row r="602" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="602" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I602" s="42"/>
       <c r="J602" s="42"/>
     </row>
-    <row r="603" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="603" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I603" s="42"/>
       <c r="J603" s="42"/>
     </row>
-    <row r="604" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="604" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I604" s="42"/>
       <c r="J604" s="42"/>
     </row>
-    <row r="605" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="605" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I605" s="42"/>
       <c r="J605" s="42"/>
     </row>
-    <row r="606" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="606" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I606" s="42"/>
       <c r="J606" s="42"/>
     </row>
-    <row r="607" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="607" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I607" s="42"/>
       <c r="J607" s="42"/>
     </row>
-    <row r="608" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="608" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I608" s="42"/>
       <c r="J608" s="42"/>
     </row>
-    <row r="609" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="609" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I609" s="42"/>
       <c r="J609" s="42"/>
     </row>
-    <row r="610" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="610" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I610" s="42"/>
       <c r="J610" s="42"/>
     </row>
-    <row r="611" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="611" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I611" s="42"/>
       <c r="J611" s="42"/>
     </row>
-    <row r="612" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="612" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I612" s="42"/>
       <c r="J612" s="42"/>
     </row>
-    <row r="613" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="613" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I613" s="42"/>
       <c r="J613" s="42"/>
     </row>
-    <row r="614" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="614" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I614" s="42"/>
       <c r="J614" s="42"/>
     </row>
-    <row r="615" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="615" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I615" s="42"/>
       <c r="J615" s="42"/>
     </row>
-    <row r="616" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="616" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I616" s="42"/>
       <c r="J616" s="42"/>
     </row>
-    <row r="617" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="617" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I617" s="42"/>
       <c r="J617" s="42"/>
     </row>
-    <row r="618" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="618" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I618" s="42"/>
       <c r="J618" s="42"/>
     </row>
-    <row r="619" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="619" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I619" s="42"/>
       <c r="J619" s="42"/>
     </row>
-    <row r="620" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="620" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I620" s="42"/>
       <c r="J620" s="42"/>
     </row>
-    <row r="621" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="621" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I621" s="42"/>
       <c r="J621" s="42"/>
     </row>
-    <row r="622" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="622" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I622" s="42"/>
       <c r="J622" s="42"/>
     </row>
-    <row r="623" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="623" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I623" s="42"/>
       <c r="J623" s="42"/>
     </row>
-    <row r="624" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="624" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I624" s="42"/>
       <c r="J624" s="42"/>
     </row>
-    <row r="625" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="625" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I625" s="42"/>
       <c r="J625" s="42"/>
     </row>
-    <row r="626" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="626" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I626" s="42"/>
       <c r="J626" s="42"/>
     </row>
-    <row r="627" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="627" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I627" s="42"/>
       <c r="J627" s="42"/>
     </row>
-    <row r="628" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="628" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I628" s="42"/>
       <c r="J628" s="42"/>
     </row>
-    <row r="629" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="629" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I629" s="42"/>
       <c r="J629" s="42"/>
     </row>
-    <row r="630" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="630" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I630" s="42"/>
       <c r="J630" s="42"/>
     </row>
-    <row r="631" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="631" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I631" s="42"/>
       <c r="J631" s="42"/>
     </row>
-    <row r="632" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="632" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I632" s="42"/>
       <c r="J632" s="42"/>
     </row>
-    <row r="633" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="633" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I633" s="42"/>
       <c r="J633" s="42"/>
     </row>
-    <row r="634" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="634" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I634" s="42"/>
       <c r="J634" s="42"/>
     </row>
-    <row r="635" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="635" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I635" s="42"/>
       <c r="J635" s="42"/>
     </row>
-    <row r="636" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="636" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I636" s="42"/>
       <c r="J636" s="42"/>
     </row>
-    <row r="637" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="637" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I637" s="42"/>
       <c r="J637" s="42"/>
     </row>
-    <row r="638" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="638" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I638" s="42"/>
       <c r="J638" s="42"/>
     </row>
-    <row r="639" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="639" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I639" s="42"/>
       <c r="J639" s="42"/>
     </row>
-    <row r="640" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="640" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I640" s="42"/>
       <c r="J640" s="42"/>
     </row>
-    <row r="641" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="641" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I641" s="42"/>
       <c r="J641" s="42"/>
     </row>
-    <row r="642" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="642" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I642" s="42"/>
       <c r="J642" s="42"/>
     </row>
-    <row r="643" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="643" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I643" s="42"/>
       <c r="J643" s="42"/>
     </row>
-    <row r="644" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="644" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I644" s="42"/>
       <c r="J644" s="42"/>
     </row>
-    <row r="645" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="645" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I645" s="42"/>
       <c r="J645" s="42"/>
     </row>
-    <row r="646" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="646" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I646" s="42"/>
       <c r="J646" s="42"/>
     </row>
-    <row r="647" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="647" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I647" s="42"/>
       <c r="J647" s="42"/>
     </row>
-    <row r="648" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="648" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I648" s="42"/>
       <c r="J648" s="42"/>
     </row>
-    <row r="649" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="649" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I649" s="42"/>
       <c r="J649" s="42"/>
     </row>
-    <row r="650" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="650" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I650" s="42"/>
       <c r="J650" s="42"/>
     </row>
-    <row r="651" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="651" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I651" s="42"/>
       <c r="J651" s="42"/>
     </row>
-    <row r="652" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="652" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I652" s="42"/>
       <c r="J652" s="42"/>
     </row>
-    <row r="653" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="653" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I653" s="42"/>
       <c r="J653" s="42"/>
     </row>
-    <row r="654" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="654" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I654" s="42"/>
       <c r="J654" s="42"/>
     </row>
-    <row r="655" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="655" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I655" s="42"/>
       <c r="J655" s="42"/>
     </row>
-    <row r="656" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="656" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I656" s="42"/>
       <c r="J656" s="42"/>
     </row>
-    <row r="657" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="657" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I657" s="42"/>
       <c r="J657" s="42"/>
     </row>
-    <row r="658" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="658" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I658" s="42"/>
       <c r="J658" s="42"/>
     </row>
-    <row r="659" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="659" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I659" s="42"/>
       <c r="J659" s="42"/>
     </row>
-    <row r="660" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="660" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I660" s="42"/>
       <c r="J660" s="42"/>
     </row>
-    <row r="661" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="661" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I661" s="42"/>
       <c r="J661" s="42"/>
     </row>
-    <row r="662" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="662" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I662" s="42"/>
       <c r="J662" s="42"/>
     </row>
-    <row r="663" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="663" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I663" s="42"/>
       <c r="J663" s="42"/>
     </row>
-    <row r="664" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="664" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I664" s="42"/>
       <c r="J664" s="42"/>
     </row>
-    <row r="665" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="665" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I665" s="42"/>
       <c r="J665" s="42"/>
     </row>
-    <row r="666" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="666" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I666" s="42"/>
       <c r="J666" s="42"/>
     </row>
-    <row r="667" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="667" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I667" s="42"/>
       <c r="J667" s="42"/>
     </row>
-    <row r="668" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="668" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I668" s="42"/>
       <c r="J668" s="42"/>
     </row>
-    <row r="669" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="669" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I669" s="42"/>
       <c r="J669" s="42"/>
     </row>
-    <row r="670" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="670" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I670" s="42"/>
       <c r="J670" s="42"/>
     </row>
-    <row r="671" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="671" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I671" s="42"/>
       <c r="J671" s="42"/>
     </row>
-    <row r="672" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="672" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I672" s="42"/>
       <c r="J672" s="42"/>
     </row>
-    <row r="673" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="673" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I673" s="42"/>
       <c r="J673" s="42"/>
     </row>
-    <row r="674" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="674" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I674" s="42"/>
       <c r="J674" s="42"/>
     </row>
-    <row r="675" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="675" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I675" s="42"/>
       <c r="J675" s="42"/>
     </row>
-    <row r="676" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="676" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I676" s="42"/>
       <c r="J676" s="42"/>
     </row>
-    <row r="677" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="677" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I677" s="42"/>
       <c r="J677" s="42"/>
     </row>
-    <row r="678" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="678" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I678" s="42"/>
       <c r="J678" s="42"/>
     </row>
-    <row r="679" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="679" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I679" s="42"/>
       <c r="J679" s="42"/>
     </row>
-    <row r="680" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="680" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I680" s="42"/>
       <c r="J680" s="42"/>
     </row>
-    <row r="681" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="681" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I681" s="42"/>
       <c r="J681" s="42"/>
     </row>
-    <row r="682" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="682" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I682" s="42"/>
       <c r="J682" s="42"/>
     </row>
-    <row r="683" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="683" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I683" s="42"/>
       <c r="J683" s="42"/>
     </row>
-    <row r="684" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="684" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I684" s="42"/>
       <c r="J684" s="42"/>
     </row>
-    <row r="685" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="685" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I685" s="42"/>
       <c r="J685" s="42"/>
     </row>
-    <row r="686" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="686" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I686" s="42"/>
       <c r="J686" s="42"/>
     </row>
-    <row r="687" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="687" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I687" s="42"/>
       <c r="J687" s="42"/>
     </row>
-    <row r="688" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="688" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I688" s="42"/>
       <c r="J688" s="42"/>
     </row>
-    <row r="689" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="689" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I689" s="42"/>
       <c r="J689" s="42"/>
     </row>
-    <row r="690" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="690" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I690" s="42"/>
       <c r="J690" s="42"/>
     </row>
-    <row r="691" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="691" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I691" s="42"/>
       <c r="J691" s="42"/>
     </row>
-    <row r="692" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="692" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I692" s="42"/>
       <c r="J692" s="42"/>
     </row>
-    <row r="693" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="693" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I693" s="42"/>
       <c r="J693" s="42"/>
     </row>
-    <row r="694" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="694" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I694" s="42"/>
       <c r="J694" s="42"/>
     </row>
-    <row r="695" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="695" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I695" s="42"/>
       <c r="J695" s="42"/>
     </row>
-    <row r="696" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="696" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I696" s="42"/>
       <c r="J696" s="42"/>
     </row>
-    <row r="697" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="697" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I697" s="42"/>
       <c r="J697" s="42"/>
     </row>
-    <row r="698" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="698" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I698" s="42"/>
       <c r="J698" s="42"/>
     </row>
-    <row r="699" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="699" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I699" s="42"/>
       <c r="J699" s="42"/>
     </row>
-    <row r="700" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="700" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I700" s="42"/>
       <c r="J700" s="42"/>
     </row>
-    <row r="701" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="701" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I701" s="42"/>
       <c r="J701" s="42"/>
     </row>
-    <row r="702" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="702" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I702" s="42"/>
       <c r="J702" s="42"/>
     </row>
-    <row r="703" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="703" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I703" s="42"/>
       <c r="J703" s="42"/>
     </row>
-    <row r="704" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="704" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I704" s="42"/>
       <c r="J704" s="42"/>
     </row>
-    <row r="705" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="705" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I705" s="42"/>
       <c r="J705" s="42"/>
     </row>
-    <row r="706" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="706" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I706" s="42"/>
       <c r="J706" s="42"/>
     </row>
-    <row r="707" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="707" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I707" s="42"/>
       <c r="J707" s="42"/>
     </row>
-    <row r="708" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="708" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I708" s="42"/>
       <c r="J708" s="42"/>
     </row>
-    <row r="709" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="709" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I709" s="42"/>
       <c r="J709" s="42"/>
     </row>
-    <row r="710" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="710" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I710" s="42"/>
       <c r="J710" s="42"/>
     </row>
-    <row r="711" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="711" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I711" s="42"/>
       <c r="J711" s="42"/>
     </row>
-    <row r="712" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="712" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I712" s="42"/>
       <c r="J712" s="42"/>
     </row>
-    <row r="713" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="713" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I713" s="42"/>
       <c r="J713" s="42"/>
     </row>
-    <row r="714" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="714" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I714" s="42"/>
       <c r="J714" s="42"/>
     </row>
-    <row r="715" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="715" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I715" s="42"/>
       <c r="J715" s="42"/>
     </row>
-    <row r="716" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="716" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I716" s="42"/>
       <c r="J716" s="42"/>
     </row>
-    <row r="717" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="717" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I717" s="42"/>
       <c r="J717" s="42"/>
     </row>
-    <row r="718" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="718" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I718" s="42"/>
       <c r="J718" s="42"/>
     </row>
-    <row r="719" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="719" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I719" s="42"/>
       <c r="J719" s="42"/>
     </row>
-    <row r="720" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="720" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I720" s="42"/>
       <c r="J720" s="42"/>
     </row>
-    <row r="721" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="721" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I721" s="42"/>
       <c r="J721" s="42"/>
     </row>
-    <row r="722" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="722" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I722" s="42"/>
       <c r="J722" s="42"/>
     </row>
-    <row r="723" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="723" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I723" s="42"/>
       <c r="J723" s="42"/>
     </row>
-    <row r="724" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="724" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I724" s="42"/>
       <c r="J724" s="42"/>
     </row>
-    <row r="725" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="725" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I725" s="42"/>
       <c r="J725" s="42"/>
     </row>
-    <row r="726" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="726" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I726" s="42"/>
       <c r="J726" s="42"/>
     </row>
-    <row r="727" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="727" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I727" s="42"/>
       <c r="J727" s="42"/>
     </row>
-    <row r="728" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="728" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I728" s="42"/>
       <c r="J728" s="42"/>
     </row>
-    <row r="729" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="729" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I729" s="42"/>
       <c r="J729" s="42"/>
     </row>
-    <row r="730" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="730" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I730" s="42"/>
       <c r="J730" s="42"/>
     </row>
-    <row r="731" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="731" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I731" s="42"/>
       <c r="J731" s="42"/>
     </row>
-    <row r="732" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="732" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I732" s="42"/>
       <c r="J732" s="42"/>
     </row>
-    <row r="733" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="733" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I733" s="42"/>
       <c r="J733" s="42"/>
     </row>
-    <row r="734" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="734" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I734" s="42"/>
       <c r="J734" s="42"/>
     </row>
-    <row r="735" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="735" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I735" s="42"/>
       <c r="J735" s="42"/>
     </row>
-    <row r="736" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="736" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I736" s="42"/>
       <c r="J736" s="42"/>
     </row>
-    <row r="737" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="737" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I737" s="42"/>
       <c r="J737" s="42"/>
     </row>
-    <row r="738" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="738" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I738" s="42"/>
       <c r="J738" s="42"/>
     </row>
-    <row r="739" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="739" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I739" s="42"/>
       <c r="J739" s="42"/>
     </row>
-    <row r="740" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="740" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I740" s="42"/>
       <c r="J740" s="42"/>
     </row>
-    <row r="741" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="741" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I741" s="42"/>
       <c r="J741" s="42"/>
     </row>
-    <row r="742" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="742" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I742" s="42"/>
       <c r="J742" s="42"/>
     </row>
-    <row r="743" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="743" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I743" s="42"/>
       <c r="J743" s="42"/>
     </row>
-    <row r="744" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="744" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I744" s="42"/>
       <c r="J744" s="42"/>
     </row>
-    <row r="745" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="745" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I745" s="42"/>
       <c r="J745" s="42"/>
     </row>
-    <row r="746" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="746" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I746" s="42"/>
       <c r="J746" s="42"/>
     </row>
-    <row r="747" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="747" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I747" s="42"/>
       <c r="J747" s="42"/>
     </row>
-    <row r="748" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="748" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I748" s="42"/>
       <c r="J748" s="42"/>
     </row>
-    <row r="749" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="749" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I749" s="42"/>
       <c r="J749" s="42"/>
     </row>
-    <row r="750" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="750" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I750" s="42"/>
       <c r="J750" s="42"/>
     </row>
-    <row r="751" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="751" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I751" s="42"/>
       <c r="J751" s="42"/>
     </row>
-    <row r="752" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="752" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I752" s="42"/>
       <c r="J752" s="42"/>
     </row>
-    <row r="753" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="753" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I753" s="42"/>
       <c r="J753" s="42"/>
     </row>
-    <row r="754" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="754" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I754" s="42"/>
       <c r="J754" s="42"/>
     </row>
-    <row r="755" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="755" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I755" s="42"/>
       <c r="J755" s="42"/>
     </row>
-    <row r="756" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="756" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I756" s="42"/>
       <c r="J756" s="42"/>
     </row>
-    <row r="757" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="757" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I757" s="42"/>
       <c r="J757" s="42"/>
     </row>
-    <row r="758" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="758" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I758" s="42"/>
       <c r="J758" s="42"/>
     </row>
-    <row r="759" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="759" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I759" s="42"/>
       <c r="J759" s="42"/>
     </row>
-    <row r="760" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="760" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I760" s="42"/>
       <c r="J760" s="42"/>
     </row>
-    <row r="761" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="761" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I761" s="42"/>
       <c r="J761" s="42"/>
     </row>
-    <row r="762" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="762" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I762" s="42"/>
       <c r="J762" s="42"/>
     </row>
-    <row r="763" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="763" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I763" s="42"/>
       <c r="J763" s="42"/>
     </row>
-    <row r="764" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="764" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I764" s="42"/>
       <c r="J764" s="42"/>
     </row>
-    <row r="765" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="765" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I765" s="42"/>
       <c r="J765" s="42"/>
     </row>
-    <row r="766" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="766" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I766" s="42"/>
       <c r="J766" s="42"/>
     </row>
-    <row r="767" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="767" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I767" s="42"/>
       <c r="J767" s="42"/>
     </row>
-    <row r="768" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="768" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I768" s="42"/>
       <c r="J768" s="42"/>
     </row>
-    <row r="769" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="769" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I769" s="42"/>
       <c r="J769" s="42"/>
     </row>
-    <row r="770" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="770" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I770" s="42"/>
       <c r="J770" s="42"/>
     </row>
-    <row r="771" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="771" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I771" s="42"/>
       <c r="J771" s="42"/>
     </row>
-    <row r="772" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="772" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I772" s="42"/>
       <c r="J772" s="42"/>
     </row>
-    <row r="773" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="773" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I773" s="42"/>
       <c r="J773" s="42"/>
     </row>
-    <row r="774" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="774" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I774" s="42"/>
       <c r="J774" s="42"/>
     </row>
-    <row r="775" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="775" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I775" s="42"/>
       <c r="J775" s="42"/>
     </row>
-    <row r="776" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="776" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I776" s="42"/>
       <c r="J776" s="42"/>
     </row>
-    <row r="777" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="777" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I777" s="42"/>
       <c r="J777" s="42"/>
     </row>
-    <row r="778" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="778" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I778" s="42"/>
       <c r="J778" s="42"/>
     </row>
-    <row r="779" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="779" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I779" s="42"/>
       <c r="J779" s="42"/>
     </row>
-    <row r="780" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="780" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I780" s="42"/>
       <c r="J780" s="42"/>
     </row>
-    <row r="781" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="781" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I781" s="42"/>
       <c r="J781" s="42"/>
     </row>
-    <row r="782" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="782" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I782" s="42"/>
       <c r="J782" s="42"/>
     </row>
-    <row r="783" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="783" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I783" s="42"/>
       <c r="J783" s="42"/>
     </row>
-    <row r="784" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="784" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I784" s="42"/>
       <c r="J784" s="42"/>
     </row>
-    <row r="785" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="785" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I785" s="42"/>
       <c r="J785" s="42"/>
     </row>
-    <row r="786" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="786" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I786" s="42"/>
       <c r="J786" s="42"/>
     </row>
-    <row r="787" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="787" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I787" s="42"/>
       <c r="J787" s="42"/>
     </row>
-    <row r="788" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="788" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I788" s="42"/>
       <c r="J788" s="42"/>
     </row>
-    <row r="789" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="789" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I789" s="42"/>
       <c r="J789" s="42"/>
     </row>
-    <row r="790" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="790" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I790" s="42"/>
       <c r="J790" s="42"/>
     </row>
-    <row r="791" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="791" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I791" s="42"/>
       <c r="J791" s="42"/>
     </row>
-    <row r="792" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="792" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I792" s="42"/>
       <c r="J792" s="42"/>
     </row>
-    <row r="793" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="793" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I793" s="42"/>
       <c r="J793" s="42"/>
     </row>
-    <row r="794" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="794" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I794" s="42"/>
       <c r="J794" s="42"/>
     </row>
-    <row r="795" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="795" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I795" s="42"/>
       <c r="J795" s="42"/>
     </row>
-    <row r="796" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="796" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I796" s="42"/>
       <c r="J796" s="42"/>
     </row>
-    <row r="797" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="797" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I797" s="42"/>
       <c r="J797" s="42"/>
     </row>
-    <row r="798" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="798" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I798" s="42"/>
       <c r="J798" s="42"/>
     </row>
-    <row r="799" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="799" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I799" s="42"/>
       <c r="J799" s="42"/>
     </row>
-    <row r="800" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="800" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I800" s="42"/>
       <c r="J800" s="42"/>
     </row>
-    <row r="801" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="801" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I801" s="42"/>
       <c r="J801" s="42"/>
     </row>
-    <row r="802" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="802" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I802" s="42"/>
       <c r="J802" s="42"/>
     </row>
-    <row r="803" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="803" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I803" s="42"/>
       <c r="J803" s="42"/>
     </row>
-    <row r="804" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="804" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I804" s="42"/>
       <c r="J804" s="42"/>
     </row>
-    <row r="805" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="805" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I805" s="42"/>
       <c r="J805" s="42"/>
     </row>
-    <row r="806" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="806" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I806" s="42"/>
       <c r="J806" s="42"/>
     </row>
-    <row r="807" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="807" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I807" s="42"/>
       <c r="J807" s="42"/>
     </row>
-    <row r="808" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="808" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I808" s="42"/>
       <c r="J808" s="42"/>
     </row>
-    <row r="809" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="809" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I809" s="42"/>
       <c r="J809" s="42"/>
     </row>
-    <row r="810" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="810" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I810" s="42"/>
       <c r="J810" s="42"/>
     </row>
-    <row r="811" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="811" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I811" s="42"/>
       <c r="J811" s="42"/>
     </row>
-    <row r="812" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="812" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I812" s="42"/>
       <c r="J812" s="42"/>
     </row>
-    <row r="813" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="813" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I813" s="42"/>
       <c r="J813" s="42"/>
     </row>
-    <row r="814" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="814" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I814" s="42"/>
       <c r="J814" s="42"/>
     </row>
-    <row r="815" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="815" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I815" s="42"/>
       <c r="J815" s="42"/>
     </row>
-    <row r="816" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="816" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I816" s="42"/>
       <c r="J816" s="42"/>
     </row>
-    <row r="817" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="817" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I817" s="42"/>
       <c r="J817" s="42"/>
     </row>
-    <row r="818" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="818" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I818" s="42"/>
       <c r="J818" s="42"/>
     </row>
-    <row r="819" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="819" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I819" s="42"/>
       <c r="J819" s="42"/>
     </row>
-    <row r="820" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="820" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I820" s="42"/>
       <c r="J820" s="42"/>
     </row>
-    <row r="821" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="821" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I821" s="42"/>
       <c r="J821" s="42"/>
     </row>
-    <row r="822" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="822" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I822" s="42"/>
       <c r="J822" s="42"/>
     </row>
-    <row r="823" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="823" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I823" s="42"/>
       <c r="J823" s="42"/>
     </row>
-    <row r="824" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="824" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I824" s="42"/>
       <c r="J824" s="42"/>
     </row>
-    <row r="825" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="825" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I825" s="42"/>
       <c r="J825" s="42"/>
     </row>
-    <row r="826" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="826" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I826" s="42"/>
       <c r="J826" s="42"/>
     </row>
-    <row r="827" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="827" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I827" s="42"/>
       <c r="J827" s="42"/>
     </row>
-    <row r="828" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="828" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I828" s="42"/>
       <c r="J828" s="42"/>
     </row>
-    <row r="829" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="829" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I829" s="42"/>
       <c r="J829" s="42"/>
     </row>
-    <row r="830" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="830" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I830" s="42"/>
       <c r="J830" s="42"/>
     </row>
-    <row r="831" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="831" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I831" s="42"/>
       <c r="J831" s="42"/>
     </row>
-    <row r="832" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="832" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I832" s="42"/>
       <c r="J832" s="42"/>
     </row>
-    <row r="833" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="833" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I833" s="42"/>
       <c r="J833" s="42"/>
     </row>
-    <row r="834" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="834" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I834" s="42"/>
       <c r="J834" s="42"/>
     </row>
-    <row r="835" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="835" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I835" s="42"/>
       <c r="J835" s="42"/>
     </row>
-    <row r="836" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="836" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I836" s="42"/>
       <c r="J836" s="42"/>
     </row>
-    <row r="837" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="837" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I837" s="42"/>
       <c r="J837" s="42"/>
     </row>
-    <row r="838" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="838" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I838" s="42"/>
       <c r="J838" s="42"/>
     </row>
-    <row r="839" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="839" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I839" s="42"/>
       <c r="J839" s="42"/>
     </row>
-    <row r="840" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="840" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I840" s="42"/>
       <c r="J840" s="42"/>
     </row>
-    <row r="841" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="841" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I841" s="42"/>
       <c r="J841" s="42"/>
     </row>
-    <row r="842" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="842" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I842" s="42"/>
       <c r="J842" s="42"/>
     </row>
-    <row r="843" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="843" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I843" s="42"/>
       <c r="J843" s="42"/>
     </row>
-    <row r="844" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="844" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I844" s="42"/>
       <c r="J844" s="42"/>
     </row>
-    <row r="845" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="845" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I845" s="42"/>
       <c r="J845" s="42"/>
     </row>
-    <row r="846" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="846" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I846" s="42"/>
       <c r="J846" s="42"/>
     </row>
-    <row r="847" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="847" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I847" s="42"/>
       <c r="J847" s="42"/>
     </row>
-    <row r="848" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="848" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I848" s="42"/>
       <c r="J848" s="42"/>
     </row>
-    <row r="849" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="849" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I849" s="42"/>
       <c r="J849" s="42"/>
     </row>
-    <row r="850" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="850" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I850" s="42"/>
       <c r="J850" s="42"/>
     </row>
-    <row r="851" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="851" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I851" s="42"/>
       <c r="J851" s="42"/>
     </row>
-    <row r="852" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="852" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I852" s="42"/>
       <c r="J852" s="42"/>
     </row>
-    <row r="853" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="853" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I853" s="42"/>
       <c r="J853" s="42"/>
     </row>
-    <row r="854" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="854" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I854" s="42"/>
       <c r="J854" s="42"/>
     </row>
-    <row r="855" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="855" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I855" s="42"/>
       <c r="J855" s="42"/>
     </row>
-    <row r="856" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="856" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I856" s="42"/>
       <c r="J856" s="42"/>
     </row>
-    <row r="857" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="857" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I857" s="42"/>
       <c r="J857" s="42"/>
     </row>
-    <row r="858" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="858" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I858" s="42"/>
       <c r="J858" s="42"/>
     </row>
-    <row r="859" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="859" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I859" s="42"/>
       <c r="J859" s="42"/>
     </row>
-    <row r="860" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="860" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I860" s="42"/>
       <c r="J860" s="42"/>
     </row>
-    <row r="861" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="861" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I861" s="42"/>
       <c r="J861" s="42"/>
     </row>
-    <row r="862" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="862" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I862" s="42"/>
       <c r="J862" s="42"/>
     </row>
-    <row r="863" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="863" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I863" s="42"/>
       <c r="J863" s="42"/>
     </row>
-    <row r="864" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="864" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I864" s="42"/>
       <c r="J864" s="42"/>
     </row>
-    <row r="865" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="865" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I865" s="42"/>
       <c r="J865" s="42"/>
     </row>
-    <row r="866" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="866" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I866" s="42"/>
       <c r="J866" s="42"/>
     </row>
-    <row r="867" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="867" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I867" s="42"/>
       <c r="J867" s="42"/>
     </row>
-    <row r="868" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="868" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I868" s="42"/>
       <c r="J868" s="42"/>
     </row>
-    <row r="869" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="869" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I869" s="42"/>
       <c r="J869" s="42"/>
     </row>
-    <row r="870" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="870" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I870" s="42"/>
       <c r="J870" s="42"/>
     </row>
-    <row r="871" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="871" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I871" s="42"/>
       <c r="J871" s="42"/>
     </row>
-    <row r="872" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="872" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I872" s="42"/>
       <c r="J872" s="42"/>
     </row>
-    <row r="873" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="873" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I873" s="42"/>
       <c r="J873" s="42"/>
     </row>
-    <row r="874" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="874" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I874" s="42"/>
       <c r="J874" s="42"/>
     </row>
-    <row r="875" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="875" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I875" s="42"/>
       <c r="J875" s="42"/>
     </row>
-    <row r="876" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="876" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I876" s="42"/>
       <c r="J876" s="42"/>
     </row>
-    <row r="877" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="877" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I877" s="42"/>
       <c r="J877" s="42"/>
     </row>
-    <row r="878" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="878" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I878" s="42"/>
       <c r="J878" s="42"/>
     </row>
-    <row r="879" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="879" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I879" s="42"/>
       <c r="J879" s="42"/>
     </row>
-    <row r="880" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="880" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I880" s="42"/>
       <c r="J880" s="42"/>
     </row>
-    <row r="881" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="881" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I881" s="42"/>
       <c r="J881" s="42"/>
     </row>
-    <row r="882" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="882" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I882" s="42"/>
       <c r="J882" s="42"/>
     </row>
-    <row r="883" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="883" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I883" s="42"/>
       <c r="J883" s="42"/>
     </row>
-    <row r="884" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="884" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I884" s="42"/>
       <c r="J884" s="42"/>
     </row>
-    <row r="885" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="885" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I885" s="42"/>
       <c r="J885" s="42"/>
     </row>
-    <row r="886" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="886" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I886" s="42"/>
       <c r="J886" s="42"/>
     </row>
-    <row r="887" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="887" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I887" s="42"/>
       <c r="J887" s="42"/>
     </row>
-    <row r="888" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="888" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I888" s="42"/>
       <c r="J888" s="42"/>
     </row>
-    <row r="889" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="889" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I889" s="42"/>
       <c r="J889" s="42"/>
     </row>
-    <row r="890" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="890" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I890" s="42"/>
       <c r="J890" s="42"/>
     </row>
-    <row r="891" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="891" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I891" s="42"/>
       <c r="J891" s="42"/>
     </row>
-    <row r="892" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="892" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I892" s="42"/>
       <c r="J892" s="42"/>
     </row>
-    <row r="893" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="893" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I893" s="42"/>
       <c r="J893" s="42"/>
     </row>
-    <row r="894" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="894" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I894" s="42"/>
       <c r="J894" s="42"/>
     </row>
-    <row r="895" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="895" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I895" s="42"/>
       <c r="J895" s="42"/>
     </row>
-    <row r="896" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="896" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I896" s="42"/>
       <c r="J896" s="42"/>
     </row>
-    <row r="897" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="897" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I897" s="42"/>
       <c r="J897" s="42"/>
     </row>
-    <row r="898" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="898" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I898" s="42"/>
       <c r="J898" s="42"/>
     </row>
-    <row r="899" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="899" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I899" s="42"/>
       <c r="J899" s="42"/>
     </row>
-    <row r="900" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="900" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I900" s="42"/>
       <c r="J900" s="42"/>
     </row>
-    <row r="901" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="901" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I901" s="42"/>
       <c r="J901" s="42"/>
     </row>
-    <row r="902" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="902" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I902" s="42"/>
       <c r="J902" s="42"/>
     </row>
-    <row r="903" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="903" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I903" s="42"/>
       <c r="J903" s="42"/>
     </row>
-    <row r="904" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="904" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I904" s="42"/>
       <c r="J904" s="42"/>
     </row>
-    <row r="905" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="905" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I905" s="42"/>
       <c r="J905" s="42"/>
     </row>
-    <row r="906" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="906" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I906" s="42"/>
       <c r="J906" s="42"/>
     </row>
-    <row r="907" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="907" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I907" s="42"/>
       <c r="J907" s="42"/>
     </row>
-    <row r="908" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="908" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I908" s="42"/>
       <c r="J908" s="42"/>
     </row>
-    <row r="909" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="909" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I909" s="42"/>
       <c r="J909" s="42"/>
     </row>
-    <row r="910" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="910" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I910" s="42"/>
       <c r="J910" s="42"/>
     </row>
-    <row r="911" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="911" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I911" s="42"/>
       <c r="J911" s="42"/>
     </row>
-    <row r="912" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="912" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I912" s="42"/>
       <c r="J912" s="42"/>
     </row>
-    <row r="913" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="913" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I913" s="42"/>
       <c r="J913" s="42"/>
     </row>
-    <row r="914" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="914" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I914" s="42"/>
       <c r="J914" s="42"/>
     </row>
-    <row r="915" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="915" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I915" s="42"/>
       <c r="J915" s="42"/>
     </row>
-    <row r="916" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="916" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I916" s="42"/>
       <c r="J916" s="42"/>
     </row>
-    <row r="917" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="917" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I917" s="42"/>
       <c r="J917" s="42"/>
     </row>
-    <row r="918" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="918" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I918" s="42"/>
       <c r="J918" s="42"/>
     </row>
-    <row r="919" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="919" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I919" s="42"/>
       <c r="J919" s="42"/>
     </row>
-    <row r="920" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="920" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I920" s="42"/>
       <c r="J920" s="42"/>
     </row>
-    <row r="921" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="921" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I921" s="42"/>
       <c r="J921" s="42"/>
     </row>
-    <row r="922" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="922" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I922" s="42"/>
       <c r="J922" s="42"/>
     </row>
-    <row r="923" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="923" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I923" s="42"/>
       <c r="J923" s="42"/>
     </row>
-    <row r="924" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="924" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I924" s="42"/>
       <c r="J924" s="42"/>
     </row>
-    <row r="925" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="925" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I925" s="42"/>
       <c r="J925" s="42"/>
     </row>
-    <row r="926" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="926" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I926" s="42"/>
       <c r="J926" s="42"/>
     </row>
-    <row r="927" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="927" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I927" s="42"/>
       <c r="J927" s="42"/>
     </row>
-    <row r="928" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="928" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I928" s="42"/>
       <c r="J928" s="42"/>
     </row>
-    <row r="929" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="929" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I929" s="42"/>
       <c r="J929" s="42"/>
     </row>
-    <row r="930" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="930" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I930" s="42"/>
       <c r="J930" s="42"/>
     </row>
-    <row r="931" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="931" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I931" s="42"/>
       <c r="J931" s="42"/>
     </row>
-    <row r="932" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="932" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I932" s="42"/>
       <c r="J932" s="42"/>
     </row>
-    <row r="933" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="933" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I933" s="42"/>
       <c r="J933" s="42"/>
     </row>
-    <row r="934" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="934" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I934" s="42"/>
       <c r="J934" s="42"/>
     </row>
-    <row r="935" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="935" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I935" s="42"/>
       <c r="J935" s="42"/>
     </row>
-    <row r="936" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="936" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I936" s="42"/>
       <c r="J936" s="42"/>
     </row>
-    <row r="937" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="937" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I937" s="42"/>
       <c r="J937" s="42"/>
     </row>
-    <row r="938" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="938" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I938" s="42"/>
       <c r="J938" s="42"/>
     </row>
-    <row r="939" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="939" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I939" s="42"/>
       <c r="J939" s="42"/>
     </row>
-    <row r="940" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="940" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I940" s="42"/>
       <c r="J940" s="42"/>
     </row>
-    <row r="941" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="941" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I941" s="42"/>
       <c r="J941" s="42"/>
     </row>
-    <row r="942" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="942" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I942" s="42"/>
       <c r="J942" s="42"/>
     </row>
-    <row r="943" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="943" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I943" s="42"/>
       <c r="J943" s="42"/>
     </row>
-    <row r="944" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="944" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I944" s="42"/>
       <c r="J944" s="42"/>
     </row>
-    <row r="945" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="945" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I945" s="42"/>
       <c r="J945" s="42"/>
     </row>
-    <row r="946" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="946" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I946" s="42"/>
       <c r="J946" s="42"/>
     </row>
-    <row r="947" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="947" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I947" s="42"/>
       <c r="J947" s="42"/>
     </row>
-    <row r="948" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="948" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I948" s="42"/>
       <c r="J948" s="42"/>
     </row>
-    <row r="949" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="949" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I949" s="42"/>
       <c r="J949" s="42"/>
     </row>
-    <row r="950" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="950" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I950" s="42"/>
       <c r="J950" s="42"/>
     </row>
-    <row r="951" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="951" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I951" s="42"/>
       <c r="J951" s="42"/>
     </row>
-    <row r="952" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="952" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I952" s="42"/>
       <c r="J952" s="42"/>
     </row>
-    <row r="953" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="953" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I953" s="42"/>
       <c r="J953" s="42"/>
     </row>
-    <row r="954" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="954" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I954" s="42"/>
       <c r="J954" s="42"/>
     </row>
-    <row r="955" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="955" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I955" s="42"/>
       <c r="J955" s="42"/>
     </row>
-    <row r="956" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="956" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I956" s="42"/>
       <c r="J956" s="42"/>
     </row>
-    <row r="957" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="957" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I957" s="42"/>
       <c r="J957" s="42"/>
     </row>
-    <row r="958" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="958" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I958" s="42"/>
       <c r="J958" s="42"/>
     </row>
-    <row r="959" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="959" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I959" s="42"/>
       <c r="J959" s="42"/>
     </row>
-    <row r="960" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="960" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I960" s="42"/>
       <c r="J960" s="42"/>
     </row>
-    <row r="961" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="961" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I961" s="42"/>
       <c r="J961" s="42"/>
     </row>
-    <row r="962" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="962" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I962" s="42"/>
       <c r="J962" s="42"/>
     </row>
-    <row r="963" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="963" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I963" s="42"/>
       <c r="J963" s="42"/>
     </row>
-    <row r="964" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="964" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I964" s="42"/>
       <c r="J964" s="42"/>
     </row>
-    <row r="965" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="965" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I965" s="42"/>
       <c r="J965" s="42"/>
     </row>
-    <row r="966" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="966" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I966" s="42"/>
       <c r="J966" s="42"/>
     </row>
-    <row r="967" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="967" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I967" s="42"/>
       <c r="J967" s="42"/>
     </row>
-    <row r="968" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="968" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I968" s="42"/>
       <c r="J968" s="42"/>
     </row>
-    <row r="969" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="969" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I969" s="42"/>
       <c r="J969" s="42"/>
     </row>
-    <row r="970" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="970" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I970" s="42"/>
       <c r="J970" s="42"/>
     </row>
-    <row r="971" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="971" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I971" s="42"/>
       <c r="J971" s="42"/>
     </row>
-    <row r="972" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="972" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I972" s="42"/>
       <c r="J972" s="42"/>
     </row>
-    <row r="973" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="973" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I973" s="42"/>
       <c r="J973" s="42"/>
     </row>
-    <row r="974" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="974" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I974" s="42"/>
       <c r="J974" s="42"/>
     </row>
-    <row r="975" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="975" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I975" s="42"/>
       <c r="J975" s="42"/>
     </row>
-    <row r="976" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="976" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I976" s="42"/>
       <c r="J976" s="42"/>
     </row>
-    <row r="977" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="977" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I977" s="42"/>
       <c r="J977" s="42"/>
     </row>
-    <row r="978" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="978" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I978" s="42"/>
       <c r="J978" s="42"/>
     </row>
-    <row r="979" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="979" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I979" s="42"/>
       <c r="J979" s="42"/>
     </row>
-    <row r="980" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="980" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I980" s="42"/>
       <c r="J980" s="42"/>
     </row>
-    <row r="981" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="981" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I981" s="42"/>
       <c r="J981" s="42"/>
     </row>
-    <row r="982" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="982" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I982" s="42"/>
       <c r="J982" s="42"/>
     </row>
-    <row r="983" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="983" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I983" s="42"/>
       <c r="J983" s="42"/>
     </row>
-    <row r="984" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="984" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I984" s="42"/>
       <c r="J984" s="42"/>
     </row>
-    <row r="985" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="985" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I985" s="42"/>
       <c r="J985" s="42"/>
     </row>
-    <row r="986" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="986" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I986" s="42"/>
       <c r="J986" s="42"/>
     </row>
-    <row r="987" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="987" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I987" s="42"/>
       <c r="J987" s="42"/>
     </row>
-    <row r="988" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="988" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I988" s="42"/>
       <c r="J988" s="42"/>
     </row>
-    <row r="989" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="989" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I989" s="42"/>
       <c r="J989" s="42"/>
     </row>
-    <row r="990" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="990" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I990" s="42"/>
       <c r="J990" s="42"/>
     </row>
-    <row r="991" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="991" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I991" s="42"/>
       <c r="J991" s="42"/>
     </row>
-    <row r="992" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="992" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I992" s="42"/>
       <c r="J992" s="42"/>
     </row>
-    <row r="993" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="993" spans="1:13" x14ac:dyDescent="0.25">
       <c r="I993" s="42"/>
       <c r="J993" s="42"/>
     </row>
-    <row r="994" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="994" spans="1:13" x14ac:dyDescent="0.25">
       <c r="I994" s="42"/>
       <c r="J994" s="42"/>
     </row>
-    <row r="995" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="995" spans="1:13" x14ac:dyDescent="0.25">
       <c r="I995" s="42"/>
       <c r="J995" s="42"/>
     </row>
-    <row r="996" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="996" spans="1:13" x14ac:dyDescent="0.25">
       <c r="I996" s="42"/>
       <c r="J996" s="42"/>
     </row>
-    <row r="997" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="997" spans="1:13" x14ac:dyDescent="0.25">
       <c r="I997" s="42"/>
       <c r="J997" s="42"/>
     </row>
-    <row r="998" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="998" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A998">
         <v>467</v>
       </c>
@@ -19822,7 +19948,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="999" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="999" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A999">
         <v>468</v>
       </c>
@@ -19857,7 +19983,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1000" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1000" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A1000">
         <v>469</v>
       </c>
@@ -19892,7 +20018,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1001" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1001" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A1001">
         <v>470</v>
       </c>
@@ -19927,7 +20053,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1002" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1002" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A1002">
         <v>471</v>
       </c>
@@ -19962,7 +20088,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1003" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1003" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A1003">
         <v>472</v>
       </c>
@@ -19997,7 +20123,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1004" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1004" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1004">
         <v>473</v>
       </c>
@@ -20032,7 +20158,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1005" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1005" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A1005">
         <v>474</v>
       </c>
@@ -20067,7 +20193,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1006" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1006" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A1006">
         <v>475</v>
       </c>
@@ -20099,7 +20225,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1007" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1007" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A1007">
         <v>476</v>
       </c>
@@ -20131,7 +20257,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1008" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1008" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1008">
         <v>477</v>
       </c>
@@ -20163,7 +20289,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1009" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1009" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A1009">
         <v>478</v>
       </c>
@@ -20195,7 +20321,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1010" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1010" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A1010">
         <v>479</v>
       </c>
@@ -20227,7 +20353,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1011" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1011" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A1011">
         <v>480</v>
       </c>
@@ -20259,7 +20385,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1012" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1012" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A1012">
         <v>481</v>
       </c>
@@ -20291,7 +20417,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1013" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1013" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1013">
         <v>482</v>
       </c>
@@ -20323,7 +20449,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1014" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1014" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A1014">
         <v>483</v>
       </c>
@@ -20355,7 +20481,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1015" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1015" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1015">
         <v>484</v>
       </c>
@@ -20387,7 +20513,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1016" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1016" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A1016">
         <v>485</v>
       </c>
@@ -20419,7 +20545,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1017" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1017" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A1017">
         <v>486</v>
       </c>
@@ -20451,7 +20577,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1018" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1018" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A1018">
         <v>487</v>
       </c>
@@ -20483,7 +20609,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1019" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1019" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A1019">
         <v>488</v>
       </c>
@@ -20515,7 +20641,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1020" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1020" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A1020">
         <v>489</v>
       </c>
@@ -20547,7 +20673,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1021" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1021" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1021">
         <v>490</v>
       </c>
@@ -20579,7 +20705,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1022" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1022" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A1022">
         <v>491</v>
       </c>
@@ -20611,7 +20737,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1023" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1023" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1023">
         <v>492</v>
       </c>
@@ -20643,7 +20769,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1024" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1024" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1024">
         <v>493</v>
       </c>
@@ -20675,7 +20801,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1025" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1025" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1025">
         <v>494</v>
       </c>
@@ -20707,7 +20833,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1026" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1026" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1026">
         <v>495</v>
       </c>
@@ -20739,7 +20865,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1027" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1027" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1027">
         <v>496</v>
       </c>
@@ -20771,7 +20897,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1028" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1028" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1028">
         <v>497</v>
       </c>
@@ -20803,7 +20929,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1029" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1029" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1029">
         <v>498</v>
       </c>
@@ -20835,7 +20961,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1030" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1030" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1030">
         <v>499</v>
       </c>
@@ -20867,7 +20993,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1031" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1031" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1031">
         <v>500</v>
       </c>
@@ -20899,7 +21025,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1032" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1032" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1032">
         <v>501</v>
       </c>
@@ -20931,7 +21057,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1033" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1033" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1033">
         <v>502</v>
       </c>
@@ -20963,7 +21089,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1034" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1034" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1034">
         <v>503</v>
       </c>
@@ -20995,7 +21121,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1035" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1035" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1035">
         <v>504</v>
       </c>
@@ -21027,7 +21153,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1036" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1036" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1036">
         <v>505</v>
       </c>
@@ -21059,7 +21185,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1037" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1037" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1037">
         <v>506</v>
       </c>
@@ -21091,7 +21217,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1038" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1038" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1038">
         <v>507</v>
       </c>
@@ -21123,7 +21249,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1039" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1039" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1039">
         <v>508</v>
       </c>
@@ -21155,7 +21281,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1040" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1040" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1040">
         <v>509</v>
       </c>
@@ -21187,7 +21313,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1041" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1041" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1041">
         <v>510</v>
       </c>
@@ -21219,7 +21345,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1042" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1042" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1042">
         <v>511</v>
       </c>
@@ -21251,7 +21377,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1043" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1043" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1043">
         <v>512</v>
       </c>
@@ -21283,7 +21409,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1044" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1044" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1044">
         <v>513</v>
       </c>
@@ -21315,7 +21441,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1045" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1045" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1045">
         <v>514</v>
       </c>
@@ -21347,7 +21473,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1046" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1046" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1046">
         <v>515</v>
       </c>
@@ -21379,7 +21505,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1047" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1047" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1047">
         <v>516</v>
       </c>
@@ -21411,7 +21537,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1048" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1048" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1048">
         <v>517</v>
       </c>
@@ -21443,7 +21569,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1049" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1049" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1049">
         <v>518</v>
       </c>
@@ -21475,7 +21601,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1050" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1050" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1050">
         <v>519</v>
       </c>
@@ -21507,7 +21633,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1051" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1051" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1051">
         <v>520</v>
       </c>
@@ -21539,7 +21665,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1052" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1052" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A1052">
         <v>521</v>
       </c>
@@ -21571,7 +21697,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1053" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1053" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A1053">
         <v>522</v>
       </c>
@@ -21603,7 +21729,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1054" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1054" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1054">
         <v>523</v>
       </c>
@@ -21635,7 +21761,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="1055" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1055" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1055">
         <v>524</v>
       </c>
@@ -21661,7 +21787,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="1056" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1056" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1056">
         <v>525</v>
       </c>
@@ -21687,7 +21813,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="1057" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1057" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1057">
         <v>526</v>
       </c>
@@ -21713,7 +21839,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="1058" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1058" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1058">
         <v>527</v>
       </c>
@@ -21739,7 +21865,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="1059" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1059" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1059">
         <v>528</v>
       </c>
@@ -21765,7 +21891,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="1060" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1060" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1060">
         <v>529</v>
       </c>
@@ -21791,7 +21917,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="1061" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1061" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1061">
         <v>530</v>
       </c>
@@ -21817,7 +21943,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="1062" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1062" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1062">
         <v>531</v>
       </c>
@@ -21843,7 +21969,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="1063" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1063" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1063">
         <v>532</v>
       </c>
@@ -21869,7 +21995,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="1064" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1064" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1064">
         <v>533</v>
       </c>
@@ -21895,7 +22021,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="1065" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1065" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1065">
         <v>534</v>
       </c>
@@ -21921,7 +22047,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="1066" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1066" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1066">
         <v>535</v>
       </c>
@@ -21947,7 +22073,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="1067" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1067" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1067">
         <v>536</v>
       </c>
@@ -21973,7 +22099,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="1068" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1068" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1068">
         <v>537</v>
       </c>
@@ -21999,7 +22125,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="1069" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1069" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1069">
         <v>538</v>
       </c>
@@ -22025,7 +22151,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="1070" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1070" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1070">
         <v>539</v>
       </c>
@@ -22051,7 +22177,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="1071" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1071" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1071">
         <v>540</v>
       </c>
@@ -22077,7 +22203,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="1072" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1072" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1072">
         <v>541</v>
       </c>
@@ -22103,7 +22229,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="1073" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1073" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1073">
         <v>542</v>
       </c>
@@ -22129,7 +22255,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="1074" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1074" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1074">
         <v>543</v>
       </c>
@@ -22155,7 +22281,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="1075" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1075" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1075">
         <v>544</v>
       </c>
@@ -22181,7 +22307,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="1076" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1076" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1076">
         <v>545</v>
       </c>
@@ -22204,7 +22330,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="1077" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1077" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1077">
         <v>546</v>
       </c>
@@ -22227,7 +22353,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="1078" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1078" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1078">
         <v>547</v>
       </c>
@@ -22256,7 +22382,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1079" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1079" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1079">
         <v>548</v>
       </c>
@@ -22285,7 +22411,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1080" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1080" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1080">
         <v>549</v>
       </c>
@@ -22314,7 +22440,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1081" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1081" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1081">
         <v>550</v>
       </c>
@@ -22343,7 +22469,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1082" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1082" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1082">
         <v>551</v>
       </c>
@@ -22372,7 +22498,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1083" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1083" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1083">
         <v>552</v>
       </c>
@@ -22401,7 +22527,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1084" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1084" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1084">
         <v>553</v>
       </c>
@@ -22430,7 +22556,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1085" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1085" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1085">
         <v>554</v>
       </c>
@@ -22459,7 +22585,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1086" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1086" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1086">
         <v>555</v>
       </c>
@@ -22488,7 +22614,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1087" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1087" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1087">
         <v>556</v>
       </c>
@@ -22517,7 +22643,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1088" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1088" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1088">
         <v>557</v>
       </c>
@@ -22546,7 +22672,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1089" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1089" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1089">
         <v>558</v>
       </c>
@@ -22575,7 +22701,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1090" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1090" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1090">
         <v>559</v>
       </c>
@@ -22604,7 +22730,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1091" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1091" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1091">
         <v>560</v>
       </c>
@@ -22633,7 +22759,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1092" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1092" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1092">
         <v>561</v>
       </c>
@@ -22662,7 +22788,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1093" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1093" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1093">
         <v>562</v>
       </c>
@@ -22691,7 +22817,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1094" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1094" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1094">
         <v>563</v>
       </c>
@@ -22720,7 +22846,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1095" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1095" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1095">
         <v>564</v>
       </c>
@@ -22749,7 +22875,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1096" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1096" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1096">
         <v>565</v>
       </c>
@@ -22778,7 +22904,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1097" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1097" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1097">
         <v>566</v>
       </c>
@@ -22807,7 +22933,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1098" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1098" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1098">
         <v>567</v>
       </c>
@@ -22836,7 +22962,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1099" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1099" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1099">
         <v>568</v>
       </c>
@@ -22865,7 +22991,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1100" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1100" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1100">
         <v>569</v>
       </c>
@@ -22894,7 +23020,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1101" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1101" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1101">
         <v>570</v>
       </c>
@@ -22923,7 +23049,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1102" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1102" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1102">
         <v>571</v>
       </c>
@@ -22952,7 +23078,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1103" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1103" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1103">
         <v>572</v>
       </c>
@@ -22981,7 +23107,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1104" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1104" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1104">
         <v>573</v>
       </c>
@@ -23010,7 +23136,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1105" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1105" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1105">
         <v>574</v>
       </c>
@@ -23039,7 +23165,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1106" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1106" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1106">
         <v>575</v>
       </c>
@@ -23068,7 +23194,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1107" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1107" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1107">
         <v>576</v>
       </c>
@@ -23097,7 +23223,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1108" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1108" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1108">
         <v>577</v>
       </c>
@@ -23126,7 +23252,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1109" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1109" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1109">
         <v>578</v>
       </c>
@@ -23155,7 +23281,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1110" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1110" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1110">
         <v>579</v>
       </c>
@@ -23184,7 +23310,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1111" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1111" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1111">
         <v>580</v>
       </c>
@@ -23213,7 +23339,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1112" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1112" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1112">
         <v>581</v>
       </c>
@@ -23242,7 +23368,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1113" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1113" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1113">
         <v>582</v>
       </c>
@@ -23271,7 +23397,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1114" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1114" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1114">
         <v>583</v>
       </c>
@@ -23300,7 +23426,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1115" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1115" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1115">
         <v>584</v>
       </c>
@@ -23329,7 +23455,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1116" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1116" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1116">
         <v>585</v>
       </c>
@@ -23358,7 +23484,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1117" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1117" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1117">
         <v>586</v>
       </c>
@@ -23387,7 +23513,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1118" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1118" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1118">
         <v>587</v>
       </c>
@@ -23416,7 +23542,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1119" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1119" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1119">
         <v>588</v>
       </c>
@@ -23445,7 +23571,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1120" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1120" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1120">
         <v>589</v>
       </c>
@@ -23474,7 +23600,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1121" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1121" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1121">
         <v>590</v>
       </c>
@@ -23503,7 +23629,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1122" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1122" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1122">
         <v>591</v>
       </c>
@@ -23532,7 +23658,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1123" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1123" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1123">
         <v>592</v>
       </c>
@@ -23561,7 +23687,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1124" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1124" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1124">
         <v>593</v>
       </c>
@@ -23587,7 +23713,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1125" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1125" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1125">
         <v>594</v>
       </c>
@@ -23613,7 +23739,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1126" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1126" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1126">
         <v>595</v>
       </c>
@@ -23642,7 +23768,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1127" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1127" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1127">
         <v>596</v>
       </c>
@@ -23671,7 +23797,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1128" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1128" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1128">
         <v>597</v>
       </c>
@@ -23700,7 +23826,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1129" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1129" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1129">
         <v>598</v>
       </c>
@@ -23729,7 +23855,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1130" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1130" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1130">
         <v>599</v>
       </c>
@@ -23758,7 +23884,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1131" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1131" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1131">
         <v>600</v>
       </c>
@@ -23787,7 +23913,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1132" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1132" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1132">
         <v>601</v>
       </c>
@@ -23816,7 +23942,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1133" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1133" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1133">
         <v>602</v>
       </c>
@@ -23845,7 +23971,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1134" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1134" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1134">
         <v>603</v>
       </c>
@@ -23874,7 +24000,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1135" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1135" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1135">
         <v>604</v>
       </c>
@@ -23903,7 +24029,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1136" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1136" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1136">
         <v>605</v>
       </c>
@@ -23932,7 +24058,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1137" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1137" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1137">
         <v>606</v>
       </c>
@@ -23961,7 +24087,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1138" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1138" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1138">
         <v>607</v>
       </c>
@@ -23990,7 +24116,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1139" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1139" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1139">
         <v>608</v>
       </c>
@@ -24019,7 +24145,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1140" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1140" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1140">
         <v>609</v>
       </c>
@@ -24048,7 +24174,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1141" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1141" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1141">
         <v>610</v>
       </c>
@@ -24077,7 +24203,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1142" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1142" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1142">
         <v>611</v>
       </c>
@@ -24106,7 +24232,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1143" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1143" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1143">
         <v>612</v>
       </c>
@@ -24135,7 +24261,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1144" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1144" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1144">
         <v>613</v>
       </c>
@@ -24164,7 +24290,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1145" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1145" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1145">
         <v>614</v>
       </c>
@@ -24193,7 +24319,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1146" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1146" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1146">
         <v>615</v>
       </c>
@@ -24222,7 +24348,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1147" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1147" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1147">
         <v>616</v>
       </c>
@@ -24251,7 +24377,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1148" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1148" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1148">
         <v>617</v>
       </c>
@@ -24277,7 +24403,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1149" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1149" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1149">
         <v>618</v>
       </c>
@@ -24303,7 +24429,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1150" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1150" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1150">
         <v>619</v>
       </c>
@@ -24329,7 +24455,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1151" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1151" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1151">
         <v>620</v>
       </c>
@@ -24358,7 +24484,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="1152" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1152" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1152">
         <v>621</v>
       </c>
@@ -24381,7 +24507,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="1153" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1153" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1153">
         <v>622</v>
       </c>
@@ -24404,7 +24530,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="1154" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1154" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1154">
         <v>307</v>
       </c>
@@ -24424,7 +24550,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="1155" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1155" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1155">
         <v>316</v>
       </c>
@@ -24444,7 +24570,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="1156" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1156" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1156">
         <v>320</v>
       </c>
@@ -24464,7 +24590,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="1157" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1157" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1157">
         <v>325</v>
       </c>
@@ -24484,7 +24610,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="1158" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1158" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1158">
         <v>336</v>
       </c>
@@ -24504,7 +24630,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="1159" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1159" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1159">
         <v>338</v>
       </c>
@@ -24527,7 +24653,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="1160" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1160" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1160">
         <v>344</v>
       </c>
@@ -24547,7 +24673,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="1161" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1161" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1161">
         <v>345</v>
       </c>
@@ -24567,7 +24693,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="1162" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1162" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1162">
         <v>346</v>
       </c>
@@ -24587,7 +24713,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="1163" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1163" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1163">
         <v>348</v>
       </c>
@@ -24607,7 +24733,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="1164" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1164" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1164">
         <v>349</v>
       </c>
@@ -24627,7 +24753,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="1165" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1165" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1165">
         <v>362</v>
       </c>
@@ -24650,7 +24776,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="1166" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1166" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1166">
         <v>364</v>
       </c>
@@ -24670,7 +24796,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="1167" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1167" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1167">
         <v>461</v>
       </c>
@@ -24681,7 +24807,7 @@
         <v>1301</v>
       </c>
       <c r="E1167" t="s">
-        <v>1068</v>
+        <v>1304</v>
       </c>
       <c r="F1167" t="s">
         <v>428</v>
@@ -24693,7 +24819,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="1168" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1168" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1168">
         <v>464</v>
       </c>
@@ -24716,7 +24842,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="1169" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1169" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1169">
         <v>465</v>
       </c>
@@ -24733,6 +24859,971 @@
         <v>428</v>
       </c>
       <c r="M1169" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1170" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1170">
+        <v>623</v>
+      </c>
+      <c r="B1170" s="3" t="s">
+        <v>1305</v>
+      </c>
+      <c r="D1170" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1170" t="s">
+        <v>1068</v>
+      </c>
+      <c r="F1170" t="s">
+        <v>428</v>
+      </c>
+      <c r="K1170" t="s">
+        <v>1088</v>
+      </c>
+      <c r="L1170" t="s">
+        <v>928</v>
+      </c>
+      <c r="M1170" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1171" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1171">
+        <v>624</v>
+      </c>
+      <c r="B1171" s="3" t="s">
+        <v>1306</v>
+      </c>
+      <c r="E1171" t="s">
+        <v>1304</v>
+      </c>
+      <c r="F1171" t="s">
+        <v>431</v>
+      </c>
+      <c r="K1171" t="s">
+        <v>717</v>
+      </c>
+      <c r="M1171" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1172" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1172">
+        <v>625</v>
+      </c>
+      <c r="B1172" s="3" t="s">
+        <v>1307</v>
+      </c>
+      <c r="E1172" t="s">
+        <v>1304</v>
+      </c>
+      <c r="F1172" t="s">
+        <v>428</v>
+      </c>
+      <c r="K1172" t="s">
+        <v>717</v>
+      </c>
+      <c r="M1172" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1173" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1173">
+        <v>626</v>
+      </c>
+      <c r="B1173" s="3" t="s">
+        <v>1308</v>
+      </c>
+      <c r="E1173" t="s">
+        <v>1304</v>
+      </c>
+      <c r="F1173" t="s">
+        <v>428</v>
+      </c>
+      <c r="K1173" t="s">
+        <v>717</v>
+      </c>
+      <c r="M1173" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1174" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A1174">
+        <v>627</v>
+      </c>
+      <c r="B1174" s="3" t="s">
+        <v>1309</v>
+      </c>
+      <c r="D1174" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1174" t="s">
+        <v>1304</v>
+      </c>
+      <c r="F1174" t="s">
+        <v>431</v>
+      </c>
+      <c r="K1174" t="s">
+        <v>1088</v>
+      </c>
+      <c r="M1174" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1175" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1175">
+        <v>628</v>
+      </c>
+      <c r="B1175" s="3" t="s">
+        <v>1310</v>
+      </c>
+      <c r="E1175" t="s">
+        <v>1304</v>
+      </c>
+      <c r="F1175" t="s">
+        <v>428</v>
+      </c>
+      <c r="K1175" t="s">
+        <v>1088</v>
+      </c>
+      <c r="M1175" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1176" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1176">
+        <v>629</v>
+      </c>
+      <c r="B1176" s="3" t="s">
+        <v>1311</v>
+      </c>
+      <c r="E1176" t="s">
+        <v>1304</v>
+      </c>
+      <c r="F1176" t="s">
+        <v>428</v>
+      </c>
+      <c r="K1176" t="s">
+        <v>1088</v>
+      </c>
+      <c r="M1176" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1177" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1177">
+        <v>630</v>
+      </c>
+      <c r="B1177" s="3" t="s">
+        <v>1312</v>
+      </c>
+      <c r="E1177" t="s">
+        <v>1304</v>
+      </c>
+      <c r="F1177" t="s">
+        <v>431</v>
+      </c>
+      <c r="K1177" t="s">
+        <v>1088</v>
+      </c>
+      <c r="M1177" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1178" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1178">
+        <v>631</v>
+      </c>
+      <c r="B1178" s="3" t="s">
+        <v>1313</v>
+      </c>
+      <c r="E1178" t="s">
+        <v>1304</v>
+      </c>
+      <c r="F1178" t="s">
+        <v>428</v>
+      </c>
+      <c r="K1178" t="s">
+        <v>1088</v>
+      </c>
+      <c r="M1178" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1179" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1179">
+        <v>632</v>
+      </c>
+      <c r="B1179" s="3" t="s">
+        <v>1314</v>
+      </c>
+      <c r="E1179" t="s">
+        <v>1304</v>
+      </c>
+      <c r="F1179" t="s">
+        <v>428</v>
+      </c>
+      <c r="K1179" t="s">
+        <v>1088</v>
+      </c>
+      <c r="M1179" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1180" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1180">
+        <v>633</v>
+      </c>
+      <c r="B1180" s="3" t="s">
+        <v>1315</v>
+      </c>
+      <c r="E1180" t="s">
+        <v>1304</v>
+      </c>
+      <c r="F1180" t="s">
+        <v>431</v>
+      </c>
+      <c r="K1180" t="s">
+        <v>1088</v>
+      </c>
+      <c r="M1180" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1181" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1181">
+        <v>634</v>
+      </c>
+      <c r="B1181" s="3" t="s">
+        <v>1316</v>
+      </c>
+      <c r="E1181" t="s">
+        <v>1304</v>
+      </c>
+      <c r="F1181" t="s">
+        <v>428</v>
+      </c>
+      <c r="K1181" t="s">
+        <v>1088</v>
+      </c>
+      <c r="M1181" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1182" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1182">
+        <v>635</v>
+      </c>
+      <c r="B1182" s="3" t="s">
+        <v>1317</v>
+      </c>
+      <c r="E1182" t="s">
+        <v>1304</v>
+      </c>
+      <c r="F1182" t="s">
+        <v>428</v>
+      </c>
+      <c r="K1182" t="s">
+        <v>1088</v>
+      </c>
+      <c r="M1182" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1183" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1183">
+        <v>636</v>
+      </c>
+      <c r="B1183" s="3" t="s">
+        <v>1318</v>
+      </c>
+      <c r="E1183" t="s">
+        <v>1304</v>
+      </c>
+      <c r="F1183" t="s">
+        <v>431</v>
+      </c>
+      <c r="K1183" t="s">
+        <v>1088</v>
+      </c>
+      <c r="M1183" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1184" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A1184">
+        <v>637</v>
+      </c>
+      <c r="B1184" s="3" t="s">
+        <v>1319</v>
+      </c>
+      <c r="E1184" t="s">
+        <v>1304</v>
+      </c>
+      <c r="F1184" t="s">
+        <v>428</v>
+      </c>
+      <c r="K1184" t="s">
+        <v>1088</v>
+      </c>
+      <c r="M1184" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1185" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1185">
+        <v>638</v>
+      </c>
+      <c r="B1185" s="3" t="s">
+        <v>1320</v>
+      </c>
+      <c r="E1185" t="s">
+        <v>1304</v>
+      </c>
+      <c r="F1185" t="s">
+        <v>428</v>
+      </c>
+      <c r="K1185" t="s">
+        <v>1088</v>
+      </c>
+      <c r="M1185" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1186" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1186">
+        <v>639</v>
+      </c>
+      <c r="B1186" s="3" t="s">
+        <v>1321</v>
+      </c>
+      <c r="E1186" t="s">
+        <v>1304</v>
+      </c>
+      <c r="F1186" t="s">
+        <v>428</v>
+      </c>
+      <c r="K1186" t="s">
+        <v>1088</v>
+      </c>
+      <c r="M1186" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1187" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1187">
+        <v>640</v>
+      </c>
+      <c r="B1187" s="3" t="s">
+        <v>1322</v>
+      </c>
+      <c r="E1187" t="s">
+        <v>1304</v>
+      </c>
+      <c r="F1187" t="s">
+        <v>431</v>
+      </c>
+      <c r="K1187" t="s">
+        <v>1088</v>
+      </c>
+      <c r="M1187" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1188" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1188">
+        <v>641</v>
+      </c>
+      <c r="B1188" s="3" t="s">
+        <v>1323</v>
+      </c>
+      <c r="E1188" t="s">
+        <v>1304</v>
+      </c>
+      <c r="F1188" t="s">
+        <v>428</v>
+      </c>
+      <c r="K1188" t="s">
+        <v>1088</v>
+      </c>
+      <c r="M1188" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1189" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1189">
+        <v>642</v>
+      </c>
+      <c r="B1189" s="3" t="s">
+        <v>1324</v>
+      </c>
+      <c r="E1189" t="s">
+        <v>1304</v>
+      </c>
+      <c r="F1189" t="s">
+        <v>431</v>
+      </c>
+      <c r="K1189" t="s">
+        <v>1088</v>
+      </c>
+      <c r="M1189" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1190" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1190">
+        <v>643</v>
+      </c>
+      <c r="B1190" s="3" t="s">
+        <v>1325</v>
+      </c>
+      <c r="E1190" t="s">
+        <v>1304</v>
+      </c>
+      <c r="F1190" t="s">
+        <v>428</v>
+      </c>
+      <c r="K1190" t="s">
+        <v>1088</v>
+      </c>
+      <c r="M1190" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1191" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1191">
+        <v>644</v>
+      </c>
+      <c r="B1191" s="3" t="s">
+        <v>1326</v>
+      </c>
+      <c r="E1191" t="s">
+        <v>1304</v>
+      </c>
+      <c r="F1191" t="s">
+        <v>428</v>
+      </c>
+      <c r="K1191" t="s">
+        <v>1088</v>
+      </c>
+      <c r="M1191" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1192" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1192">
+        <v>645</v>
+      </c>
+      <c r="B1192" s="3" t="s">
+        <v>1327</v>
+      </c>
+      <c r="E1192" t="s">
+        <v>1304</v>
+      </c>
+      <c r="F1192" t="s">
+        <v>431</v>
+      </c>
+      <c r="K1192" t="s">
+        <v>1088</v>
+      </c>
+      <c r="M1192" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1193" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1193">
+        <v>646</v>
+      </c>
+      <c r="B1193" s="3" t="s">
+        <v>1328</v>
+      </c>
+      <c r="E1193" t="s">
+        <v>1304</v>
+      </c>
+      <c r="F1193" t="s">
+        <v>428</v>
+      </c>
+      <c r="K1193" t="s">
+        <v>1088</v>
+      </c>
+      <c r="M1193" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1194" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1194">
+        <v>647</v>
+      </c>
+      <c r="B1194" s="3" t="s">
+        <v>1329</v>
+      </c>
+      <c r="E1194" t="s">
+        <v>1304</v>
+      </c>
+      <c r="F1194" t="s">
+        <v>428</v>
+      </c>
+      <c r="K1194" t="s">
+        <v>1088</v>
+      </c>
+      <c r="M1194" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1195" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1195">
+        <v>648</v>
+      </c>
+      <c r="B1195" s="3" t="s">
+        <v>1330</v>
+      </c>
+      <c r="E1195" t="s">
+        <v>1304</v>
+      </c>
+      <c r="F1195" t="s">
+        <v>428</v>
+      </c>
+      <c r="K1195" t="s">
+        <v>1088</v>
+      </c>
+      <c r="M1195" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1196" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1196">
+        <v>649</v>
+      </c>
+      <c r="B1196" s="3" t="s">
+        <v>1331</v>
+      </c>
+      <c r="E1196" t="s">
+        <v>1304</v>
+      </c>
+      <c r="F1196" t="s">
+        <v>431</v>
+      </c>
+      <c r="K1196" t="s">
+        <v>1088</v>
+      </c>
+      <c r="M1196" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1197" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1197">
+        <v>650</v>
+      </c>
+      <c r="B1197" s="3" t="s">
+        <v>1332</v>
+      </c>
+      <c r="E1197" t="s">
+        <v>1304</v>
+      </c>
+      <c r="F1197" t="s">
+        <v>428</v>
+      </c>
+      <c r="K1197" t="s">
+        <v>1088</v>
+      </c>
+      <c r="M1197" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1198" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1198">
+        <v>651</v>
+      </c>
+      <c r="B1198" s="3" t="s">
+        <v>1333</v>
+      </c>
+      <c r="E1198" t="s">
+        <v>1304</v>
+      </c>
+      <c r="F1198" t="s">
+        <v>428</v>
+      </c>
+      <c r="K1198" t="s">
+        <v>1088</v>
+      </c>
+      <c r="M1198" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1199" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1199">
+        <v>652</v>
+      </c>
+      <c r="B1199" s="3" t="s">
+        <v>1334</v>
+      </c>
+      <c r="E1199" t="s">
+        <v>1304</v>
+      </c>
+      <c r="F1199" t="s">
+        <v>428</v>
+      </c>
+      <c r="K1199" t="s">
+        <v>1088</v>
+      </c>
+      <c r="M1199" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1200" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1200">
+        <v>653</v>
+      </c>
+      <c r="B1200" s="3" t="s">
+        <v>1335</v>
+      </c>
+      <c r="E1200" t="s">
+        <v>1304</v>
+      </c>
+      <c r="F1200" t="s">
+        <v>428</v>
+      </c>
+      <c r="K1200" t="s">
+        <v>717</v>
+      </c>
+      <c r="M1200" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1201" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1201">
+        <v>654</v>
+      </c>
+      <c r="B1201" s="3" t="s">
+        <v>1336</v>
+      </c>
+      <c r="E1201" t="s">
+        <v>1304</v>
+      </c>
+      <c r="F1201" t="s">
+        <v>428</v>
+      </c>
+      <c r="K1201" t="s">
+        <v>1088</v>
+      </c>
+      <c r="M1201" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1202" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1202">
+        <v>655</v>
+      </c>
+      <c r="B1202" s="3" t="s">
+        <v>1337</v>
+      </c>
+      <c r="E1202" t="s">
+        <v>1304</v>
+      </c>
+      <c r="F1202" t="s">
+        <v>428</v>
+      </c>
+      <c r="K1202" t="s">
+        <v>1088</v>
+      </c>
+      <c r="M1202" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1203" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1203">
+        <v>656</v>
+      </c>
+      <c r="B1203" s="3" t="s">
+        <v>1338</v>
+      </c>
+      <c r="E1203" t="s">
+        <v>1304</v>
+      </c>
+      <c r="F1203" t="s">
+        <v>428</v>
+      </c>
+      <c r="K1203" t="s">
+        <v>1088</v>
+      </c>
+      <c r="M1203" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1204" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1204">
+        <v>657</v>
+      </c>
+      <c r="B1204" s="3" t="s">
+        <v>1339</v>
+      </c>
+      <c r="E1204" t="s">
+        <v>1304</v>
+      </c>
+      <c r="F1204" t="s">
+        <v>428</v>
+      </c>
+      <c r="K1204" t="s">
+        <v>1088</v>
+      </c>
+      <c r="M1204" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1205" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1205">
+        <v>658</v>
+      </c>
+      <c r="B1205" s="3" t="s">
+        <v>1340</v>
+      </c>
+      <c r="E1205" t="s">
+        <v>1304</v>
+      </c>
+      <c r="F1205" t="s">
+        <v>428</v>
+      </c>
+      <c r="K1205" t="s">
+        <v>1088</v>
+      </c>
+      <c r="M1205" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1206" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1206">
+        <v>659</v>
+      </c>
+      <c r="B1206" s="3" t="s">
+        <v>1341</v>
+      </c>
+      <c r="E1206" t="s">
+        <v>1304</v>
+      </c>
+      <c r="F1206" t="s">
+        <v>428</v>
+      </c>
+      <c r="K1206" t="s">
+        <v>1088</v>
+      </c>
+      <c r="M1206" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1207" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1207">
+        <v>660</v>
+      </c>
+      <c r="B1207" s="3" t="s">
+        <v>1342</v>
+      </c>
+      <c r="E1207" t="s">
+        <v>1304</v>
+      </c>
+      <c r="F1207" t="s">
+        <v>428</v>
+      </c>
+      <c r="K1207" t="s">
+        <v>1088</v>
+      </c>
+      <c r="M1207" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1208" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1208">
+        <v>661</v>
+      </c>
+      <c r="B1208" s="3" t="s">
+        <v>1343</v>
+      </c>
+      <c r="E1208" t="s">
+        <v>1304</v>
+      </c>
+      <c r="F1208" t="s">
+        <v>428</v>
+      </c>
+      <c r="K1208" t="s">
+        <v>1088</v>
+      </c>
+      <c r="M1208" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1209" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1209">
+        <v>326</v>
+      </c>
+      <c r="B1209" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="C1209" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="D1209" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1209" t="s">
+        <v>1344</v>
+      </c>
+      <c r="F1209" t="s">
+        <v>428</v>
+      </c>
+      <c r="K1209" t="s">
+        <v>688</v>
+      </c>
+      <c r="M1209" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1210" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A1210">
+        <v>328</v>
+      </c>
+      <c r="B1210" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="C1210" s="3" t="s">
+        <v>617</v>
+      </c>
+      <c r="D1210" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1210" t="s">
+        <v>1344</v>
+      </c>
+      <c r="F1210" t="s">
+        <v>431</v>
+      </c>
+      <c r="K1210" t="s">
+        <v>688</v>
+      </c>
+      <c r="M1210" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1211" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1211">
+        <v>337</v>
+      </c>
+      <c r="B1211" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="C1211" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="D1211" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1211" t="s">
+        <v>1345</v>
+      </c>
+      <c r="F1211" t="s">
+        <v>428</v>
+      </c>
+      <c r="K1211" t="s">
+        <v>688</v>
+      </c>
+      <c r="L1211" t="s">
+        <v>926</v>
+      </c>
+      <c r="M1211" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1212" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A1212">
+        <v>350</v>
+      </c>
+      <c r="B1212" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="C1212" s="3" t="s">
+        <v>639</v>
+      </c>
+      <c r="D1212" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1212" t="s">
+        <v>1344</v>
+      </c>
+      <c r="F1212" t="s">
+        <v>428</v>
+      </c>
+      <c r="K1212" t="s">
+        <v>696</v>
+      </c>
+      <c r="M1212" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1213" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="A1213">
+        <v>351</v>
+      </c>
+      <c r="B1213" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="C1213" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="D1213" t="s">
+        <v>868</v>
+      </c>
+      <c r="E1213" t="s">
+        <v>1068</v>
+      </c>
+      <c r="F1213" t="s">
+        <v>428</v>
+      </c>
+      <c r="K1213" t="s">
+        <v>696</v>
+      </c>
+      <c r="M1213" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1214" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1214">
+        <v>360</v>
+      </c>
+      <c r="B1214" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="C1214" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="E1214" t="s">
+        <v>1345</v>
+      </c>
+      <c r="F1214" t="s">
+        <v>431</v>
+      </c>
+      <c r="M1214" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1215" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1215">
+        <v>361</v>
+      </c>
+      <c r="B1215" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="C1215" s="3" t="s">
+        <v>650</v>
+      </c>
+      <c r="D1215" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1215" t="s">
+        <v>1344</v>
+      </c>
+      <c r="F1215" t="s">
+        <v>428</v>
+      </c>
+      <c r="M1215" t="s">
         <v>69</v>
       </c>
     </row>
@@ -24810,42 +25901,42 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:A7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="48.109375" customWidth="1"/>
+    <col min="1" max="1" width="48.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
         <v>66</v>
       </c>

--- a/project_time_sheet.xlsx
+++ b/project_time_sheet.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94D1AB1E-C469-4E40-A1AA-4EFF035FF54C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91B4AD7D-A954-4152-8836-CF0E9DDF5EDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3900" uniqueCount="1346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3921" uniqueCount="1346">
   <si>
     <t xml:space="preserve">  Project Time Sheet — User Guide</t>
   </si>
@@ -24978,11 +24978,14 @@
       <c r="B1175" s="3" t="s">
         <v>1310</v>
       </c>
+      <c r="D1175" t="s">
+        <v>61</v>
+      </c>
       <c r="E1175" t="s">
         <v>1304</v>
       </c>
       <c r="F1175" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="K1175" t="s">
         <v>1088</v>
@@ -25022,7 +25025,7 @@
         <v>1304</v>
       </c>
       <c r="F1177" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="K1177" t="s">
         <v>1088</v>
@@ -25038,6 +25041,9 @@
       <c r="B1178" s="3" t="s">
         <v>1313</v>
       </c>
+      <c r="D1178" t="s">
+        <v>61</v>
+      </c>
       <c r="E1178" t="s">
         <v>1304</v>
       </c>
@@ -25058,11 +25064,14 @@
       <c r="B1179" s="3" t="s">
         <v>1314</v>
       </c>
+      <c r="D1179" t="s">
+        <v>61</v>
+      </c>
       <c r="E1179" t="s">
         <v>1304</v>
       </c>
       <c r="F1179" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="K1179" t="s">
         <v>1088</v>
@@ -25078,11 +25087,14 @@
       <c r="B1180" s="3" t="s">
         <v>1315</v>
       </c>
+      <c r="D1180" t="s">
+        <v>61</v>
+      </c>
       <c r="E1180" t="s">
         <v>1304</v>
       </c>
       <c r="F1180" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="K1180" t="s">
         <v>1088</v>
@@ -25102,7 +25114,7 @@
         <v>1304</v>
       </c>
       <c r="F1181" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="K1181" t="s">
         <v>1088</v>
@@ -25142,7 +25154,7 @@
         <v>1304</v>
       </c>
       <c r="F1183" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="K1183" t="s">
         <v>1088</v>
@@ -25178,11 +25190,14 @@
       <c r="B1185" s="3" t="s">
         <v>1320</v>
       </c>
+      <c r="D1185" t="s">
+        <v>61</v>
+      </c>
       <c r="E1185" t="s">
         <v>1304</v>
       </c>
       <c r="F1185" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="K1185" t="s">
         <v>1088</v>
@@ -25198,11 +25213,14 @@
       <c r="B1186" s="3" t="s">
         <v>1321</v>
       </c>
+      <c r="D1186" t="s">
+        <v>61</v>
+      </c>
       <c r="E1186" t="s">
         <v>1304</v>
       </c>
       <c r="F1186" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="K1186" t="s">
         <v>1088</v>
@@ -25218,11 +25236,14 @@
       <c r="B1187" s="3" t="s">
         <v>1322</v>
       </c>
+      <c r="D1187" t="s">
+        <v>61</v>
+      </c>
       <c r="E1187" t="s">
         <v>1304</v>
       </c>
       <c r="F1187" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="K1187" t="s">
         <v>1088</v>
@@ -25258,8 +25279,11 @@
       <c r="B1189" s="3" t="s">
         <v>1324</v>
       </c>
+      <c r="D1189" t="s">
+        <v>61</v>
+      </c>
       <c r="E1189" t="s">
-        <v>1304</v>
+        <v>78</v>
       </c>
       <c r="F1189" t="s">
         <v>431</v>
@@ -25278,6 +25302,9 @@
       <c r="B1190" s="3" t="s">
         <v>1325</v>
       </c>
+      <c r="D1190" t="s">
+        <v>61</v>
+      </c>
       <c r="E1190" t="s">
         <v>1304</v>
       </c>
@@ -25318,6 +25345,9 @@
       <c r="B1192" s="3" t="s">
         <v>1327</v>
       </c>
+      <c r="D1192" t="s">
+        <v>61</v>
+      </c>
       <c r="E1192" t="s">
         <v>1304</v>
       </c>
@@ -25338,11 +25368,14 @@
       <c r="B1193" s="3" t="s">
         <v>1328</v>
       </c>
+      <c r="D1193" t="s">
+        <v>61</v>
+      </c>
       <c r="E1193" t="s">
-        <v>1304</v>
+        <v>78</v>
       </c>
       <c r="F1193" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="K1193" t="s">
         <v>1088</v>
@@ -25362,7 +25395,7 @@
         <v>1304</v>
       </c>
       <c r="F1194" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="K1194" t="s">
         <v>1088</v>
@@ -25378,6 +25411,9 @@
       <c r="B1195" s="3" t="s">
         <v>1330</v>
       </c>
+      <c r="D1195" t="s">
+        <v>61</v>
+      </c>
       <c r="E1195" t="s">
         <v>1304</v>
       </c>
@@ -25402,7 +25438,7 @@
         <v>1304</v>
       </c>
       <c r="F1196" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="K1196" t="s">
         <v>1088</v>
@@ -25418,11 +25454,14 @@
       <c r="B1197" s="3" t="s">
         <v>1332</v>
       </c>
+      <c r="D1197" t="s">
+        <v>61</v>
+      </c>
       <c r="E1197" t="s">
         <v>1304</v>
       </c>
       <c r="F1197" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="K1197" t="s">
         <v>1088</v>
@@ -25438,11 +25477,14 @@
       <c r="B1198" s="3" t="s">
         <v>1333</v>
       </c>
+      <c r="D1198" t="s">
+        <v>61</v>
+      </c>
       <c r="E1198" t="s">
         <v>1304</v>
       </c>
       <c r="F1198" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="K1198" t="s">
         <v>1088</v>
@@ -25458,11 +25500,14 @@
       <c r="B1199" s="3" t="s">
         <v>1334</v>
       </c>
+      <c r="D1199" t="s">
+        <v>61</v>
+      </c>
       <c r="E1199" t="s">
         <v>1304</v>
       </c>
       <c r="F1199" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="K1199" t="s">
         <v>1088</v>
@@ -25518,11 +25563,14 @@
       <c r="B1202" s="3" t="s">
         <v>1337</v>
       </c>
+      <c r="D1202" t="s">
+        <v>62</v>
+      </c>
       <c r="E1202" t="s">
         <v>1304</v>
       </c>
       <c r="F1202" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="K1202" t="s">
         <v>1088</v>
@@ -25558,6 +25606,9 @@
       <c r="B1204" s="3" t="s">
         <v>1339</v>
       </c>
+      <c r="D1204" t="s">
+        <v>61</v>
+      </c>
       <c r="E1204" t="s">
         <v>1304</v>
       </c>
@@ -25578,11 +25629,14 @@
       <c r="B1205" s="3" t="s">
         <v>1340</v>
       </c>
+      <c r="D1205" t="s">
+        <v>61</v>
+      </c>
       <c r="E1205" t="s">
         <v>1304</v>
       </c>
       <c r="F1205" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="K1205" t="s">
         <v>1088</v>
@@ -25598,6 +25652,9 @@
       <c r="B1206" s="3" t="s">
         <v>1341</v>
       </c>
+      <c r="D1206" t="s">
+        <v>61</v>
+      </c>
       <c r="E1206" t="s">
         <v>1304</v>
       </c>
@@ -25618,6 +25675,9 @@
       <c r="B1207" s="3" t="s">
         <v>1342</v>
       </c>
+      <c r="D1207" t="s">
+        <v>61</v>
+      </c>
       <c r="E1207" t="s">
         <v>1304</v>
       </c>
@@ -25637,6 +25697,9 @@
       </c>
       <c r="B1208" s="3" t="s">
         <v>1343</v>
+      </c>
+      <c r="D1208" t="s">
+        <v>61</v>
       </c>
       <c r="E1208" t="s">
         <v>1304</v>
@@ -25953,15 +26016,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100959716F11FB6F9409089B98D1C11D330" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bc55ac45923017d94ee4534da3224188">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2e20d828-e3fd-41fd-921c-fbe0ff523ae8" xmlns:ns3="adfc7943-f9ee-4478-a01e-ebfcb6e54f53" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5bc17ad4f23ab8382a0bb5b03decca58" ns2:_="" ns3:_="">
     <xsd:import namespace="2e20d828-e3fd-41fd-921c-fbe0ff523ae8"/>
@@ -26216,6 +26270,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -26228,14 +26291,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{737DCCA1-99B2-40A5-A4E9-9FBBAC380C60}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CE6A3B7-F954-4629-B802-2205DECE6851}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -26254,6 +26309,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{737DCCA1-99B2-40A5-A4E9-9FBBAC380C60}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{407A8743-A532-48E3-9004-715BF423F4DA}">
   <ds:schemaRefs>
